--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Ra9d124309b454e2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="Rb4e61b54807c4cb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="Rd367eae3a35e4f80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="R694ebbb3e90b43d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="Rb8d9515338ac451f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R5e2ea74fc504431a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R2993a1d994fb4336"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd7404e0a428f4a17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="Ra82668d8132142ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R9370d4144ded4990"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="R65cd50a8a54c4972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="R2ee49ae408fc4191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R0cd5248b7b1f42de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R8a9e52306752465b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="15">
+  <x:fonts count="16">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -104,8 +104,14 @@
       <x:color rgb="FF1565C0"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF243B53"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -132,8 +138,18 @@
         <x:fgColor rgb="FFFFF4E5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF155E75"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF155E75"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -149,11 +165,25 @@
         <x:color rgb="FFC9D8E3"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E3EA"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD8E3EA"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E3EA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E3EA"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="55">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -230,6 +260,46 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -457,7 +527,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="25" t="str">
-        <x:v>设计、内容与实现状态的中央索引｜最后核对：2026-08-04｜正式入口：TowerDescent3D.tscn</x:v>
+        <x:v>设计、内容与实现状态的中央索引｜最后核对：2026-08-05｜正式入口：TowerDescent3D.tscn</x:v>
       </x:c>
       <x:c r="B2" s="25"/>
       <x:c r="C2" s="25"/>
@@ -532,7 +602,7 @@
         <x:v>枪身、子弹、配件、数值、价格和产出</x:v>
       </x:c>
       <x:c r="H6" s="29" t="str">
-        <x:v>正式3D以BlueprintRegistry为数值源</x:v>
+        <x:v>枪型定义与WeaponInstance分离；实例/命运槽/装配随枪已验收，逐条专属表现待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="46" customHeight="1">
@@ -562,7 +632,7 @@
         <x:v>28张卡片功能、参数和背景</x:v>
       </x:c>
       <x:c r="H7" s="29" t="str">
-        <x:v>先迁移稳定ID，再做跨局存档</x:v>
+        <x:v>三作用域22/2/4张已运行时路由；作用域/目标/槽位提示已实装</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="46" customHeight="1">
@@ -652,7 +722,7 @@
         <x:v>物品、价格、稀有度和掉落池</x:v>
       </x:c>
       <x:c r="H10" s="29" t="str">
-        <x:v>Boss专钥匙不可进入普通池</x:v>
+        <x:v>武器成品必须携带实例ID与完整构筑快照</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -733,16 +803,16 @@
         <x:v>已冻结</x:v>
       </x:c>
       <x:c r="E15" s="29" t="str">
-        <x:v>正式3D可用</x:v>
+        <x:v>正式3D核心闭环已验收</x:v>
       </x:c>
       <x:c r="F15" s="29" t="str">
-        <x:v>稳定ID/逐卡QA</x:v>
+        <x:v>逐卡专属表现QA/高级比较</x:v>
       </x:c>
       <x:c r="G15" s="29" t="str">
         <x:v>04_技术施工_战斗与局内成长.md</x:v>
       </x:c>
       <x:c r="H15" s="29" t="str">
-        <x:v>平行配置待治理</x:v>
+        <x:v>构筑随具体枪械实例；唯一ID、8槽、作用域、换装、保险、撤离与存档已实装</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -863,10 +933,10 @@
         <x:v>边界已冻结</x:v>
       </x:c>
       <x:c r="E20" s="29" t="str">
-        <x:v>基地/结算可用</x:v>
+        <x:v>基地/结算与武器实例迁移可用</x:v>
       </x:c>
       <x:c r="F20" s="29" t="str">
-        <x:v>多域事务/迁移</x:v>
+        <x:v>结算幂等/复活策略</x:v>
       </x:c>
       <x:c r="G20" s="29" t="str">
         <x:v>09_技术施工_存档结算与复活.md</x:v>
@@ -917,6 +987,12 @@
     <x:col min="12" max="12" width="28" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="34" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="40" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="13" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="39" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="30" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="42" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="42" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -939,7 +1015,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>现有正式注册表：7枪身、8子弹、6配件。枪身价格/掉落取可拾取成品，蓝图掉落另列；权重只在同一掉落池内比较。</x:v>
+        <x:v>正式注册：7枪身、8子弹、6配件。独立WeaponInstance与普通枪8命运槽已实装；实例/槽位/装配基础反馈已验收，逐条专属表现继续QA。</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -1016,6 +1092,24 @@
       <x:c r="N4" s="13" t="str">
         <x:v>备注</x:v>
       </x:c>
+      <x:c r="O4" s="48" t="str">
+        <x:v>基础命运槽</x:v>
+      </x:c>
+      <x:c r="P4" s="48" t="str">
+        <x:v>实例/装配规则</x:v>
+      </x:c>
+      <x:c r="Q4" s="48" t="str">
+        <x:v>新设计实现状态</x:v>
+      </x:c>
+      <x:c r="R4" s="48" t="str">
+        <x:v>功能UI提示</x:v>
+      </x:c>
+      <x:c r="S4" s="48" t="str">
+        <x:v>武器/战斗表现</x:v>
+      </x:c>
+      <x:c r="T4" s="48" t="str">
+        <x:v>表现实现状态</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="17" t="str">
@@ -1058,6 +1152,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N5" s="17" t="str"/>
+      <x:c r="O5" s="46"/>
+      <x:c r="P5" s="45" t="str">
+        <x:v>可拆卸、可替换、可交易；不占命运槽；安装结果写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q5" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R5" s="45" t="str">
+        <x:v>弹匣槽显示容量/换弹差值与治疗触发说明；安装前后对比，注明可拆卸、不占命运槽</x:v>
+      </x:c>
+      <x:c r="S5" s="45" t="str">
+        <x:v>更大弹匣实体与换弹动作同步；治疗触发时弹匣图标和绿色脉冲同时出现</x:v>
+      </x:c>
+      <x:c r="T5" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="17" t="str">
@@ -1100,6 +1210,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N6" s="17" t="str"/>
+      <x:c r="O6" s="46"/>
+      <x:c r="P6" s="45" t="str">
+        <x:v>可拆卸、可替换、可交易；不占命运槽；安装结果写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q6" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R6" s="45" t="str">
+        <x:v>外接槽显示复制概率、可复制对象和触发条件；触发链显示来源与限制</x:v>
+      </x:c>
+      <x:c r="S6" s="45" t="str">
+        <x:v>枪身出现实体贴纸；触发复制时产生对象残影、专属图标脉冲和短音效</x:v>
+      </x:c>
+      <x:c r="T6" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="17" t="str">
@@ -1142,6 +1268,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N7" s="17" t="str"/>
+      <x:c r="O7" s="46"/>
+      <x:c r="P7" s="45" t="str">
+        <x:v>可拆卸、可替换、可交易；不占命运槽；安装结果写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q7" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R7" s="45" t="str">
+        <x:v>外接槽显示拉力强度、作用对象和范围；战斗HUD保留吸附行为图标</x:v>
+      </x:c>
+      <x:c r="S7" s="45" t="str">
+        <x:v>小风扇叶片持续转动；受力对象显示朝向流线，触发点播放吸附短音</x:v>
+      </x:c>
+      <x:c r="T7" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="17" t="str">
@@ -1184,6 +1326,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N8" s="17" t="str"/>
+      <x:c r="O8" s="46"/>
+      <x:c r="P8" s="45" t="str">
+        <x:v>可拆卸、可替换、可交易；不占命运槽；安装结果写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q8" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R8" s="45" t="str">
+        <x:v>枪托槽显示扩散变化和弹跳行为；提供准星散布前后对比</x:v>
+      </x:c>
+      <x:c r="S8" s="45" t="str">
+        <x:v>橡胶枪托实体挂接；后坐/准星收束可见，弹跳命中显示方向折线</x:v>
+      </x:c>
+      <x:c r="T8" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="17" t="str">
@@ -1226,6 +1384,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N9" s="17" t="str"/>
+      <x:c r="O9" s="46"/>
+      <x:c r="P9" s="45" t="str">
+        <x:v>可拆卸、可替换、可交易；不占命运槽；安装结果写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q9" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R9" s="45" t="str">
+        <x:v>瞄具槽显示伤害、扩散/暴击来源和瞄准差值；注明兼容枪型</x:v>
+      </x:c>
+      <x:c r="S9" s="45" t="str">
+        <x:v>实际瞄具模型、瞄准姿态与准星同步变化；暴击命中使用高亮反馈</x:v>
+      </x:c>
+      <x:c r="T9" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="17" t="str">
@@ -1268,6 +1442,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N10" s="17" t="str"/>
+      <x:c r="O10" s="46"/>
+      <x:c r="P10" s="45" t="str">
+        <x:v>可拆卸、可替换、可交易；不占命运槽；安装结果写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q10" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R10" s="45" t="str">
+        <x:v>枪口槽显示弹丸数与扩散差值，并预览弹道扇形</x:v>
+      </x:c>
+      <x:c r="S10" s="45" t="str">
+        <x:v>三叉枪口实体；开火时多枪口火焰、多弹道和声层同步</x:v>
+      </x:c>
+      <x:c r="T10" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="17" t="str">
@@ -1310,6 +1500,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N11" s="17" t="str"/>
+      <x:c r="O11" s="46"/>
+      <x:c r="P11" s="45" t="str">
+        <x:v>可更换子弹模块；不占命运槽；弹道配置写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q11" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R11" s="45" t="str">
+        <x:v>子弹页显示体积、伤害、速度差值和大型弹体标签</x:v>
+      </x:c>
+      <x:c r="S11" s="45" t="str">
+        <x:v>膨胀弹体、较重尾迹与命中体积一致，不能只改伤害数值</x:v>
+      </x:c>
+      <x:c r="T11" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="17" t="str">
@@ -1352,6 +1558,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N12" s="17" t="str"/>
+      <x:c r="O12" s="46"/>
+      <x:c r="P12" s="45" t="str">
+        <x:v>可更换子弹模块；不占命运槽；弹道配置写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q12" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R12" s="45" t="str">
+        <x:v>显示伤害、速度、牵引范围/强度和受影响对象</x:v>
+      </x:c>
+      <x:c r="S12" s="45" t="str">
+        <x:v>黑洞核心、吸入流线和范围边界清晰；命中/结束有收束反馈</x:v>
+      </x:c>
+      <x:c r="T12" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="17" t="str">
@@ -1394,6 +1616,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N13" s="17" t="str"/>
+      <x:c r="O13" s="46"/>
+      <x:c r="P13" s="45" t="str">
+        <x:v>可更换子弹模块；不占命运槽；弹道配置写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q13" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R13" s="45" t="str">
+        <x:v>显示弹跳次数、可反弹表面和剩余次数</x:v>
+      </x:c>
+      <x:c r="S13" s="45" t="str">
+        <x:v>反弹点有折线闪光与计数递减，飞行方向变化清楚可读</x:v>
+      </x:c>
+      <x:c r="T13" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="17" t="str">
@@ -1436,6 +1674,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N14" s="17" t="str"/>
+      <x:c r="O14" s="46"/>
+      <x:c r="P14" s="45" t="str">
+        <x:v>可更换子弹模块；不占命运槽；弹道配置写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q14" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R14" s="45" t="str">
+        <x:v>显示爆炸伤害、半径和触发时机；地面预览危险圈</x:v>
+      </x:c>
+      <x:c r="S14" s="45" t="str">
+        <x:v>弹体、尾迹、爆炸半径与伤害时点同步，低特效下保留轮廓圈</x:v>
+      </x:c>
+      <x:c r="T14" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="17" t="str">
@@ -1478,6 +1732,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N15" s="17" t="str"/>
+      <x:c r="O15" s="46"/>
+      <x:c r="P15" s="45" t="str">
+        <x:v>可更换子弹模块；不占命运槽；弹道配置写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q15" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R15" s="45" t="str">
+        <x:v>显示追踪强度、锁定条件和当前目标标记</x:v>
+      </x:c>
+      <x:c r="S15" s="45" t="str">
+        <x:v>锁定框、弯曲尾迹和转向动作一致；目标丢失有解除提示</x:v>
+      </x:c>
+      <x:c r="T15" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="17" t="str">
@@ -1520,6 +1790,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N16" s="17" t="str"/>
+      <x:c r="O16" s="46"/>
+      <x:c r="P16" s="45" t="str">
+        <x:v>可更换子弹模块；不占命运槽；弹道配置写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q16" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R16" s="45" t="str">
+        <x:v>显示穿透等级、可穿对象和命中衰减规则</x:v>
+      </x:c>
+      <x:c r="S16" s="45" t="str">
+        <x:v>穿透命中显示连续贯穿线与剩余层数，不在首个目标处假性消失</x:v>
+      </x:c>
+      <x:c r="T16" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="17" t="str">
@@ -1562,6 +1848,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N17" s="17" t="str"/>
+      <x:c r="O17" s="46"/>
+      <x:c r="P17" s="45" t="str">
+        <x:v>可更换子弹模块；不占命运槽；弹道配置写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q17" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R17" s="45" t="str">
+        <x:v>显示为基准弹药，并作为其他模块的属性/行为对比基线</x:v>
+      </x:c>
+      <x:c r="S17" s="45" t="str">
+        <x:v>使用清晰中性弹体、尾迹和命中；不附加误导性的元素效果</x:v>
+      </x:c>
+      <x:c r="T17" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="17" t="str">
@@ -1604,6 +1906,22 @@
         <x:v>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="N18" s="17" t="str"/>
+      <x:c r="O18" s="46"/>
+      <x:c r="P18" s="45" t="str">
+        <x:v>可更换子弹模块；不占命运槽；弹道配置写入目标weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="Q18" s="47" t="str">
+        <x:v>[已实装] 可换装、不占命运槽，并随目标WeaponInstance完整保存/恢复</x:v>
+      </x:c>
+      <x:c r="R18" s="45" t="str">
+        <x:v>显示黏附对象、持续/引爆条件与每秒效果</x:v>
+      </x:c>
+      <x:c r="S18" s="45" t="str">
+        <x:v>命中后弹体留在表面并显示倒计时/状态，结束时反馈与结算同步</x:v>
+      </x:c>
+      <x:c r="T18" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="17" t="str">
@@ -1649,6 +1967,24 @@
       <x:c r="N19" s="17" t="str">
         <x:v>装配ID=bp_charge；成品物品ID=weapon_charge；蓝图物品ID=bp_charge</x:v>
       </x:c>
+      <x:c r="O19" s="46" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P19" s="45" t="str">
+        <x:v>成品生成永久weapon_instance_id；命运槽、子弹模块与配件随实例在装备/背包/地面/商店/保险/存档间移动</x:v>
+      </x:c>
+      <x:c r="Q19" s="47" t="str">
+        <x:v>[已实装] 唯一实例ID、8槽基线、完整构筑/弹药/命运记录随枪转移与存档</x:v>
+      </x:c>
+      <x:c r="R19" s="45" t="str">
+        <x:v>HUD和详情显示蓄力阶段、当前倍率、超蓄力风险、弹量和换弹</x:v>
+      </x:c>
+      <x:c r="S19" s="45" t="str">
+        <x:v>枪身能量逐级充盈、音高与震动递增；释放弹体大小和穿透随阶段变化</x:v>
+      </x:c>
+      <x:c r="T19" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="17" t="str">
@@ -1694,6 +2030,24 @@
       <x:c r="N20" s="17" t="str">
         <x:v>装配ID=bp_launcher；成品物品ID=weapon_launcher；蓝图物品ID=bp_launcher</x:v>
       </x:c>
+      <x:c r="O20" s="46" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P20" s="45" t="str">
+        <x:v>成品生成永久weapon_instance_id；命运槽、子弹模块与配件随实例在装备/背包/地面/商店/保险/存档间移动</x:v>
+      </x:c>
+      <x:c r="Q20" s="47" t="str">
+        <x:v>[已实装] 唯一实例ID、8槽基线、完整构筑/弹药/命运记录随枪转移与存档</x:v>
+      </x:c>
+      <x:c r="R20" s="45" t="str">
+        <x:v>显示抛物线、爆炸半径、弹量与安全距离；瞄准时给落点预览</x:v>
+      </x:c>
+      <x:c r="S20" s="45" t="str">
+        <x:v>发射器抬升动作、弧线弹道、落点圈和爆炸反馈一致</x:v>
+      </x:c>
+      <x:c r="T20" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="17" t="str">
@@ -1739,6 +2093,24 @@
       <x:c r="N21" s="17" t="str">
         <x:v>装配ID=bp_machinegun；成品物品ID=weapon_machinegun；蓝图物品ID=bp_machinegun</x:v>
       </x:c>
+      <x:c r="O21" s="46" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P21" s="45" t="str">
+        <x:v>成品生成永久weapon_instance_id；命运槽、子弹模块与配件随实例在装备/背包/地面/商店/保险/存档间移动</x:v>
+      </x:c>
+      <x:c r="Q21" s="47" t="str">
+        <x:v>[已实装] 唯一实例ID、8槽基线、完整构筑/弹药/命运记录随枪转移与存档</x:v>
+      </x:c>
+      <x:c r="R21" s="45" t="str">
+        <x:v>显示高射速、弹量、扩散与持续射击节奏；低弹药警告明显</x:v>
+      </x:c>
+      <x:c r="S21" s="45" t="str">
+        <x:v>连续枪口焰、机械循环和后坐累积可读，不能用单发动画冒充连射</x:v>
+      </x:c>
+      <x:c r="T21" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="17" t="str">
@@ -1784,6 +2156,24 @@
       <x:c r="N22" s="17" t="str">
         <x:v>装配ID=bp_pistol；成品物品ID=weapon_pistol；蓝图物品ID=bp_pistol</x:v>
       </x:c>
+      <x:c r="O22" s="46" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P22" s="45" t="str">
+        <x:v>成品生成永久weapon_instance_id；命运槽、子弹模块与配件随实例在装备/背包/地面/商店/保险/存档间移动</x:v>
+      </x:c>
+      <x:c r="Q22" s="47" t="str">
+        <x:v>[已实装] 唯一实例ID、8槽基线、完整构筑/弹药/命运记录随枪转移与存档</x:v>
+      </x:c>
+      <x:c r="R22" s="45" t="str">
+        <x:v>显示半自动节奏、伤害、弹量与精准度，作为轻型基准枪比较</x:v>
+      </x:c>
+      <x:c r="S22" s="45" t="str">
+        <x:v>每次点击有清晰单发后坐、枪口焰与复位，轮廓轻巧</x:v>
+      </x:c>
+      <x:c r="T22" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="17" t="str">
@@ -1829,6 +2219,24 @@
       <x:c r="N23" s="17" t="str">
         <x:v>装配ID=bp_rifle；成品物品ID=weapon_rifle；蓝图物品ID=bp_rifle</x:v>
       </x:c>
+      <x:c r="O23" s="46" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P23" s="45" t="str">
+        <x:v>成品生成永久weapon_instance_id；命运槽、子弹模块与配件随实例在装备/背包/地面/商店/保险/存档间移动</x:v>
+      </x:c>
+      <x:c r="Q23" s="47" t="str">
+        <x:v>[已实装] 唯一实例ID、8槽基线、完整构筑/弹药/命运记录随枪转移与存档</x:v>
+      </x:c>
+      <x:c r="R23" s="45" t="str">
+        <x:v>显示中距离连发、伤害、射速、弹量和扩散的平衡定位</x:v>
+      </x:c>
+      <x:c r="S23" s="45" t="str">
+        <x:v>连发节奏、枪身动作和中等后坐一致，弹道辨识稳定</x:v>
+      </x:c>
+      <x:c r="T23" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="17" t="str">
@@ -1874,6 +2282,24 @@
       <x:c r="N24" s="17" t="str">
         <x:v>装配ID=bp_shotgun；成品物品ID=weapon_shotgun；蓝图物品ID=bp_shotgun</x:v>
       </x:c>
+      <x:c r="O24" s="46" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P24" s="45" t="str">
+        <x:v>成品生成永久weapon_instance_id；命运槽、子弹模块与配件随实例在装备/背包/地面/商店/保险/存档间移动</x:v>
+      </x:c>
+      <x:c r="Q24" s="47" t="str">
+        <x:v>[已实装] 唯一实例ID、8槽基线、完整构筑/弹药/命运记录随枪转移与存档</x:v>
+      </x:c>
+      <x:c r="R24" s="45" t="str">
+        <x:v>显示每发弹丸数、散布锥、近距收益、弹量与换弹</x:v>
+      </x:c>
+      <x:c r="S24" s="45" t="str">
+        <x:v>多弹丸扇形、强后坐和近距命中层次同步；命中数量可读</x:v>
+      </x:c>
+      <x:c r="T24" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="17" t="str">
@@ -1919,16 +2345,38 @@
       <x:c r="N25" s="17" t="str">
         <x:v>装配ID=bp_sniper；成品物品ID=weapon_sniper；蓝图物品ID=bp_sniper</x:v>
       </x:c>
+      <x:c r="O25" s="46" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P25" s="45" t="str">
+        <x:v>成品生成永久weapon_instance_id；命运槽、子弹模块与配件随实例在装备/背包/地面/商店/保险/存档间移动</x:v>
+      </x:c>
+      <x:c r="Q25" s="47" t="str">
+        <x:v>[已实装] 唯一实例ID、8槽基线、完整构筑/弹药/命运记录随枪转移与存档</x:v>
+      </x:c>
+      <x:c r="R25" s="45" t="str">
+        <x:v>显示高伤害、低射速、精准/穿透与瞄准状态；提供远距比较</x:v>
+      </x:c>
+      <x:c r="S25" s="45" t="str">
+        <x:v>长枪轮廓、瞄准准星、强单发反馈和贯穿线一致，射击时点明确</x:v>
+      </x:c>
+      <x:c r="T25" s="47" t="str">
+        <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:N1"/>
-    <x:mergeCell ref="A2:N2"/>
-    <x:mergeCell ref="A3:N3"/>
+    <x:mergeCell ref="A1:T1"/>
+    <x:mergeCell ref="A2:T2"/>
+    <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="K5:K25">
       <x:formula1>"[已实装],[用户设计],[Codex补充]"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="O19:O25">
+      <x:formula1>0</x:formula1>
+      <x:formula2>99</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1954,6 +2402,12 @@
     <x:col min="13" max="13" width="34" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="36" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="42" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="13" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="38" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="28" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="44" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="44" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -1977,7 +2431,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>28张当前可用预设。稳定ID为本版设计ID；当前代码运行时fate_card_####不可用于存档。背景短文为Codex补充，不改变卡片功能。</x:v>
+        <x:v>28张当前预设：22张WEAPON、2张CHARACTER、4张WORLD。稳定ID、作用域路由、武器永久槽和选择反馈已实装；逐卡专属战斗/角色/世界表现继续QA。</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -2059,6 +2513,24 @@
       <x:c r="O4" s="13" t="str">
         <x:v>备注</x:v>
       </x:c>
+      <x:c r="P4" s="48" t="str">
+        <x:v>作用域</x:v>
+      </x:c>
+      <x:c r="Q4" s="48" t="str">
+        <x:v>槽位/所有者规则</x:v>
+      </x:c>
+      <x:c r="R4" s="48" t="str">
+        <x:v>新设计实现状态</x:v>
+      </x:c>
+      <x:c r="S4" s="48" t="str">
+        <x:v>选择/槽位UI提示</x:v>
+      </x:c>
+      <x:c r="T4" s="48" t="str">
+        <x:v>触发/战斗/世界表现</x:v>
+      </x:c>
+      <x:c r="U4" s="48" t="str">
+        <x:v>表现实现状态</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="17" t="str">
@@ -2096,13 +2568,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M5" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N5" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O5" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0001（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P5" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q5" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R5" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S5" s="45" t="str">
+        <x:v>显示目标装配节点、体积倍率与伴随属性差值；预览将写入下一永久槽</x:v>
+      </x:c>
+      <x:c r="T5" s="45" t="str">
+        <x:v>被放大的枪体/挂件/弹体同步改变轮廓、动作重量和尾迹，命中体积与规则一致</x:v>
+      </x:c>
+      <x:c r="U5" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
@@ -2141,13 +2631,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M6" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N6" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O6" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0002（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P6" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q6" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R6" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S6" s="45" t="str">
+        <x:v>显示射速提升、过热/代价参数与目标枪；HUD预留热量/惩罚提示</x:v>
+      </x:c>
+      <x:c r="T6" s="45" t="str">
+        <x:v>枪管热色、机械循环、枪口节奏和过热反馈同步，不能只让数值变快</x:v>
+      </x:c>
+      <x:c r="U6" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
@@ -2186,13 +2694,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M7" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N7" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O7" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0003（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P7" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q7" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R7" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S7" s="45" t="str">
+        <x:v>显示伤害、穿透/破甲规则和目标枪下一槽</x:v>
+      </x:c>
+      <x:c r="T7" s="45" t="str">
+        <x:v>弹体使用贯穿线；护甲命中出现破盾裂纹与剩余穿透提示</x:v>
+      </x:c>
+      <x:c r="U7" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
@@ -2231,13 +2757,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M8" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N8" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O8" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0004（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P8" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q8" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R8" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S8" s="45" t="str">
+        <x:v>显示目标子弹节点、携枪规则和派生攻击链</x:v>
+      </x:c>
+      <x:c r="T8" s="45" t="str">
+        <x:v>投射物上可见微型枪械或等价轮廓；派生开火有独立枪口焰且来源可追溯</x:v>
+      </x:c>
+      <x:c r="U8" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
@@ -2276,13 +2820,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M9" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N9" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O9" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0005（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P9" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q9" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R9" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S9" s="45" t="str">
+        <x:v>显示目标枪、附加枪节点、射击关系和下一槽位置</x:v>
+      </x:c>
+      <x:c r="T9" s="45" t="str">
+        <x:v>主枪上出现副枪实体/能量轮廓；同步或派生开火用不同声层区分</x:v>
+      </x:c>
+      <x:c r="U9" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
@@ -2323,13 +2885,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M10" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N10" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O10" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0006（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P10" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q10" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R10" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S10" s="45" t="str">
+        <x:v>显示寄生目标、命中触发条件和效果来源</x:v>
+      </x:c>
+      <x:c r="T10" s="45" t="str">
+        <x:v>寄生部位有有机脉冲；命中触发时局部亮起并在目标处播放专属反馈</x:v>
+      </x:c>
+      <x:c r="U10" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
@@ -2370,13 +2950,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M11" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N11" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O11" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0007（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P11" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q11" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R11" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S11" s="45" t="str">
+        <x:v>显示目标子弹、主动转向/追踪参数与失去目标规则</x:v>
+      </x:c>
+      <x:c r="T11" s="45" t="str">
+        <x:v>弹体获得生命化轮廓与转向动作，尾迹表现主动寻敌而非普通追踪</x:v>
+      </x:c>
+      <x:c r="U11" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
@@ -2417,13 +3015,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M12" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N12" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O12" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0008（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P12" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q12" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R12" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S12" s="45" t="str">
+        <x:v>显示落地部署条件、炮塔持续/攻击参数和触发链</x:v>
+      </x:c>
+      <x:c r="T12" s="45" t="str">
+        <x:v>弹体落地变为可辨炮塔，生成、攻击、结束三阶段均有反馈</x:v>
+      </x:c>
+      <x:c r="U12" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
@@ -2464,13 +3080,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M13" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N13" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O13" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0009（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P13" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q13" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R13" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S13" s="45" t="str">
+        <x:v>显示落地后的返航/追踪目标、持续时间和结束规则</x:v>
+      </x:c>
+      <x:c r="T13" s="45" t="str">
+        <x:v>落地时生成返航弧线与目标标记，回收/消失时给出明确收束</x:v>
+      </x:c>
+      <x:c r="U13" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
@@ -2511,13 +3145,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M14" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N14" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O14" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0010（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P14" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q14" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R14" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S14" s="45" t="str">
+        <x:v>显示命中后的返回路径、可再次命中规则和伤害倍率</x:v>
+      </x:c>
+      <x:c r="T14" s="45" t="str">
+        <x:v>命中后尾迹反色并沿清晰弧线返回，回到枪/玩家时有回收音</x:v>
+      </x:c>
+      <x:c r="U14" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
@@ -2558,13 +3210,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M15" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N15" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O15" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0011（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P15" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q15" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R15" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S15" s="45" t="str">
+        <x:v>显示连锁次数、范围、后续伤害比例和目标枪槽位</x:v>
+      </x:c>
+      <x:c r="T15" s="45" t="str">
+        <x:v>敌人间产生按顺序跳转的电弧；每次跳转与实际结算同步</x:v>
+      </x:c>
+      <x:c r="U15" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
@@ -2605,13 +3275,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M16" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N16" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O16" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0012（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P16" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q16" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R16" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S16" s="45" t="str">
+        <x:v>显示弹跳次数、表面规则与剩余次数</x:v>
+      </x:c>
+      <x:c r="T16" s="45" t="str">
+        <x:v>每次反弹有折线闪光、方向变化和剩余计数，不以普通命中VFX混淆</x:v>
+      </x:c>
+      <x:c r="U16" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
@@ -2652,13 +3340,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M17" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N17" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O17" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0013（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P17" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q17" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R17" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S17" s="45" t="str">
+        <x:v>显示复制延迟、第二波数量/伤害和触发来源</x:v>
+      </x:c>
+      <x:c r="T17" s="45" t="str">
+        <x:v>第一波后保留轨迹残影，延迟到点生成第二波并用次级声层区分</x:v>
+      </x:c>
+      <x:c r="U17" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
@@ -2699,13 +3405,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M18" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N18" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O18" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0014（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P18" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q18" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R18" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S18" s="45" t="str">
+        <x:v>显示燃烧持续、每秒伤害、叠层/刷新规则</x:v>
+      </x:c>
+      <x:c r="T18" s="45" t="str">
+        <x:v>弹体火焰尾迹、目标燃烧状态图标和每跳伤害反馈同步</x:v>
+      </x:c>
+      <x:c r="U18" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
@@ -2746,13 +3470,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M19" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N19" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O19" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0015（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P19" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q19" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R19" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S19" s="45" t="str">
+        <x:v>显示冻结/减速强度、持续时间和免疫规则</x:v>
+      </x:c>
+      <x:c r="T19" s="45" t="str">
+        <x:v>冰晶尾迹、目标覆霜与冻结破碎反馈清楚，免疫时显示免疫原因</x:v>
+      </x:c>
+      <x:c r="U19" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
@@ -2793,13 +3535,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M20" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N20" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O20" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0016（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P20" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q20" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R20" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S20" s="45" t="str">
+        <x:v>显示中毒伤害、持续、最大叠层和当前层数</x:v>
+      </x:c>
+      <x:c r="T20" s="45" t="str">
+        <x:v>毒雾尾迹、目标层数图标和持续伤害节奏同步，达到上限有强调</x:v>
+      </x:c>
+      <x:c r="U20" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
@@ -2840,13 +3600,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M21" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N21" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O21" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0017（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P21" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q21" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R21" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S21" s="45" t="str">
+        <x:v>显示失控行为、伤害/射速代价和风险徽记</x:v>
+      </x:c>
+      <x:c r="T21" s="45" t="str">
+        <x:v>枪身警示脉冲、异常后坐/弹道与危险音色对应真实失控规则</x:v>
+      </x:c>
+      <x:c r="U21" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
@@ -2887,13 +3665,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M22" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N22" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O22" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0018（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P22" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q22" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R22" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S22" s="45" t="str">
+        <x:v>显示成长触发、每层倍率、当前/最大层数</x:v>
+      </x:c>
+      <x:c r="T22" s="45" t="str">
+        <x:v>弹体或节点随层数渐进增大；HUD层数与尺寸变化同步，满层明显收束</x:v>
+      </x:c>
+      <x:c r="U22" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
@@ -2934,13 +3730,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M23" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N23" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O23" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0019（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P23" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q23" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R23" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S23" s="45" t="str">
+        <x:v>显示换弹触发、爆炸伤害/半径；换弹按钮旁持续危险标志</x:v>
+      </x:c>
+      <x:c r="T23" s="45" t="str">
+        <x:v>换弹开始显示范围圈与充能，结算时爆炸VFX/音效和伤害时点一致</x:v>
+      </x:c>
+      <x:c r="U23" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
@@ -2981,13 +3795,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M24" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N24" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O24" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0020（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P24" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q24" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R24" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S24" s="45" t="str">
+        <x:v>HUD显示1–7发计数和第7发效果预览；详情写明计数重置规则</x:v>
+      </x:c>
+      <x:c r="T24" s="45" t="str">
+        <x:v>第7发枪身、弹体和枪口焰同时高亮，命中使用专属反馈</x:v>
+      </x:c>
+      <x:c r="U24" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
@@ -3028,13 +3860,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M25" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N25" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O25" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0021（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P25" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q25" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R25" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S25" s="45" t="str">
+        <x:v>显示暴击击杀条件、奖励倍率/层数和当前进度</x:v>
+      </x:c>
+      <x:c r="T25" s="45" t="str">
+        <x:v>暴击击杀出现区别于普通暴击的印记，奖励生效时HUD来源图标亮起</x:v>
+      </x:c>
+      <x:c r="U25" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="54" customHeight="1">
@@ -3073,13 +3923,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M26" s="17" t="str">
-        <x:v>正式3D卡池与效果执行器已接；逐卡表现待QA</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N26" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O26" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0022（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P26" s="46" t="str">
+        <x:v>WEAPON</x:v>
+      </x:c>
+      <x:c r="Q26" s="45" t="str">
+        <x:v>占目标枪械下一个永久命运槽；按序追加、不可拆卸/替换/回退</x:v>
+      </x:c>
+      <x:c r="R26" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S26" s="45" t="str">
+        <x:v>显示目标节点、尺寸倍率和伤害/速度等伴随变化</x:v>
+      </x:c>
+      <x:c r="T26" s="45" t="str">
+        <x:v>目标获得夸张但不遮挡视野的体积变化；碰撞与命中轮廓保持一致</x:v>
+      </x:c>
+      <x:c r="U26" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="54" customHeight="1">
@@ -3118,13 +3986,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M27" s="17" t="str">
-        <x:v>效果执行器存在；正式3D地图触发仍需清除兼容依赖</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N27" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O27" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0023（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P27" s="46" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q27" s="45" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落规则状态</x:v>
+      </x:c>
+      <x:c r="R27" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S27" s="45" t="str">
+        <x:v>标记WORLD、不占武器槽；显示增援阈值、波数和影响房间</x:v>
+      </x:c>
+      <x:c r="T27" s="45" t="str">
+        <x:v>地图/房间出现增援警报、入口方向和敌人波次反馈，枪身不刻印</x:v>
+      </x:c>
+      <x:c r="U27" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="54" customHeight="1">
@@ -3163,13 +4049,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M28" s="17" t="str">
-        <x:v>效果执行器存在；正式3D地图触发仍需清除兼容依赖</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N28" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O28" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0024（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P28" s="46" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q28" s="45" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R28" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S28" s="45" t="str">
+        <x:v>标记CHARACTER、不占武器槽；显示标记数量、触发条件和角色状态</x:v>
+      </x:c>
+      <x:c r="T28" s="45" t="str">
+        <x:v>目标头顶出现可读标记；达成条件时角色HUD进度完成，枪械外观不变</x:v>
+      </x:c>
+      <x:c r="U28" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="54" customHeight="1">
@@ -3208,13 +4112,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M29" s="17" t="str">
-        <x:v>效果执行器存在；正式3D地图触发仍需清除兼容依赖</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N29" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O29" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0025（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P29" s="46" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q29" s="45" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落规则状态</x:v>
+      </x:c>
+      <x:c r="R29" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S29" s="45" t="str">
+        <x:v>标记WORLD、不占武器槽；显示下一宝箱升级次数和消耗条件</x:v>
+      </x:c>
+      <x:c r="T29" s="45" t="str">
+        <x:v>地图/宝箱图标带幸运标记，实际开箱时品质升级动画后再消耗状态</x:v>
+      </x:c>
+      <x:c r="U29" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="54" customHeight="1">
@@ -3253,13 +4175,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M30" s="17" t="str">
-        <x:v>效果执行器存在；正式3D地图触发仍需清除兼容依赖</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N30" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O30" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0026（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P30" s="46" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q30" s="45" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落规则状态</x:v>
+      </x:c>
+      <x:c r="R30" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S30" s="45" t="str">
+        <x:v>标记WORLD、不占武器槽；显示下一次额外掉落的触发对象/次数</x:v>
+      </x:c>
+      <x:c r="T30" s="45" t="str">
+        <x:v>有效击杀或开箱时出现额外掉落光束和来源提示，触发后计数归零</x:v>
+      </x:c>
+      <x:c r="U30" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="54" customHeight="1">
@@ -3298,13 +4238,31 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M31" s="17" t="str">
-        <x:v>效果执行器存在；正式3D地图触发仍需清除兼容依赖</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N31" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O31" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0027（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P31" s="46" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q31" s="45" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落规则状态</x:v>
+      </x:c>
+      <x:c r="R31" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S31" s="45" t="str">
+        <x:v>标记WORLD、不占武器槽；显示全局代价、影响范围和持续时间</x:v>
+      </x:c>
+      <x:c r="T31" s="45" t="str">
+        <x:v>小地图边框、环境异常和受影响单位图标统一使用诅咒语言，枪械不占槽</x:v>
+      </x:c>
+      <x:c r="U31" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="54" customHeight="1">
@@ -3343,27 +4301,48 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M32" s="17" t="str">
-        <x:v>效果执行器存在；正式3D地图触发仍需清除兼容依赖</x:v>
+        <x:v>正式3D效果执行、稳定ID、三作用域与武器命运槽已验收；逐卡专属表现待QA</x:v>
       </x:c>
       <x:c r="N32" s="17" t="str">
-        <x:v>src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd</x:v>
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd</x:v>
       </x:c>
       <x:c r="O32" s="17" t="str">
-        <x:v>当前运行时ID=fate_card_0028（不稳定，必须迁移到左侧稳定ID）</x:v>
+        <x:v>运行时与存档均使用左侧stable_card_id；卡片记录携带效果参数快照</x:v>
+      </x:c>
+      <x:c r="P32" s="46" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q32" s="45" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R32" s="47" t="str">
+        <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
+      </x:c>
+      <x:c r="S32" s="45" t="str">
+        <x:v>标记CHARACTER、不占武器槽；显示低生命阈值、增益、持续和冷却</x:v>
+      </x:c>
+      <x:c r="T32" s="45" t="str">
+        <x:v>低血量时角色HUD与轮廓触发祝福，结束/冷却明确，枪械轨道不改变</x:v>
+      </x:c>
+      <x:c r="U32" s="47" t="str">
+        <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:O1"/>
-    <x:mergeCell ref="A2:O2"/>
-    <x:mergeCell ref="A3:O3"/>
+    <x:mergeCell ref="A1:U1"/>
+    <x:mergeCell ref="A2:U2"/>
+    <x:mergeCell ref="A3:U3"/>
   </x:mergeCells>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="H5:H32">
       <x:formula1>"[已实装],[用户设计],[Codex补充]"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="L5:L32">
       <x:formula1>"[已实装],[用户设计],[Codex补充]"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="P5:P32">
+      <x:formula1>"WEAPON,CHARACTER,WORLD"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5808,13 +6787,13 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M30" s="17" t="str">
-        <x:v>已注册；具体掉落概率按同池权重计算</x:v>
+        <x:v>基础成品已注册；独立WeaponInstance与随枪构筑未实装</x:v>
       </x:c>
       <x:c r="N30" s="17" t="str">
         <x:v>src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="O30" s="17" t="str">
-        <x:v>tags=weapon、gun_body、charge</x:v>
+        <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="54" customHeight="1">
@@ -5851,13 +6830,13 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M31" s="17" t="str">
-        <x:v>已注册；具体掉落概率按同池权重计算</x:v>
+        <x:v>基础成品已注册；独立WeaponInstance与随枪构筑未实装</x:v>
       </x:c>
       <x:c r="N31" s="17" t="str">
         <x:v>src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="O31" s="17" t="str">
-        <x:v>tags=weapon、gun_body、launcher</x:v>
+        <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="54" customHeight="1">
@@ -5894,13 +6873,13 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M32" s="17" t="str">
-        <x:v>已注册；具体掉落概率按同池权重计算</x:v>
+        <x:v>基础成品已注册；独立WeaponInstance与随枪构筑未实装</x:v>
       </x:c>
       <x:c r="N32" s="17" t="str">
         <x:v>src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="O32" s="17" t="str">
-        <x:v>tags=weapon、gun_body、auto</x:v>
+        <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="54" customHeight="1">
@@ -5937,13 +6916,13 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M33" s="17" t="str">
-        <x:v>已注册；具体掉落概率按同池权重计算</x:v>
+        <x:v>基础成品已注册；独立WeaponInstance与随枪构筑未实装</x:v>
       </x:c>
       <x:c r="N33" s="17" t="str">
         <x:v>src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="O33" s="17" t="str">
-        <x:v>tags=weapon、gun_body、pistol</x:v>
+        <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="54" customHeight="1">
@@ -5980,13 +6959,13 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M34" s="17" t="str">
-        <x:v>已注册；具体掉落概率按同池权重计算</x:v>
+        <x:v>基础成品已注册；独立WeaponInstance与随枪构筑未实装</x:v>
       </x:c>
       <x:c r="N34" s="17" t="str">
         <x:v>src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="O34" s="17" t="str">
-        <x:v>tags=weapon、gun_body、rifle</x:v>
+        <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="54" customHeight="1">
@@ -6023,13 +7002,13 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M35" s="17" t="str">
-        <x:v>已注册；具体掉落概率按同池权重计算</x:v>
+        <x:v>基础成品已注册；独立WeaponInstance与随枪构筑未实装</x:v>
       </x:c>
       <x:c r="N35" s="17" t="str">
         <x:v>src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="O35" s="17" t="str">
-        <x:v>tags=weapon、gun_body、shotgun</x:v>
+        <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="54" customHeight="1">
@@ -6066,13 +7045,13 @@
         <x:v>[已实装]</x:v>
       </x:c>
       <x:c r="M36" s="17" t="str">
-        <x:v>已注册；具体掉落概率按同池权重计算</x:v>
+        <x:v>基础成品已注册；独立WeaponInstance与随枪构筑未实装</x:v>
       </x:c>
       <x:c r="N36" s="17" t="str">
         <x:v>src/base/ItemRegistry.gd</x:v>
       </x:c>
       <x:c r="O36" s="17" t="str">
-        <x:v>tags=weapon、gun_body、sniper</x:v>
+        <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="54" customHeight="1">
@@ -6681,6 +7660,422 @@
         <x:v>[Codex补充]</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="44" customHeight="1">
+      <x:c r="A23" s="45" t="str">
+        <x:v>武器实例</x:v>
+      </x:c>
+      <x:c r="B23" s="45" t="str">
+        <x:v>weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="C23" s="45" t="str">
+        <x:v>永久绑定一把具体枪械的唯一物品主键</x:v>
+      </x:c>
+      <x:c r="D23" s="45" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E23" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F23" s="45" t="str">
+        <x:v>战斗/存档</x:v>
+      </x:c>
+      <x:c r="G23" s="45" t="str">
+        <x:v>全局唯一；跨装备、背包、地面、交易、保险与存档不变</x:v>
+      </x:c>
+      <x:c r="H23" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="44" customHeight="1">
+      <x:c r="A24" s="45" t="str">
+        <x:v>武器实例</x:v>
+      </x:c>
+      <x:c r="B24" s="45" t="str">
+        <x:v>weapon_content_id</x:v>
+      </x:c>
+      <x:c r="C24" s="45" t="str">
+        <x:v>该实例引用的枪型内容定义ID</x:v>
+      </x:c>
+      <x:c r="D24" s="45" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E24" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F24" s="45" t="str">
+        <x:v>内容/战斗</x:v>
+      </x:c>
+      <x:c r="G24" s="45" t="str">
+        <x:v>必须引用武器成品定义；不能代替实例ID</x:v>
+      </x:c>
+      <x:c r="H24" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="44" customHeight="1">
+      <x:c r="A25" s="45" t="str">
+        <x:v>武器实例</x:v>
+      </x:c>
+      <x:c r="B25" s="45" t="str">
+        <x:v>fate_slot_capacity</x:v>
+      </x:c>
+      <x:c r="C25" s="45" t="str">
+        <x:v>该枪可容纳的永久命运升级数量</x:v>
+      </x:c>
+      <x:c r="D25" s="45" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="E25" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F25" s="45" t="str">
+        <x:v>战斗</x:v>
+      </x:c>
+      <x:c r="G25" s="45" t="str">
+        <x:v>普通枪基础8；类型/稀有度可数据覆盖；0–99</x:v>
+      </x:c>
+      <x:c r="H25" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="44" customHeight="1">
+      <x:c r="A26" s="45" t="str">
+        <x:v>武器实例</x:v>
+      </x:c>
+      <x:c r="B26" s="45" t="str">
+        <x:v>fate_upgrades[]</x:v>
+      </x:c>
+      <x:c r="C26" s="45" t="str">
+        <x:v>按应用顺序保存的不可逆武器命运升级记录</x:v>
+      </x:c>
+      <x:c r="D26" s="45" t="str">
+        <x:v>array</x:v>
+      </x:c>
+      <x:c r="E26" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F26" s="45" t="str">
+        <x:v>战斗/存档</x:v>
+      </x:c>
+      <x:c r="G26" s="45" t="str">
+        <x:v>slot_index从1连续；不可删除、替换、排序或跨枪转移</x:v>
+      </x:c>
+      <x:c r="H26" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="44" customHeight="1">
+      <x:c r="A27" s="45" t="str">
+        <x:v>武器实例</x:v>
+      </x:c>
+      <x:c r="B27" s="45" t="str">
+        <x:v>attachment_slots{}</x:v>
+      </x:c>
+      <x:c r="C27" s="45" t="str">
+        <x:v>可拆卸配件与子弹模块槽位快照</x:v>
+      </x:c>
+      <x:c r="D27" s="45" t="str">
+        <x:v>dict</x:v>
+      </x:c>
+      <x:c r="E27" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F27" s="45" t="str">
+        <x:v>战斗/背包</x:v>
+      </x:c>
+      <x:c r="G27" s="45" t="str">
+        <x:v>不占命运槽；卸装与交换必须事务化</x:v>
+      </x:c>
+      <x:c r="H27" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="44" customHeight="1">
+      <x:c r="A28" s="45" t="str">
+        <x:v>命运卡</x:v>
+      </x:c>
+      <x:c r="B28" s="45" t="str">
+        <x:v>作用域</x:v>
+      </x:c>
+      <x:c r="C28" s="45" t="str">
+        <x:v>卡片规则所有者：WEAPON/CHARACTER/WORLD</x:v>
+      </x:c>
+      <x:c r="D28" s="45" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="E28" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F28" s="45" t="str">
+        <x:v>战斗/角色/关卡</x:v>
+      </x:c>
+      <x:c r="G28" s="45" t="str">
+        <x:v>三选一；WEAPON写枪械实例，另两类不占武器槽</x:v>
+      </x:c>
+      <x:c r="H28" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="44" customHeight="1">
+      <x:c r="A29" s="45" t="str">
+        <x:v>命运卡</x:v>
+      </x:c>
+      <x:c r="B29" s="45" t="str">
+        <x:v>武器槽规则</x:v>
+      </x:c>
+      <x:c r="C29" s="45" t="str">
+        <x:v>说明是否占槽及失败时的消耗/回滚策略</x:v>
+      </x:c>
+      <x:c r="D29" s="45" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E29" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F29" s="45" t="str">
+        <x:v>战斗</x:v>
+      </x:c>
+      <x:c r="G29" s="45" t="str">
+        <x:v>WEAPON占下一个永久槽；满槽失败不消耗；其他作用域不占槽</x:v>
+      </x:c>
+      <x:c r="H29" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="44" customHeight="1">
+      <x:c r="A30" s="45" t="str">
+        <x:v>武器/命运卡</x:v>
+      </x:c>
+      <x:c r="B30" s="45" t="str">
+        <x:v>ui_summary</x:v>
+      </x:c>
+      <x:c r="C30" s="45" t="str">
+        <x:v>列表、卡面与武器表现页的一句话可执行规则</x:v>
+      </x:c>
+      <x:c r="D30" s="45" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E30" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F30" s="45" t="str">
+        <x:v>UI/内容</x:v>
+      </x:c>
+      <x:c r="G30" s="45" t="str">
+        <x:v>必须与作用域、目标与实际效果一致</x:v>
+      </x:c>
+      <x:c r="H30" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="44" customHeight="1">
+      <x:c r="A31" s="45" t="str">
+        <x:v>武器/命运卡</x:v>
+      </x:c>
+      <x:c r="B31" s="45" t="str">
+        <x:v>ui_target_preview</x:v>
+      </x:c>
+      <x:c r="C31" s="45" t="str">
+        <x:v>应用前的目标、槽位、数值与行为差值</x:v>
+      </x:c>
+      <x:c r="D31" s="45" t="str">
+        <x:v>string/dict</x:v>
+      </x:c>
+      <x:c r="E31" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F31" s="45" t="str">
+        <x:v>UI/战斗</x:v>
+      </x:c>
+      <x:c r="G31" s="45" t="str">
+        <x:v>WEAPON必须含实例ID尾号与下一槽；其他作用域含所有者</x:v>
+      </x:c>
+      <x:c r="H31" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="44" customHeight="1">
+      <x:c r="A32" s="45" t="str">
+        <x:v>武器/命运卡</x:v>
+      </x:c>
+      <x:c r="B32" s="45" t="str">
+        <x:v>ui_success_feedback</x:v>
+      </x:c>
+      <x:c r="C32" s="45" t="str">
+        <x:v>事务成功后的槽位、字段高亮与短提示</x:v>
+      </x:c>
+      <x:c r="D32" s="45" t="str">
+        <x:v>string/dict</x:v>
+      </x:c>
+      <x:c r="E32" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F32" s="45" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="G32" s="45" t="str">
+        <x:v>只能在领域事务提交后播放</x:v>
+      </x:c>
+      <x:c r="H32" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="44" customHeight="1">
+      <x:c r="A33" s="45" t="str">
+        <x:v>武器/命运卡</x:v>
+      </x:c>
+      <x:c r="B33" s="45" t="str">
+        <x:v>ui_failure_feedback</x:v>
+      </x:c>
+      <x:c r="C33" s="45" t="str">
+        <x:v>按失败原因返回的可修正文案</x:v>
+      </x:c>
+      <x:c r="D33" s="45" t="str">
+        <x:v>dict</x:v>
+      </x:c>
+      <x:c r="E33" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F33" s="45" t="str">
+        <x:v>UI/领域</x:v>
+      </x:c>
+      <x:c r="G33" s="45" t="str">
+        <x:v>满槽、不兼容、目标丢失、背包满、冲突不可共用通用失败</x:v>
+      </x:c>
+      <x:c r="H33" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="44" customHeight="1">
+      <x:c r="A34" s="45" t="str">
+        <x:v>武器/命运卡</x:v>
+      </x:c>
+      <x:c r="B34" s="45" t="str">
+        <x:v>weapon_visual_tags[]</x:v>
+      </x:c>
+      <x:c r="C34" s="45" t="str">
+        <x:v>枪身、挂件、刻痕、能量线路和动作表现标签</x:v>
+      </x:c>
+      <x:c r="D34" s="45" t="str">
+        <x:v>array</x:v>
+      </x:c>
+      <x:c r="E34" s="45" t="str">
+        <x:v>按需</x:v>
+      </x:c>
+      <x:c r="F34" s="45" t="str">
+        <x:v>美术/战斗</x:v>
+      </x:c>
+      <x:c r="G34" s="45" t="str">
+        <x:v>永久命运与可拆配件使用不同视觉语言</x:v>
+      </x:c>
+      <x:c r="H34" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="44" customHeight="1">
+      <x:c r="A35" s="45" t="str">
+        <x:v>武器/命运卡</x:v>
+      </x:c>
+      <x:c r="B35" s="45" t="str">
+        <x:v>projectile_visual_tags[]</x:v>
+      </x:c>
+      <x:c r="C35" s="45" t="str">
+        <x:v>弹体、尾迹和飞行轨迹表现标签</x:v>
+      </x:c>
+      <x:c r="D35" s="45" t="str">
+        <x:v>array</x:v>
+      </x:c>
+      <x:c r="E35" s="45" t="str">
+        <x:v>按需</x:v>
+      </x:c>
+      <x:c r="F35" s="45" t="str">
+        <x:v>美术/战斗</x:v>
+      </x:c>
+      <x:c r="G35" s="45" t="str">
+        <x:v>与真实弹道和触发行为一致</x:v>
+      </x:c>
+      <x:c r="H35" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="44" customHeight="1">
+      <x:c r="A36" s="45" t="str">
+        <x:v>武器/命运卡</x:v>
+      </x:c>
+      <x:c r="B36" s="45" t="str">
+        <x:v>impact_visual_tags[]</x:v>
+      </x:c>
+      <x:c r="C36" s="45" t="str">
+        <x:v>命中、爆炸、状态、连锁和世界反馈标签</x:v>
+      </x:c>
+      <x:c r="D36" s="45" t="str">
+        <x:v>array</x:v>
+      </x:c>
+      <x:c r="E36" s="45" t="str">
+        <x:v>按需</x:v>
+      </x:c>
+      <x:c r="F36" s="45" t="str">
+        <x:v>美术/战斗</x:v>
+      </x:c>
+      <x:c r="G36" s="45" t="str">
+        <x:v>结算时点与视觉时点一致</x:v>
+      </x:c>
+      <x:c r="H36" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="44" customHeight="1">
+      <x:c r="A37" s="45" t="str">
+        <x:v>武器/命运卡</x:v>
+      </x:c>
+      <x:c r="B37" s="45" t="str">
+        <x:v>audio_cue_id</x:v>
+      </x:c>
+      <x:c r="C37" s="45" t="str">
+        <x:v>安装、应用、触发或失败音频提示</x:v>
+      </x:c>
+      <x:c r="D37" s="45" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E37" s="45" t="str">
+        <x:v>按需</x:v>
+      </x:c>
+      <x:c r="F37" s="45" t="str">
+        <x:v>音频/UI</x:v>
+      </x:c>
+      <x:c r="G37" s="45" t="str">
+        <x:v>高频触发需限流，不能造成音频刷屏</x:v>
+      </x:c>
+      <x:c r="H37" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="44" customHeight="1">
+      <x:c r="A38" s="45" t="str">
+        <x:v>武器/命运卡</x:v>
+      </x:c>
+      <x:c r="B38" s="45" t="str">
+        <x:v>presentation_status</x:v>
+      </x:c>
+      <x:c r="C38" s="45" t="str">
+        <x:v>逐条UI与可感知表现完成状态</x:v>
+      </x:c>
+      <x:c r="D38" s="45" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="E38" s="45" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F38" s="45" t="str">
+        <x:v>制作管理</x:v>
+      </x:c>
+      <x:c r="G38" s="45" t="str">
+        <x:v>未设计/已设计未实装/已实装待QA/已验收</x:v>
+      </x:c>
+      <x:c r="H38" s="47" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd7404e0a428f4a17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="Ra82668d8132142ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R9370d4144ded4990"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="R65cd50a8a54c4972"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="R2ee49ae408fc4191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R0cd5248b7b1f42de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R8a9e52306752465b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R10d9995288834436"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="Rc3d980954e3743ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R0935ea593cc8495b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="R11886247d3c547e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="Reb384d97692a4056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R8482ba14b0fc40ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R0e5e5e1b4cd54a39"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="16">
+  <x:fonts count="17">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -110,6 +110,11 @@
       <x:color rgb="FF243B53"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1565C0"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
   <x:fills count="8">
     <x:fill>
@@ -183,7 +188,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="55">
+  <x:cellXfs count="58">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -300,6 +305,13 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -610,12 +622,10 @@
         <x:v>命运卡</x:v>
       </x:c>
       <x:c r="B7" s="29" t="n">
-        <x:f>COUNTA('命运卡'!$A$5:$A$204)</x:f>
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C7" s="34" t="n">
-        <x:f>COUNTIF('命运卡'!$L$5:$L$204,"[已实装]")</x:f>
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="35" t="n">
         <x:f>COUNTIF('命运卡'!$L$5:$L$204,"[用户设计]")</x:f>
@@ -629,10 +639,10 @@
         <x:v>系统2/6</x:v>
       </x:c>
       <x:c r="G7" s="29" t="str">
-        <x:v>28张卡片功能、参数和背景</x:v>
+        <x:v>48张卡片功能、参数、天体专名和背景</x:v>
       </x:c>
       <x:c r="H7" s="29" t="str">
-        <x:v>三作用域22/2/4张已运行时路由；作用域/目标/槽位提示已实装</x:v>
+        <x:v>三作用域22/12/14张：★星星/☾月亮/☀太阳；20张新增角色/世界牌已进入正式卡池并通过结算与UI验收</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="46" customHeight="1">
@@ -2431,7 +2441,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>28张当前预设：22张WEAPON、2张CHARACTER、4张WORLD。稳定ID、作用域路由、武器永久槽和选择反馈已实装；逐卡专属战斗/角色/世界表现继续QA。</x:v>
+        <x:v>48张正式预设：22张★星星命运、12张☾月亮命运、14张☀太阳命运。稳定ID、作用域所有者、武器永久槽、20张新增牌实际结算、卡面专名和常驻观察UI已验收；逐卡专属VFX/音频继续QA。</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -2586,7 +2596,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S5" s="45" t="str">
-        <x:v>显示目标装配节点、体积倍率与伴随属性差值；预览将写入下一永久槽</x:v>
+        <x:v>★ 星星命运｜显示目标装配节点、体积倍率与伴随属性差值；预览将写入下一永久槽</x:v>
       </x:c>
       <x:c r="T5" s="45" t="str">
         <x:v>被放大的枪体/挂件/弹体同步改变轮廓、动作重量和尾迹，命中体积与规则一致</x:v>
@@ -2649,7 +2659,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S6" s="45" t="str">
-        <x:v>显示射速提升、过热/代价参数与目标枪；HUD预留热量/惩罚提示</x:v>
+        <x:v>★ 星星命运｜显示射速提升、过热/代价参数与目标枪；HUD预留热量/惩罚提示</x:v>
       </x:c>
       <x:c r="T6" s="45" t="str">
         <x:v>枪管热色、机械循环、枪口节奏和过热反馈同步，不能只让数值变快</x:v>
@@ -2712,7 +2722,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S7" s="45" t="str">
-        <x:v>显示伤害、穿透/破甲规则和目标枪下一槽</x:v>
+        <x:v>★ 星星命运｜显示伤害、穿透/破甲规则和目标枪下一槽</x:v>
       </x:c>
       <x:c r="T7" s="45" t="str">
         <x:v>弹体使用贯穿线；护甲命中出现破盾裂纹与剩余穿透提示</x:v>
@@ -2775,7 +2785,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S8" s="45" t="str">
-        <x:v>显示目标子弹节点、携枪规则和派生攻击链</x:v>
+        <x:v>★ 星星命运｜显示目标子弹节点、携枪规则和派生攻击链</x:v>
       </x:c>
       <x:c r="T8" s="45" t="str">
         <x:v>投射物上可见微型枪械或等价轮廓；派生开火有独立枪口焰且来源可追溯</x:v>
@@ -2838,7 +2848,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S9" s="45" t="str">
-        <x:v>显示目标枪、附加枪节点、射击关系和下一槽位置</x:v>
+        <x:v>★ 星星命运｜显示目标枪、附加枪节点、射击关系和下一槽位置</x:v>
       </x:c>
       <x:c r="T9" s="45" t="str">
         <x:v>主枪上出现副枪实体/能量轮廓；同步或派生开火用不同声层区分</x:v>
@@ -2903,7 +2913,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S10" s="45" t="str">
-        <x:v>显示寄生目标、命中触发条件和效果来源</x:v>
+        <x:v>★ 星星命运｜显示寄生目标、命中触发条件和效果来源</x:v>
       </x:c>
       <x:c r="T10" s="45" t="str">
         <x:v>寄生部位有有机脉冲；命中触发时局部亮起并在目标处播放专属反馈</x:v>
@@ -2968,7 +2978,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S11" s="45" t="str">
-        <x:v>显示目标子弹、主动转向/追踪参数与失去目标规则</x:v>
+        <x:v>★ 星星命运｜显示目标子弹、主动转向/追踪参数与失去目标规则</x:v>
       </x:c>
       <x:c r="T11" s="45" t="str">
         <x:v>弹体获得生命化轮廓与转向动作，尾迹表现主动寻敌而非普通追踪</x:v>
@@ -3033,7 +3043,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S12" s="45" t="str">
-        <x:v>显示落地部署条件、炮塔持续/攻击参数和触发链</x:v>
+        <x:v>★ 星星命运｜显示落地部署条件、炮塔持续/攻击参数和触发链</x:v>
       </x:c>
       <x:c r="T12" s="45" t="str">
         <x:v>弹体落地变为可辨炮塔，生成、攻击、结束三阶段均有反馈</x:v>
@@ -3098,7 +3108,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S13" s="45" t="str">
-        <x:v>显示落地后的返航/追踪目标、持续时间和结束规则</x:v>
+        <x:v>★ 星星命运｜显示落地后的返航/追踪目标、持续时间和结束规则</x:v>
       </x:c>
       <x:c r="T13" s="45" t="str">
         <x:v>落地时生成返航弧线与目标标记，回收/消失时给出明确收束</x:v>
@@ -3163,7 +3173,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S14" s="45" t="str">
-        <x:v>显示命中后的返回路径、可再次命中规则和伤害倍率</x:v>
+        <x:v>★ 星星命运｜显示命中后的返回路径、可再次命中规则和伤害倍率</x:v>
       </x:c>
       <x:c r="T14" s="45" t="str">
         <x:v>命中后尾迹反色并沿清晰弧线返回，回到枪/玩家时有回收音</x:v>
@@ -3228,7 +3238,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S15" s="45" t="str">
-        <x:v>显示连锁次数、范围、后续伤害比例和目标枪槽位</x:v>
+        <x:v>★ 星星命运｜显示连锁次数、范围、后续伤害比例和目标枪槽位</x:v>
       </x:c>
       <x:c r="T15" s="45" t="str">
         <x:v>敌人间产生按顺序跳转的电弧；每次跳转与实际结算同步</x:v>
@@ -3293,7 +3303,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S16" s="45" t="str">
-        <x:v>显示弹跳次数、表面规则与剩余次数</x:v>
+        <x:v>★ 星星命运｜显示弹跳次数、表面规则与剩余次数</x:v>
       </x:c>
       <x:c r="T16" s="45" t="str">
         <x:v>每次反弹有折线闪光、方向变化和剩余计数，不以普通命中VFX混淆</x:v>
@@ -3358,7 +3368,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S17" s="45" t="str">
-        <x:v>显示复制延迟、第二波数量/伤害和触发来源</x:v>
+        <x:v>★ 星星命运｜显示复制延迟、第二波数量/伤害和触发来源</x:v>
       </x:c>
       <x:c r="T17" s="45" t="str">
         <x:v>第一波后保留轨迹残影，延迟到点生成第二波并用次级声层区分</x:v>
@@ -3423,7 +3433,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S18" s="45" t="str">
-        <x:v>显示燃烧持续、每秒伤害、叠层/刷新规则</x:v>
+        <x:v>★ 星星命运｜显示燃烧持续、每秒伤害、叠层/刷新规则</x:v>
       </x:c>
       <x:c r="T18" s="45" t="str">
         <x:v>弹体火焰尾迹、目标燃烧状态图标和每跳伤害反馈同步</x:v>
@@ -3488,7 +3498,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S19" s="45" t="str">
-        <x:v>显示冻结/减速强度、持续时间和免疫规则</x:v>
+        <x:v>★ 星星命运｜显示冻结/减速强度、持续时间和免疫规则</x:v>
       </x:c>
       <x:c r="T19" s="45" t="str">
         <x:v>冰晶尾迹、目标覆霜与冻结破碎反馈清楚，免疫时显示免疫原因</x:v>
@@ -3553,7 +3563,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S20" s="45" t="str">
-        <x:v>显示中毒伤害、持续、最大叠层和当前层数</x:v>
+        <x:v>★ 星星命运｜显示中毒伤害、持续、最大叠层和当前层数</x:v>
       </x:c>
       <x:c r="T20" s="45" t="str">
         <x:v>毒雾尾迹、目标层数图标和持续伤害节奏同步，达到上限有强调</x:v>
@@ -3618,7 +3628,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S21" s="45" t="str">
-        <x:v>显示失控行为、伤害/射速代价和风险徽记</x:v>
+        <x:v>★ 星星命运｜显示失控行为、伤害/射速代价和风险徽记</x:v>
       </x:c>
       <x:c r="T21" s="45" t="str">
         <x:v>枪身警示脉冲、异常后坐/弹道与危险音色对应真实失控规则</x:v>
@@ -3683,7 +3693,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S22" s="45" t="str">
-        <x:v>显示成长触发、每层倍率、当前/最大层数</x:v>
+        <x:v>★ 星星命运｜显示成长触发、每层倍率、当前/最大层数</x:v>
       </x:c>
       <x:c r="T22" s="45" t="str">
         <x:v>弹体或节点随层数渐进增大；HUD层数与尺寸变化同步，满层明显收束</x:v>
@@ -3748,7 +3758,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S23" s="45" t="str">
-        <x:v>显示换弹触发、爆炸伤害/半径；换弹按钮旁持续危险标志</x:v>
+        <x:v>★ 星星命运｜显示换弹触发、爆炸伤害/半径；换弹按钮旁持续危险标志</x:v>
       </x:c>
       <x:c r="T23" s="45" t="str">
         <x:v>换弹开始显示范围圈与充能，结算时爆炸VFX/音效和伤害时点一致</x:v>
@@ -3813,7 +3823,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S24" s="45" t="str">
-        <x:v>HUD显示1–7发计数和第7发效果预览；详情写明计数重置规则</x:v>
+        <x:v>★ 星星命运｜HUD显示1–7发计数和第7发效果预览；详情写明计数重置规则</x:v>
       </x:c>
       <x:c r="T24" s="45" t="str">
         <x:v>第7发枪身、弹体和枪口焰同时高亮，命中使用专属反馈</x:v>
@@ -3878,7 +3888,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S25" s="45" t="str">
-        <x:v>显示暴击击杀条件、奖励倍率/层数和当前进度</x:v>
+        <x:v>★ 星星命运｜显示暴击击杀条件、奖励倍率/层数和当前进度</x:v>
       </x:c>
       <x:c r="T25" s="45" t="str">
         <x:v>暴击击杀出现区别于普通暴击的印记，奖励生效时HUD来源图标亮起</x:v>
@@ -3941,7 +3951,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S26" s="45" t="str">
-        <x:v>显示目标节点、尺寸倍率和伤害/速度等伴随变化</x:v>
+        <x:v>★ 星星命运｜显示目标节点、尺寸倍率和伤害/速度等伴随变化</x:v>
       </x:c>
       <x:c r="T26" s="45" t="str">
         <x:v>目标获得夸张但不遮挡视野的体积变化；碰撞与命中轮廓保持一致</x:v>
@@ -4004,7 +4014,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S27" s="45" t="str">
-        <x:v>标记WORLD、不占武器槽；显示增援阈值、波数和影响房间</x:v>
+        <x:v>☀ 太阳命运｜标记WORLD、不占武器槽；显示增援阈值、波数和影响房间</x:v>
       </x:c>
       <x:c r="T27" s="45" t="str">
         <x:v>地图/房间出现增援警报、入口方向和敌人波次反馈，枪身不刻印</x:v>
@@ -4067,7 +4077,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S28" s="45" t="str">
-        <x:v>标记CHARACTER、不占武器槽；显示标记数量、触发条件和角色状态</x:v>
+        <x:v>☾ 月亮命运｜标记CHARACTER、不占武器槽；显示标记数量、触发条件和角色状态</x:v>
       </x:c>
       <x:c r="T28" s="45" t="str">
         <x:v>目标头顶出现可读标记；达成条件时角色HUD进度完成，枪械外观不变</x:v>
@@ -4130,7 +4140,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S29" s="45" t="str">
-        <x:v>标记WORLD、不占武器槽；显示下一宝箱升级次数和消耗条件</x:v>
+        <x:v>☀ 太阳命运｜标记WORLD、不占武器槽；显示下一宝箱升级次数和消耗条件</x:v>
       </x:c>
       <x:c r="T29" s="45" t="str">
         <x:v>地图/宝箱图标带幸运标记，实际开箱时品质升级动画后再消耗状态</x:v>
@@ -4193,7 +4203,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S30" s="45" t="str">
-        <x:v>标记WORLD、不占武器槽；显示下一次额外掉落的触发对象/次数</x:v>
+        <x:v>☀ 太阳命运｜标记WORLD、不占武器槽；显示下一次额外掉落的触发对象/次数</x:v>
       </x:c>
       <x:c r="T30" s="45" t="str">
         <x:v>有效击杀或开箱时出现额外掉落光束和来源提示，触发后计数归零</x:v>
@@ -4256,7 +4266,7 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S31" s="45" t="str">
-        <x:v>标记WORLD、不占武器槽；显示全局代价、影响范围和持续时间</x:v>
+        <x:v>☀ 太阳命运｜标记WORLD、不占武器槽；显示全局代价、影响范围和持续时间</x:v>
       </x:c>
       <x:c r="T31" s="45" t="str">
         <x:v>小地图边框、环境异常和受影响单位图标统一使用诅咒语言，枪械不占槽</x:v>
@@ -4319,13 +4329,1273 @@
         <x:v>[已实装] 显式作用域与所有者分离；WEAPON线性占槽，CHARACTER/WORLD不占槽</x:v>
       </x:c>
       <x:c r="S32" s="45" t="str">
-        <x:v>标记CHARACTER、不占武器槽；显示低生命阈值、增益、持续和冷却</x:v>
+        <x:v>☾ 月亮命运｜标记CHARACTER、不占武器槽；显示低生命阈值、增益、持续和冷却</x:v>
       </x:c>
       <x:c r="T32" s="45" t="str">
         <x:v>低血量时角色HUD与轮廓触发祝福，结束/冷却明确，枪械轨道不改变</x:v>
       </x:c>
       <x:c r="U32" s="47" t="str">
         <x:v>[部分完成] 作用域、目标、下一槽、永久警告与失败原因已实装；逐卡专属VFX/音频仍待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="56" t="str">
+        <x:v>fate_moon_vitality</x:v>
+      </x:c>
+      <x:c r="B33" s="56" t="str">
+        <x:v>月相增生</x:v>
+      </x:c>
+      <x:c r="C33" s="56" t="str">
+        <x:v>强化</x:v>
+      </x:c>
+      <x:c r="D33" s="56" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="E33" s="56" t="str">
+        <x:v>生命上限+20</x:v>
+      </x:c>
+      <x:c r="F33" s="56" t="str">
+        <x:v>最大生命提升20，并立刻恢复20生命</x:v>
+      </x:c>
+      <x:c r="G33" s="56" t="str">
+        <x:v>月光让受损躯体重新生长，把本局的生存空间向上推高。</x:v>
+      </x:c>
+      <x:c r="H33" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I33" s="56"/>
+      <x:c r="J33" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=max_hp；amount=20</x:v>
+      </x:c>
+      <x:c r="K33" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L33" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M33" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N33" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O33" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P33" s="56" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q33" s="56" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R33" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S33" s="56" t="str">
+        <x:v>☾ 月亮命运｜卡面显示☾月亮命运、角色本局、不占武器槽；常驻栏显示生命来源</x:v>
+      </x:c>
+      <x:c r="T33" s="56" t="str">
+        <x:v>角色生命上限与当前生命同步增加，红色生命条立即扩容</x:v>
+      </x:c>
+      <x:c r="U33" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="56" t="str">
+        <x:v>fate_moon_stride</x:v>
+      </x:c>
+      <x:c r="B34" s="56" t="str">
+        <x:v>月影疾行</x:v>
+      </x:c>
+      <x:c r="C34" s="56" t="str">
+        <x:v>强化</x:v>
+      </x:c>
+      <x:c r="D34" s="56" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="E34" s="56" t="str">
+        <x:v>移速+12%</x:v>
+      </x:c>
+      <x:c r="F34" s="56" t="str">
+        <x:v>本局角色移动速度提升12%</x:v>
+      </x:c>
+      <x:c r="G34" s="56" t="str">
+        <x:v>月影贴着脚步移动，让角色更快穿过火力空隙。</x:v>
+      </x:c>
+      <x:c r="H34" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I34" s="56"/>
+      <x:c r="J34" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=move_speed；multiplier=1.12</x:v>
+      </x:c>
+      <x:c r="K34" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L34" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M34" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N34" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O34" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P34" s="56" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q34" s="56" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R34" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S34" s="56" t="str">
+        <x:v>☾ 月亮命运｜卡面显示☾月亮命运、移速+12%、不占武器槽</x:v>
+      </x:c>
+      <x:c r="T34" s="56" t="str">
+        <x:v>角色实际移动速度提高，月亮命运常驻栏可追溯</x:v>
+      </x:c>
+      <x:c r="U34" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="56" t="str">
+        <x:v>fate_moon_dash</x:v>
+      </x:c>
+      <x:c r="B35" s="56" t="str">
+        <x:v>新月回转</x:v>
+      </x:c>
+      <x:c r="C35" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D35" s="56" t="str">
+        <x:v>史诗</x:v>
+      </x:c>
+      <x:c r="E35" s="56" t="str">
+        <x:v>冲刺冷却-20%</x:v>
+      </x:c>
+      <x:c r="F35" s="56" t="str">
+        <x:v>本局冲刺冷却时间缩短20%</x:v>
+      </x:c>
+      <x:c r="G35" s="56" t="str">
+        <x:v>新月缩短两次位移之间的空白，让脱险节奏更紧凑。</x:v>
+      </x:c>
+      <x:c r="H35" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I35" s="56"/>
+      <x:c r="J35" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=dash_cooldown；multiplier=0.8</x:v>
+      </x:c>
+      <x:c r="K35" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L35" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M35" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N35" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O35" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P35" s="56" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q35" s="56" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R35" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S35" s="56" t="str">
+        <x:v>☾ 月亮命运｜卡面显示☾月亮命运、冲刺冷却-20%、不占武器槽</x:v>
+      </x:c>
+      <x:c r="T35" s="56" t="str">
+        <x:v>冲刺冷却实际缩短，HUD冷却进度按新时长结算</x:v>
+      </x:c>
+      <x:c r="U35" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="56" t="str">
+        <x:v>fate_moon_guard</x:v>
+      </x:c>
+      <x:c r="B36" s="56" t="str">
+        <x:v>银月护体</x:v>
+      </x:c>
+      <x:c r="C36" s="56" t="str">
+        <x:v>强化</x:v>
+      </x:c>
+      <x:c r="D36" s="56" t="str">
+        <x:v>史诗</x:v>
+      </x:c>
+      <x:c r="E36" s="56" t="str">
+        <x:v>受伤-12%</x:v>
+      </x:c>
+      <x:c r="F36" s="56" t="str">
+        <x:v>本局角色受到的伤害降低12%</x:v>
+      </x:c>
+      <x:c r="G36" s="56" t="str">
+        <x:v>银色月壳在冲击抵达前分走一部分力量。</x:v>
+      </x:c>
+      <x:c r="H36" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I36" s="56"/>
+      <x:c r="J36" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=damage_taken；multiplier=0.88</x:v>
+      </x:c>
+      <x:c r="K36" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L36" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M36" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N36" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O36" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P36" s="56" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q36" s="56" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R36" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S36" s="56" t="str">
+        <x:v>☾ 月亮命运｜卡面显示☾月亮命运、受伤-12%、不占武器槽</x:v>
+      </x:c>
+      <x:c r="T36" s="56" t="str">
+        <x:v>受击结算乘以0.88，角色状态常驻可见</x:v>
+      </x:c>
+      <x:c r="U36" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="56" t="str">
+        <x:v>fate_moon_power</x:v>
+      </x:c>
+      <x:c r="B37" s="56" t="str">
+        <x:v>月刃共鸣</x:v>
+      </x:c>
+      <x:c r="C37" s="56" t="str">
+        <x:v>强化</x:v>
+      </x:c>
+      <x:c r="D37" s="56" t="str">
+        <x:v>史诗</x:v>
+      </x:c>
+      <x:c r="E37" s="56" t="str">
+        <x:v>枪伤+12%</x:v>
+      </x:c>
+      <x:c r="F37" s="56" t="str">
+        <x:v>本局角色造成的枪械伤害提升12%</x:v>
+      </x:c>
+      <x:c r="G37" s="56" t="str">
+        <x:v>月刃不改写枪械本体，却让持有者的每次射击更有力量。</x:v>
+      </x:c>
+      <x:c r="H37" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I37" s="56"/>
+      <x:c r="J37" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=weapon_damage；multiplier=1.12</x:v>
+      </x:c>
+      <x:c r="K37" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L37" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M37" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N37" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O37" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P37" s="56" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q37" s="56" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R37" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S37" s="56" t="str">
+        <x:v>☾ 月亮命运｜卡面明确目标是角色而非当前枪，不写入星星命运槽</x:v>
+      </x:c>
+      <x:c r="T37" s="56" t="str">
+        <x:v>角色伤害乘区生效；换枪后加成仍随角色，不随枪转移</x:v>
+      </x:c>
+      <x:c r="U37" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="56" t="str">
+        <x:v>fate_moon_room_heal</x:v>
+      </x:c>
+      <x:c r="B38" s="56" t="str">
+        <x:v>潮汐疗愈</x:v>
+      </x:c>
+      <x:c r="C38" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D38" s="56" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="E38" s="56" t="str">
+        <x:v>进新房回血6</x:v>
+      </x:c>
+      <x:c r="F38" s="56" t="str">
+        <x:v>首次进入房间时恢复6生命</x:v>
+      </x:c>
+      <x:c r="G38" s="56" t="str">
+        <x:v>每个未踏足房间都会带来一次微弱潮汐，修补角色伤势。</x:v>
+      </x:c>
+      <x:c r="H38" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I38" s="56"/>
+      <x:c r="J38" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=room_heal；amount=6</x:v>
+      </x:c>
+      <x:c r="K38" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L38" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M38" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N38" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O38" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P38" s="56" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q38" s="56" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R38" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S38" s="56" t="str">
+        <x:v>☾ 月亮命运｜卡面显示☾月亮命运与进新房回血6；常驻栏保留触发来源</x:v>
+      </x:c>
+      <x:c r="T38" s="56" t="str">
+        <x:v>首次进房调用角色疗愈，红色生命条即时反馈</x:v>
+      </x:c>
+      <x:c r="U38" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="56" t="str">
+        <x:v>fate_moon_elite_heal</x:v>
+      </x:c>
+      <x:c r="B39" s="56" t="str">
+        <x:v>猎月回响</x:v>
+      </x:c>
+      <x:c r="C39" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D39" s="56" t="str">
+        <x:v>史诗</x:v>
+      </x:c>
+      <x:c r="E39" s="56" t="str">
+        <x:v>杀精英回血20</x:v>
+      </x:c>
+      <x:c r="F39" s="56" t="str">
+        <x:v>击杀精英或首领时恢复20生命</x:v>
+      </x:c>
+      <x:c r="G39" s="56" t="str">
+        <x:v>强敌倒下时留下的回响被月光收回，转成猎人的生命。</x:v>
+      </x:c>
+      <x:c r="H39" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I39" s="56"/>
+      <x:c r="J39" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=elite_heal；amount=20</x:v>
+      </x:c>
+      <x:c r="K39" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L39" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M39" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N39" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O39" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P39" s="56" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q39" s="56" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R39" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S39" s="56" t="str">
+        <x:v>☾ 月亮命运｜卡面显示☾月亮命运、精英/首领条件、不占武器槽</x:v>
+      </x:c>
+      <x:c r="T39" s="56" t="str">
+        <x:v>精英或首领击杀事件触发恢复20生命</x:v>
+      </x:c>
+      <x:c r="U39" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="56" t="str">
+        <x:v>fate_moon_first_hit</x:v>
+      </x:c>
+      <x:c r="B40" s="56" t="str">
+        <x:v>静夜屏障</x:v>
+      </x:c>
+      <x:c r="C40" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D40" s="56" t="str">
+        <x:v>传说</x:v>
+      </x:c>
+      <x:c r="E40" s="56" t="str">
+        <x:v>首次受伤减半</x:v>
+      </x:c>
+      <x:c r="F40" s="56" t="str">
+        <x:v>每个房间第一次受到的伤害降低50%</x:v>
+      </x:c>
+      <x:c r="G40" s="56" t="str">
+        <x:v>静夜只替进入者挡下第一记冲击，随后屏障沉寂。</x:v>
+      </x:c>
+      <x:c r="H40" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I40" s="56"/>
+      <x:c r="J40" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=first_hit_guard；multiplier=0.5</x:v>
+      </x:c>
+      <x:c r="K40" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L40" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M40" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N40" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O40" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P40" s="56" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q40" s="56" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R40" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S40" s="56" t="str">
+        <x:v>☾ 月亮命运｜卡面显示☾月亮命运、每房首次与减半规则</x:v>
+      </x:c>
+      <x:c r="T40" s="56" t="str">
+        <x:v>首次进入房间重置屏障；第一次受伤后立即消耗</x:v>
+      </x:c>
+      <x:c r="U40" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="56" t="str">
+        <x:v>fate_moon_last_stand</x:v>
+      </x:c>
+      <x:c r="B41" s="56" t="str">
+        <x:v>残月不灭</x:v>
+      </x:c>
+      <x:c r="C41" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D41" s="56" t="str">
+        <x:v>传说</x:v>
+      </x:c>
+      <x:c r="E41" s="56" t="str">
+        <x:v>致命伤保留1血</x:v>
+      </x:c>
+      <x:c r="F41" s="56" t="str">
+        <x:v>致命伤改为保留1生命；每张牌提供1次</x:v>
+      </x:c>
+      <x:c r="G41" s="56" t="str">
+        <x:v>残月不会阻止伤害，只在生命归零前留下最后一道弧光。</x:v>
+      </x:c>
+      <x:c r="H41" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I41" s="56"/>
+      <x:c r="J41" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=last_stand；charges=1</x:v>
+      </x:c>
+      <x:c r="K41" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L41" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M41" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N41" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O41" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P41" s="56" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q41" s="56" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R41" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S41" s="56" t="str">
+        <x:v>☾ 月亮命运｜卡面显示☾月亮命运、一次保命次数、不占武器槽</x:v>
+      </x:c>
+      <x:c r="T41" s="56" t="str">
+        <x:v>致命伤结算保留1血并消费1次；剩余次数保存在角色状态</x:v>
+      </x:c>
+      <x:c r="U41" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="56" t="str">
+        <x:v>fate_moon_ammo</x:v>
+      </x:c>
+      <x:c r="B42" s="56" t="str">
+        <x:v>月华装填</x:v>
+      </x:c>
+      <x:c r="C42" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D42" s="56" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="E42" s="56" t="str">
+        <x:v>进新房补弹20%</x:v>
+      </x:c>
+      <x:c r="F42" s="56" t="str">
+        <x:v>首次进入房间时补充弹匣容量的20%</x:v>
+      </x:c>
+      <x:c r="G42" s="56" t="str">
+        <x:v>月华在房门后凝成弹药，只补充当前手中枪械的弹匣。</x:v>
+      </x:c>
+      <x:c r="H42" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I42" s="56"/>
+      <x:c r="J42" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=room_ammo；ratio=0.2</x:v>
+      </x:c>
+      <x:c r="K42" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L42" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M42" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N42" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O42" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P42" s="56" t="str">
+        <x:v>CHARACTER</x:v>
+      </x:c>
+      <x:c r="Q42" s="56" t="str">
+        <x:v>不占武器槽；写入角色局内规则状态</x:v>
+      </x:c>
+      <x:c r="R42" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S42" s="56" t="str">
+        <x:v>☾ 月亮命运｜卡面显示☾月亮命运、进新房补弹20%、不占武器槽</x:v>
+      </x:c>
+      <x:c r="T42" s="56" t="str">
+        <x:v>首次进房按当前弹匣容量补弹，弹药HUD同步更新</x:v>
+      </x:c>
+      <x:c r="U42" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="56" t="str">
+        <x:v>fate_sun_quality</x:v>
+      </x:c>
+      <x:c r="B43" s="56" t="str">
+        <x:v>晨曦宝库</x:v>
+      </x:c>
+      <x:c r="C43" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D43" s="56" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="E43" s="56" t="str">
+        <x:v>下箱品质+1</x:v>
+      </x:c>
+      <x:c r="F43" s="56" t="str">
+        <x:v>下一个开启容器的物品品质提升1级</x:v>
+      </x:c>
+      <x:c r="G43" s="56" t="str">
+        <x:v>晨光先一步照进下个容器，把其中一件物资推向更高层级。</x:v>
+      </x:c>
+      <x:c r="H43" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I43" s="56"/>
+      <x:c r="J43" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=next_chest_quality；tiers=1</x:v>
+      </x:c>
+      <x:c r="K43" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L43" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M43" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N43" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O43" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P43" s="56" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q43" s="56" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落/撤离规则状态</x:v>
+      </x:c>
+      <x:c r="R43" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S43" s="56" t="str">
+        <x:v>☀ 太阳命运｜卡面显示☀太阳命运、世界规则、下箱品质+1、不占武器槽</x:v>
+      </x:c>
+      <x:c r="T43" s="56" t="str">
+        <x:v>世界状态记录下一箱品质；开箱后消费并生成升级物资</x:v>
+      </x:c>
+      <x:c r="U43" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="56" t="str">
+        <x:v>fate_sun_extra_loot</x:v>
+      </x:c>
+      <x:c r="B44" s="56" t="str">
+        <x:v>丰收日</x:v>
+      </x:c>
+      <x:c r="C44" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D44" s="56" t="str">
+        <x:v>史诗</x:v>
+      </x:c>
+      <x:c r="E44" s="56" t="str">
+        <x:v>下箱额外2件</x:v>
+      </x:c>
+      <x:c r="F44" s="56" t="str">
+        <x:v>下一个开启容器额外掉落2件物品</x:v>
+      </x:c>
+      <x:c r="G44" s="56" t="str">
+        <x:v>太阳延长了这一日的收成，让下一个容器吐出更多物资。</x:v>
+      </x:c>
+      <x:c r="H44" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I44" s="56"/>
+      <x:c r="J44" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=next_chest_extra；count=2</x:v>
+      </x:c>
+      <x:c r="K44" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L44" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M44" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N44" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O44" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P44" s="56" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q44" s="56" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落/撤离规则状态</x:v>
+      </x:c>
+      <x:c r="R44" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S44" s="56" t="str">
+        <x:v>☀ 太阳命运｜卡面显示☀太阳命运、下箱额外2件、不占武器槽</x:v>
+      </x:c>
+      <x:c r="T44" s="56" t="str">
+        <x:v>开箱时额外生成2件物品并清空计数</x:v>
+      </x:c>
+      <x:c r="U44" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="56" t="str">
+        <x:v>fate_sun_reinforce</x:v>
+      </x:c>
+      <x:c r="B45" s="56" t="str">
+        <x:v>日冕增援</x:v>
+      </x:c>
+      <x:c r="C45" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D45" s="56" t="str">
+        <x:v>史诗</x:v>
+      </x:c>
+      <x:c r="E45" s="56" t="str">
+        <x:v>下房敌人+3</x:v>
+      </x:c>
+      <x:c r="F45" s="56" t="str">
+        <x:v>下一个敌对房间额外出现3名敌人</x:v>
+      </x:c>
+      <x:c r="G45" s="56" t="str">
+        <x:v>日冕暴露了行动路线，下一间敌对区域会提前集结增援。</x:v>
+      </x:c>
+      <x:c r="H45" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I45" s="56"/>
+      <x:c r="J45" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=next_room_enemy_count；count=3</x:v>
+      </x:c>
+      <x:c r="K45" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L45" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M45" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N45" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O45" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P45" s="56" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q45" s="56" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落/撤离规则状态</x:v>
+      </x:c>
+      <x:c r="R45" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S45" s="56" t="str">
+        <x:v>☀ 太阳命运｜卡面显示☀太阳命运、下个敌对房间+3、不占武器槽</x:v>
+      </x:c>
+      <x:c r="T45" s="56" t="str">
+        <x:v>下一敌对房间生成表追加3名敌人后消费状态</x:v>
+      </x:c>
+      <x:c r="U45" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="56" t="str">
+        <x:v>fate_sun_reveal</x:v>
+      </x:c>
+      <x:c r="B46" s="56" t="str">
+        <x:v>曙光测绘</x:v>
+      </x:c>
+      <x:c r="C46" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D46" s="56" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="E46" s="56" t="str">
+        <x:v>揭示周围2层</x:v>
+      </x:c>
+      <x:c r="F46" s="56" t="str">
+        <x:v>立即揭示当前房间周围2层相邻房间</x:v>
+      </x:c>
+      <x:c r="G46" s="56" t="str">
+        <x:v>曙光沿走廊扩散，把附近两层连接关系投到地图上。</x:v>
+      </x:c>
+      <x:c r="H46" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I46" s="56"/>
+      <x:c r="J46" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=reveal_rooms；radius=2</x:v>
+      </x:c>
+      <x:c r="K46" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L46" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M46" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N46" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O46" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P46" s="56" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q46" s="56" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落/撤离规则状态</x:v>
+      </x:c>
+      <x:c r="R46" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S46" s="56" t="str">
+        <x:v>☀ 太阳命运｜卡面显示☀太阳命运与立即揭示范围</x:v>
+      </x:c>
+      <x:c r="T46" s="56" t="str">
+        <x:v>小地图立即揭示两层邻接房，不生成或修改枪械数据</x:v>
+      </x:c>
+      <x:c r="U46" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="56" t="str">
+        <x:v>fate_sun_key</x:v>
+      </x:c>
+      <x:c r="B47" s="56" t="str">
+        <x:v>太阳钥印</x:v>
+      </x:c>
+      <x:c r="C47" s="56" t="str">
+        <x:v>强化</x:v>
+      </x:c>
+      <x:c r="D47" s="56" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="E47" s="56" t="str">
+        <x:v>获得房间钥匙</x:v>
+      </x:c>
+      <x:c r="F47" s="56" t="str">
+        <x:v>立即获得1把普通房间钥匙</x:v>
+      </x:c>
+      <x:c r="G47" s="56" t="str">
+        <x:v>灼热印记在掌心凝成一把只属于本次行动的房间钥匙。</x:v>
+      </x:c>
+      <x:c r="H47" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I47" s="56"/>
+      <x:c r="J47" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=grant_room_key；count=1</x:v>
+      </x:c>
+      <x:c r="K47" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L47" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M47" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N47" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O47" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P47" s="56" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q47" s="56" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落/撤离规则状态</x:v>
+      </x:c>
+      <x:c r="R47" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S47" s="56" t="str">
+        <x:v>☀ 太阳命运｜卡面显示☀太阳命运、立即获得钥匙、不占武器槽</x:v>
+      </x:c>
+      <x:c r="T47" s="56" t="str">
+        <x:v>普通房间钥匙计数立即+1，HUD同步刷新</x:v>
+      </x:c>
+      <x:c r="U47" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="56" t="str">
+        <x:v>fate_sun_currency</x:v>
+      </x:c>
+      <x:c r="B48" s="56" t="str">
+        <x:v>黄金潮汐</x:v>
+      </x:c>
+      <x:c r="C48" s="56" t="str">
+        <x:v>强化</x:v>
+      </x:c>
+      <x:c r="D48" s="56" t="str">
+        <x:v>史诗</x:v>
+      </x:c>
+      <x:c r="E48" s="56" t="str">
+        <x:v>魂获取+30%</x:v>
+      </x:c>
+      <x:c r="F48" s="56" t="str">
+        <x:v>本局之后获得的魂数量提升30%</x:v>
+      </x:c>
+      <x:c r="G48" s="56" t="str">
+        <x:v>太阳把敌人遗留的魂染成金色，让之后的收获更丰厚。</x:v>
+      </x:c>
+      <x:c r="H48" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I48" s="56"/>
+      <x:c r="J48" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=currency_gain；multiplier=1.3</x:v>
+      </x:c>
+      <x:c r="K48" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L48" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M48" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N48" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O48" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P48" s="56" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q48" s="56" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落/撤离规则状态</x:v>
+      </x:c>
+      <x:c r="R48" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S48" s="56" t="str">
+        <x:v>☀ 太阳命运｜卡面显示☀太阳命运、魂获取+30%、本局持续</x:v>
+      </x:c>
+      <x:c r="T48" s="56" t="str">
+        <x:v>之后敌人魂掉落乘以1.3；太阳命运常驻栏显示来源</x:v>
+      </x:c>
+      <x:c r="U48" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="56" t="str">
+        <x:v>fate_sun_scorch</x:v>
+      </x:c>
+      <x:c r="B49" s="56" t="str">
+        <x:v>天火灼地</x:v>
+      </x:c>
+      <x:c r="C49" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D49" s="56" t="str">
+        <x:v>史诗</x:v>
+      </x:c>
+      <x:c r="E49" s="56" t="str">
+        <x:v>下房敌血-20%</x:v>
+      </x:c>
+      <x:c r="F49" s="56" t="str">
+        <x:v>下一个敌对房间的敌人最大生命降低20%</x:v>
+      </x:c>
+      <x:c r="G49" s="56" t="str">
+        <x:v>天火先扫过下一战区，让尚未现身的敌群带着灼伤入场。</x:v>
+      </x:c>
+      <x:c r="H49" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I49" s="56"/>
+      <x:c r="J49" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=next_room_enemy_hp；multiplier=0.8</x:v>
+      </x:c>
+      <x:c r="K49" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L49" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M49" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N49" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O49" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P49" s="56" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q49" s="56" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落/撤离规则状态</x:v>
+      </x:c>
+      <x:c r="R49" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S49" s="56" t="str">
+        <x:v>☀ 太阳命运｜卡面显示☀太阳命运、下房敌血-20%、一次性世界规则</x:v>
+      </x:c>
+      <x:c r="T49" s="56" t="str">
+        <x:v>下一敌对房所有波次按0.8最大生命生成，随后清除待用状态</x:v>
+      </x:c>
+      <x:c r="U49" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="56" t="str">
+        <x:v>fate_sun_trial</x:v>
+      </x:c>
+      <x:c r="B50" s="56" t="str">
+        <x:v>烈日试炼</x:v>
+      </x:c>
+      <x:c r="C50" s="56" t="str">
+        <x:v>诅咒</x:v>
+      </x:c>
+      <x:c r="D50" s="56" t="str">
+        <x:v>传说</x:v>
+      </x:c>
+      <x:c r="E50" s="56" t="str">
+        <x:v>强敌双倍魂</x:v>
+      </x:c>
+      <x:c r="F50" s="56" t="str">
+        <x:v>下一个敌对房间敌人伤害+25%，其魂掉落×2</x:v>
+      </x:c>
+      <x:c r="G50" s="56" t="str">
+        <x:v>烈日要求用更危险的一战证明资格，并用双倍魂回报胜者。</x:v>
+      </x:c>
+      <x:c r="H50" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I50" s="56"/>
+      <x:c r="J50" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=next_room_trial；damage_multiplier=1.25；currency_multiplier=2</x:v>
+      </x:c>
+      <x:c r="K50" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L50" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M50" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N50" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O50" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P50" s="56" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q50" s="56" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落/撤离规则状态</x:v>
+      </x:c>
+      <x:c r="R50" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S50" s="56" t="str">
+        <x:v>☀ 太阳命运｜卡面同时显示☀太阳命运、伤害代价、双倍魂和影响范围</x:v>
+      </x:c>
+      <x:c r="T50" s="56" t="str">
+        <x:v>下一敌对房敌伤乘1.25、魂乘2；风险与收益同时消费</x:v>
+      </x:c>
+      <x:c r="U50" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="56" t="str">
+        <x:v>fate_sun_bounty</x:v>
+      </x:c>
+      <x:c r="B51" s="56" t="str">
+        <x:v>长昼赏金</x:v>
+      </x:c>
+      <x:c r="C51" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D51" s="56" t="str">
+        <x:v>史诗</x:v>
+      </x:c>
+      <x:c r="E51" s="56" t="str">
+        <x:v>三房各奖35魂</x:v>
+      </x:c>
+      <x:c r="F51" s="56" t="str">
+        <x:v>接下来3个敌对房间肃清时各获得35魂</x:v>
+      </x:c>
+      <x:c r="G51" s="56" t="str">
+        <x:v>长昼把三次肃清写进赏金契约，每完成一间就结算一次。</x:v>
+      </x:c>
+      <x:c r="H51" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I51" s="56"/>
+      <x:c r="J51" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=room_clear_bounty；rooms=3；amount=35</x:v>
+      </x:c>
+      <x:c r="K51" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L51" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M51" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N51" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O51" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P51" s="56" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q51" s="56" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落/撤离规则状态</x:v>
+      </x:c>
+      <x:c r="R51" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S51" s="56" t="str">
+        <x:v>☀ 太阳命运｜卡面显示☀太阳命运、3房次数与每房35魂</x:v>
+      </x:c>
+      <x:c r="T51" s="56" t="str">
+        <x:v>敌对房首次肃清结算35魂并扣除1次，HUD货币同步</x:v>
+      </x:c>
+      <x:c r="U51" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="56" t="str">
+        <x:v>fate_sun_extraction</x:v>
+      </x:c>
+      <x:c r="B52" s="56" t="str">
+        <x:v>日落捷径</x:v>
+      </x:c>
+      <x:c r="C52" s="56" t="str">
+        <x:v>规则</x:v>
+      </x:c>
+      <x:c r="D52" s="56" t="str">
+        <x:v>传说</x:v>
+      </x:c>
+      <x:c r="E52" s="56" t="str">
+        <x:v>撤离时间-20%</x:v>
+      </x:c>
+      <x:c r="F52" s="56" t="str">
+        <x:v>本局所有撤离同步时间缩短20%</x:v>
+      </x:c>
+      <x:c r="G52" s="56" t="str">
+        <x:v>日落前留下的短暂通道压缩了所有撤离信标的同步过程。</x:v>
+      </x:c>
+      <x:c r="H52" s="57" t="str">
+        <x:v>[用户设计]</x:v>
+      </x:c>
+      <x:c r="I52" s="56"/>
+      <x:c r="J52" s="56" t="str">
+        <x:v>action=APPLY_SCOPED_MODIFIER；modifier=extraction_time；multiplier=0.8</x:v>
+      </x:c>
+      <x:c r="K52" s="56" t="str">
+        <x:v>门后命运/三选一/工作台共用正式卡池</x:v>
+      </x:c>
+      <x:c r="L52" s="56" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M52" s="56" t="str">
+        <x:v>正式3D作用域结算、卡池、天体专名与常驻观察UI已通过专项验收</x:v>
+      </x:c>
+      <x:c r="N52" s="56" t="str">
+        <x:v>src/weapons/FateCard.gd；src/weapons/FateCardPresets.gd；src/weapons/FateCardEngine.gd；src/game/FateCardGameBridge.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd</x:v>
+      </x:c>
+      <x:c r="O52" s="56" t="str">
+        <x:v>运行时使用stable_card_id；同名可叠加；不写入WeaponInstance命运槽</x:v>
+      </x:c>
+      <x:c r="P52" s="56" t="str">
+        <x:v>WORLD</x:v>
+      </x:c>
+      <x:c r="Q52" s="56" t="str">
+        <x:v>不占武器槽；写入行动/房间/掉落/撤离规则状态</x:v>
+      </x:c>
+      <x:c r="R52" s="56" t="str">
+        <x:v>[已实装并验收] 作用域所有者独立，可解耦维护</x:v>
+      </x:c>
+      <x:c r="S52" s="56" t="str">
+        <x:v>☀ 太阳命运｜卡面显示☀太阳命运、撤离时间-20%、本局持续</x:v>
+      </x:c>
+      <x:c r="T52" s="56" t="str">
+        <x:v>现有与后续撤离信标时长乘0.8，撤离HUD使用新时长</x:v>
+      </x:c>
+      <x:c r="U52" s="56" t="str">
+        <x:v>[核心已验收] 卡面专名、实际结算和常驻状态已完成；逐卡专属VFX/音频待QA</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R4193e4364a294f9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="R2b03e8e8b6a048b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="Rbc84983a9d584758"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="R31f2c787b89e4958"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="R1c36aec642524a58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R25996088a2e94c6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="Rcd1d3d085e0e45cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R42d5be145abb42a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="R93034406afb040b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="Rfdcb85888a5840e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="Red2c60615a1348f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="Rbd68fc2c56a4460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R5c8ed32f9e254e5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R520904e3fa6049b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1024,19 +1024,15 @@
         <x:v>掉落物品</x:v>
       </x:c>
       <x:c r="B10" s="29" t="n">
-        <x:f>COUNTA('掉落物品'!$A$5:$A$204)</x:f>
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C10" s="34" t="n">
-        <x:f>COUNTIF('掉落物品'!$L$5:$L$204,"[已实装]")</x:f>
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D10" s="35" t="n">
-        <x:f>COUNTIF('掉落物品'!$L$5:$L$204,"[用户设计]")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E10" s="36" t="n">
-        <x:f>COUNTIF('掉落物品'!$L$5:$L$204,"[Codex补充]")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F10" s="29" t="str">
@@ -1046,7 +1042,7 @@
         <x:v>物品、价格、稀有度和掉落池</x:v>
       </x:c>
       <x:c r="H10" s="29" t="str">
-        <x:v>武器成品必须携带实例ID与完整构筑快照</x:v>
+        <x:v>武器成品保留实例构筑；3种背包装备提供2/4/8扩展格并已验收缩容溢出落地</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -11922,7 +11918,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>导入ItemRegistry当前32条记录，并加入用户设计的Boss下行专用钥匙。价格0不自动代表免费；进度物不能进入普通商店和随机消耗。</x:v>
+        <x:v>导入ItemRegistry当前35条正式记录，并加入用户设计的Boss下行专用钥匙，共36条；价格0不自动代表免费，进度物不进入普通商店。</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -13454,6 +13450,147 @@
       </x:c>
       <x:c r="O37" s="17" t="str">
         <x:v>必须记录来源阶段ID；不能与item_room_key互换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>equipment_backpack_2</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>轻型腰包</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>equipment</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>backpack</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>equip_backpack（左键/拖拽）</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>装备后增加2个物品格；卸下或换包时容量不足部分落到当前房间</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>combat_floor_1×0.28；combat_floor_2×0.2；loot_common×0.22；loot_floor_1_2×0.5；scavenge_floor_1×1.2；scavenge_floor_2×0.9</x:v>
+      </x:c>
+      <x:c r="K38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>正式3D已验证：物品/装备槽/动态容量/背部Mesh/溢出落地</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>src/base/ItemRegistry.gd；src/game/InventoryModule.gd；src/world3d/Dungeon3D.gd；src/player3d/Player3D.gd</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>tags=equipment, backpack, capacity；基础12+2；浅层搜索/普通怪偏重</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>equipment_backpack_4</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>战术背包</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>equipment</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>backpack</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>uncommon</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>equip_backpack（左键/拖拽）</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>装备后增加4个物品格；卸下或换包时容量不足部分落到当前房间</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>combat_floor_3×0.22；elite_floor_1×0.85；elite_floor_2×0.55；loot_floor_1_2×0.16；loot_floor_3_4×0.65；scavenge_floor_2×0.35；scavenge_floor_3×1；scavenge_floor_4×0.8</x:v>
+      </x:c>
+      <x:c r="K39" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>正式3D已验证：物品/装备槽/动态容量/背部Mesh/溢出落地</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>src/base/ItemRegistry.gd；src/game/InventoryModule.gd；src/world3d/Dungeon3D.gd；src/player3d/Player3D.gd</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>tags=equipment, backpack, capacity；基础12+4；中层搜索/精英偏重</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>equipment_backpack_8</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>远征背包</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>equipment</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>backpack</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>rare</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>equip_backpack（左键/拖拽）</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>装备后增加8个物品格；卸下或换包时容量不足部分落到当前房间</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>boss_floor_1×1.25；boss_floor_2×1.8；elite_floor_2×0.75；loot_abyss×0.85；loot_floor_5×0.55；scavenge_floor_4×0.25；scavenge_floor_5×0.9</x:v>
+      </x:c>
+      <x:c r="K40" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L40" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>正式3D已验证：物品/装备槽/动态容量/背部Mesh/溢出落地</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>src/base/ItemRegistry.gd；src/game/InventoryModule.gd；src/world3d/Dungeon3D.gd；src/player3d/Player3D.gd</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>tags=equipment, backpack, capacity；基础12+8；深层搜索/精英/Boss偏重</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R42d5be145abb42a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="R93034406afb040b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="Rfdcb85888a5840e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="Red2c60615a1348f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="Rbd68fc2c56a4460d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R5c8ed32f9e254e5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R520904e3fa6049b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8f8fcd40f39848a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="Re20866e40c5e4317"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R7352404713ea4b27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="R19884d60427c443f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="Rba264e0971354172"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R6a862a4277ce4c1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R9cfa40dde04d48cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" r:id="R43cb3bd164774a4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="0%"/>
+    <x:numFmt numFmtId="201" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="19">
+  <x:fonts count="24">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -130,8 +132,37 @@
       <x:color rgb="FF102A43"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFE8F8FA"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF12333A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF155A32"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF31545B"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="14">
+  <x:fills count="18">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -198,8 +229,28 @@
         <x:fgColor rgb="FFFFF8E8"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF113946"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF4F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDF4E4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0C6670"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="12">
+  <x:borders count="15">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -319,11 +370,53 @@
         <x:color rgb="FFDCE6EC"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF406773"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF406773"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF406773"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF406773"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB7D1D4"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB7D1D4"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB7D1D4"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB7D1D4"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF8FC3A1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF8FC3A1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF8FC3A1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF8FC3A1"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="129">
+  <x:cellXfs count="162">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -629,11 +722,148 @@
     <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="20" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="21" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1313,6 +1543,11 @@
     <x:col min="18" max="18" width="42" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="42" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="24" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="14" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="14" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="14" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="14" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -1430,6 +1665,21 @@
       <x:c r="T4" s="48" t="str">
         <x:v>表现实现状态</x:v>
       </x:c>
+      <x:c r="U4" s="134" t="str">
+        <x:v>基地购买价</x:v>
+      </x:c>
+      <x:c r="V4" s="134" t="str">
+        <x:v>基地出售价</x:v>
+      </x:c>
+      <x:c r="W4" s="134" t="str">
+        <x:v>基地商店上架</x:v>
+      </x:c>
+      <x:c r="X4" s="134" t="str">
+        <x:v>基地库存规则</x:v>
+      </x:c>
+      <x:c r="Y4" s="134" t="str">
+        <x:v>基地货架顺序</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="17" t="str">
@@ -1488,6 +1738,23 @@
       <x:c r="T5" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U5" s="152" t="n">
+        <x:f>IF(F5&gt;0,F5,0)</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="V5" s="152" t="n">
+        <x:f>IF(F5&gt;0,ROUND(F5*0.5,0),0)</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="W5" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X5" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y5" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="17" t="str">
@@ -1546,6 +1813,23 @@
       <x:c r="T6" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U6" s="152" t="n">
+        <x:f>IF(F6&gt;0,F6,0)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="V6" s="152" t="n">
+        <x:f>IF(F6&gt;0,ROUND(F6*0.5,0),0)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="W6" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X6" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y6" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="17" t="str">
@@ -1604,6 +1888,23 @@
       <x:c r="T7" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U7" s="152" t="n">
+        <x:f>IF(F7&gt;0,F7,0)</x:f>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="V7" s="152" t="n">
+        <x:f>IF(F7&gt;0,ROUND(F7*0.5,0),0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="W7" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X7" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y7" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="17" t="str">
@@ -1662,6 +1963,23 @@
       <x:c r="T8" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U8" s="152" t="n">
+        <x:f>IF(F8&gt;0,F8,0)</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="V8" s="152" t="n">
+        <x:f>IF(F8&gt;0,ROUND(F8*0.5,0),0)</x:f>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="W8" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X8" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y8" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="17" t="str">
@@ -1720,6 +2038,23 @@
       <x:c r="T9" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U9" s="152" t="n">
+        <x:f>IF(F9&gt;0,F9,0)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="V9" s="152" t="n">
+        <x:f>IF(F9&gt;0,ROUND(F9*0.5,0),0)</x:f>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="W9" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X9" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y9" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="17" t="str">
@@ -1778,6 +2113,23 @@
       <x:c r="T10" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U10" s="152" t="n">
+        <x:f>IF(F10&gt;0,F10,0)</x:f>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="V10" s="152" t="n">
+        <x:f>IF(F10&gt;0,ROUND(F10*0.5,0),0)</x:f>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="W10" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X10" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y10" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="17" t="str">
@@ -1836,6 +2188,23 @@
       <x:c r="T11" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U11" s="152" t="n">
+        <x:f>IF(F11&gt;0,F11,0)</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="V11" s="152" t="n">
+        <x:f>IF(F11&gt;0,ROUND(F11*0.5,0),0)</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="W11" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X11" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y11" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="17" t="str">
@@ -1894,6 +2263,23 @@
       <x:c r="T12" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U12" s="152" t="n">
+        <x:f>IF(F12&gt;0,F12,0)</x:f>
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="V12" s="152" t="n">
+        <x:f>IF(F12&gt;0,ROUND(F12*0.5,0),0)</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="W12" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X12" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y12" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="17" t="str">
@@ -1952,6 +2338,23 @@
       <x:c r="T13" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U13" s="152" t="n">
+        <x:f>IF(F13&gt;0,F13,0)</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="V13" s="152" t="n">
+        <x:f>IF(F13&gt;0,ROUND(F13*0.5,0),0)</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W13" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X13" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y13" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="17" t="str">
@@ -2010,6 +2413,23 @@
       <x:c r="T14" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U14" s="152" t="n">
+        <x:f>IF(F14&gt;0,F14,0)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="V14" s="152" t="n">
+        <x:f>IF(F14&gt;0,ROUND(F14*0.5,0),0)</x:f>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="W14" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X14" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y14" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="17" t="str">
@@ -2068,6 +2488,23 @@
       <x:c r="T15" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U15" s="152" t="n">
+        <x:f>IF(F15&gt;0,F15,0)</x:f>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="V15" s="152" t="n">
+        <x:f>IF(F15&gt;0,ROUND(F15*0.5,0),0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="W15" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X15" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y15" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="17" t="str">
@@ -2126,6 +2563,23 @@
       <x:c r="T16" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U16" s="152" t="n">
+        <x:f>IF(F16&gt;0,F16,0)</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="V16" s="152" t="n">
+        <x:f>IF(F16&gt;0,ROUND(F16*0.5,0),0)</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="W16" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X16" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y16" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="17" t="str">
@@ -2184,6 +2638,23 @@
       <x:c r="T17" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U17" s="152" t="n">
+        <x:f>IF(F17&gt;0,F17,0)</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="V17" s="152" t="n">
+        <x:f>IF(F17&gt;0,ROUND(F17*0.5,0),0)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="W17" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X17" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y17" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="17" t="str">
@@ -2242,6 +2713,23 @@
       <x:c r="T18" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U18" s="152" t="n">
+        <x:f>IF(F18&gt;0,F18,0)</x:f>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="V18" s="152" t="n">
+        <x:f>IF(F18&gt;0,ROUND(F18*0.5,0),0)</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="W18" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X18" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y18" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="17" t="str">
@@ -2305,6 +2793,23 @@
       <x:c r="T19" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U19" s="152" t="n">
+        <x:f>IF(F19&gt;0,F19,0)</x:f>
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="V19" s="152" t="n">
+        <x:f>IF(F19&gt;0,ROUND(F19*0.5,0),0)</x:f>
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="W19" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X19" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y19" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="17" t="str">
@@ -2368,6 +2873,23 @@
       <x:c r="T20" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U20" s="152" t="n">
+        <x:f>IF(F20&gt;0,F20,0)</x:f>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="V20" s="152" t="n">
+        <x:f>IF(F20&gt;0,ROUND(F20*0.5,0),0)</x:f>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="W20" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X20" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y20" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="17" t="str">
@@ -2431,6 +2953,23 @@
       <x:c r="T21" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U21" s="152" t="n">
+        <x:f>IF(F21&gt;0,F21,0)</x:f>
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="V21" s="152" t="n">
+        <x:f>IF(F21&gt;0,ROUND(F21*0.5,0),0)</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="W21" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X21" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y21" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="17" t="str">
@@ -2494,6 +3033,23 @@
       <x:c r="T22" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U22" s="153" t="n">
+        <x:f>IF(F22&gt;0,F22,0)</x:f>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="V22" s="153" t="n">
+        <x:f>IF(F22&gt;0,ROUND(F22*0.5,0),0)</x:f>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="W22" s="151" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X22" s="150" t="str">
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="Y22" s="153" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="17" t="str">
@@ -2557,6 +3113,23 @@
       <x:c r="T23" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U23" s="153" t="n">
+        <x:f>IF(F23&gt;0,F23,0)</x:f>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="V23" s="153" t="n">
+        <x:f>IF(F23&gt;0,ROUND(F23*0.5,0),0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="W23" s="151" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X23" s="150" t="str">
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="Y23" s="153" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="17" t="str">
@@ -2620,6 +3193,23 @@
       <x:c r="T24" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
       </x:c>
+      <x:c r="U24" s="153" t="n">
+        <x:f>IF(F24&gt;0,F24,0)</x:f>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="V24" s="153" t="n">
+        <x:f>IF(F24&gt;0,ROUND(F24*0.5,0),0)</x:f>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="W24" s="151" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X24" s="150" t="str">
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="Y24" s="153" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="17" t="str">
@@ -2682,6 +3272,23 @@
       </x:c>
       <x:c r="T25" s="47" t="str">
         <x:v>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</x:v>
+      </x:c>
+      <x:c r="U25" s="152" t="n">
+        <x:f>IF(F25&gt;0,F25,0)</x:f>
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="V25" s="152" t="n">
+        <x:f>IF(F25&gt;0,ROUND(F25*0.5,0),0)</x:f>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="W25" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X25" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="Y25" s="152" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11895,6 +12502,11 @@
     <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="32" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="40" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="14" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12000,6 +12612,21 @@
       <x:c r="O4" s="13" t="str">
         <x:v>备注</x:v>
       </x:c>
+      <x:c r="P4" s="134" t="str">
+        <x:v>基地购买价</x:v>
+      </x:c>
+      <x:c r="Q4" s="134" t="str">
+        <x:v>基地出售价</x:v>
+      </x:c>
+      <x:c r="R4" s="134" t="str">
+        <x:v>基地商店上架</x:v>
+      </x:c>
+      <x:c r="S4" s="134" t="str">
+        <x:v>基地库存规则</x:v>
+      </x:c>
+      <x:c r="T4" s="134" t="str">
+        <x:v>基地货架顺序</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="17" t="str">
@@ -12043,6 +12670,23 @@
       <x:c r="O5" s="17" t="str">
         <x:v>tags=attachment、magazine、heal</x:v>
       </x:c>
+      <x:c r="P5" s="152" t="n">
+        <x:f>IF(F5&gt;0,F5,0)</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="Q5" s="152" t="n">
+        <x:f>IF(F5&gt;0,ROUND(F5*0.5,0),0)</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="R5" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S5" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T5" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="17" t="str">
@@ -12086,6 +12730,23 @@
       <x:c r="O6" s="17" t="str">
         <x:v>tags=attachment、mutator、copy</x:v>
       </x:c>
+      <x:c r="P6" s="152" t="n">
+        <x:f>IF(F6&gt;0,F6,0)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="Q6" s="152" t="n">
+        <x:f>IF(F6&gt;0,ROUND(F6*0.5,0),0)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="R6" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S6" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T6" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="17" t="str">
@@ -12129,6 +12790,23 @@
       <x:c r="O7" s="17" t="str">
         <x:v>tags=attachment、external、pull</x:v>
       </x:c>
+      <x:c r="P7" s="152" t="n">
+        <x:f>IF(F7&gt;0,F7,0)</x:f>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="Q7" s="152" t="n">
+        <x:f>IF(F7&gt;0,ROUND(F7*0.5,0),0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="R7" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T7" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="17" t="str">
@@ -12172,6 +12850,23 @@
       <x:c r="O8" s="17" t="str">
         <x:v>tags=attachment、stock、bounce</x:v>
       </x:c>
+      <x:c r="P8" s="152" t="n">
+        <x:f>IF(F8&gt;0,F8,0)</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="Q8" s="152" t="n">
+        <x:f>IF(F8&gt;0,ROUND(F8*0.5,0),0)</x:f>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R8" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T8" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="17" t="str">
@@ -12215,6 +12910,23 @@
       <x:c r="O9" s="17" t="str">
         <x:v>tags=attachment、scope、crit</x:v>
       </x:c>
+      <x:c r="P9" s="152" t="n">
+        <x:f>IF(F9&gt;0,F9,0)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="Q9" s="152" t="n">
+        <x:f>IF(F9&gt;0,ROUND(F9*0.5,0),0)</x:f>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="R9" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S9" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T9" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="17" t="str">
@@ -12258,6 +12970,23 @@
       <x:c r="O10" s="17" t="str">
         <x:v>tags=attachment、muzzle、multi_shot</x:v>
       </x:c>
+      <x:c r="P10" s="152" t="n">
+        <x:f>IF(F10&gt;0,F10,0)</x:f>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="Q10" s="152" t="n">
+        <x:f>IF(F10&gt;0,ROUND(F10*0.5,0),0)</x:f>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="R10" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S10" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T10" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="17" t="str">
@@ -12305,6 +13034,23 @@
       <x:c r="O11" s="17" t="str">
         <x:v>tags=blueprint、gun_body、charge</x:v>
       </x:c>
+      <x:c r="P11" s="152" t="n">
+        <x:f>IF(F11&gt;0,F11,0)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="Q11" s="152" t="n">
+        <x:f>IF(F11&gt;0,ROUND(F11*0.5,0),0)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="R11" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S11" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T11" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="17" t="str">
@@ -12352,6 +13098,23 @@
       <x:c r="O12" s="17" t="str">
         <x:v>tags=blueprint、gun_body、launcher</x:v>
       </x:c>
+      <x:c r="P12" s="152" t="n">
+        <x:f>IF(F12&gt;0,F12,0)</x:f>
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="Q12" s="152" t="n">
+        <x:f>IF(F12&gt;0,ROUND(F12*0.5,0),0)</x:f>
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="R12" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S12" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T12" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="17" t="str">
@@ -12399,6 +13162,23 @@
       <x:c r="O13" s="17" t="str">
         <x:v>tags=blueprint、gun_body、auto</x:v>
       </x:c>
+      <x:c r="P13" s="152" t="n">
+        <x:f>IF(F13&gt;0,F13,0)</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="Q13" s="152" t="n">
+        <x:f>IF(F13&gt;0,ROUND(F13*0.5,0),0)</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="R13" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T13" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="17" t="str">
@@ -12446,6 +13226,23 @@
       <x:c r="O14" s="17" t="str">
         <x:v>tags=blueprint、gun_body</x:v>
       </x:c>
+      <x:c r="P14" s="152" t="n">
+        <x:f>IF(F14&gt;0,F14,0)</x:f>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q14" s="152" t="n">
+        <x:f>IF(F14&gt;0,ROUND(F14*0.5,0),0)</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="R14" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S14" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T14" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="17" t="str">
@@ -12493,6 +13290,23 @@
       <x:c r="O15" s="17" t="str">
         <x:v>tags=blueprint、gun_body、rifle</x:v>
       </x:c>
+      <x:c r="P15" s="152" t="n">
+        <x:f>IF(F15&gt;0,F15,0)</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="Q15" s="152" t="n">
+        <x:f>IF(F15&gt;0,ROUND(F15*0.5,0),0)</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="R15" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S15" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T15" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="17" t="str">
@@ -12540,6 +13354,23 @@
       <x:c r="O16" s="17" t="str">
         <x:v>tags=blueprint、gun_body、shotgun</x:v>
       </x:c>
+      <x:c r="P16" s="152" t="n">
+        <x:f>IF(F16&gt;0,F16,0)</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Q16" s="152" t="n">
+        <x:f>IF(F16&gt;0,ROUND(F16*0.5,0),0)</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R16" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S16" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T16" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="17" t="str">
@@ -12587,6 +13418,23 @@
       <x:c r="O17" s="17" t="str">
         <x:v>tags=blueprint、gun_body、sniper</x:v>
       </x:c>
+      <x:c r="P17" s="152" t="n">
+        <x:f>IF(F17&gt;0,F17,0)</x:f>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="Q17" s="152" t="n">
+        <x:f>IF(F17&gt;0,ROUND(F17*0.5,0),0)</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="R17" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S17" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T17" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="17" t="str">
@@ -12630,6 +13478,23 @@
       <x:c r="O18" s="17" t="str">
         <x:v>tags=consumable、ammo</x:v>
       </x:c>
+      <x:c r="P18" s="152" t="n">
+        <x:f>IF(F18&gt;0,F18,0)</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q18" s="152" t="n">
+        <x:f>IF(F18&gt;0,ROUND(F18*0.5,0),0)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="R18" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S18" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T18" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="17" t="str">
@@ -12675,6 +13540,23 @@
       <x:c r="O19" s="17" t="str">
         <x:v>tags=extraction、consumable、beacon</x:v>
       </x:c>
+      <x:c r="P19" s="152" t="n">
+        <x:f>IF(F19&gt;0,F19,0)</x:f>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="Q19" s="152" t="n">
+        <x:f>IF(F19&gt;0,ROUND(F19*0.5,0),0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="R19" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S19" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T19" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="17" t="str">
@@ -12718,6 +13600,23 @@
       <x:c r="O20" s="17" t="str">
         <x:v>tags=consumable、healing</x:v>
       </x:c>
+      <x:c r="P20" s="153" t="n">
+        <x:f>IF(F20&gt;0,F20,0)</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="Q20" s="153" t="n">
+        <x:f>IF(F20&gt;0,ROUND(F20*0.5,0),0)</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R20" s="151" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S20" s="150" t="str">
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="T20" s="153" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="17" t="str">
@@ -12758,6 +13657,23 @@
       </x:c>
       <x:c r="O21" s="17" t="str">
         <x:v>tags=key、progression</x:v>
+      </x:c>
+      <x:c r="P21" s="152" t="n">
+        <x:f>IF(F21&gt;0,F21,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q21" s="152" t="n">
+        <x:f>IF(F21&gt;0,ROUND(F21*0.5,0),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R21" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S21" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T21" s="152" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
@@ -12802,6 +13718,23 @@
       <x:c r="O22" s="17" t="str">
         <x:v>tags=module、bullet、balloon、slow</x:v>
       </x:c>
+      <x:c r="P22" s="152" t="n">
+        <x:f>IF(F22&gt;0,F22,0)</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="Q22" s="152" t="n">
+        <x:f>IF(F22&gt;0,ROUND(F22*0.5,0),0)</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="R22" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S22" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T22" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="17" t="str">
@@ -12845,6 +13778,23 @@
       <x:c r="O23" s="17" t="str">
         <x:v>tags=module、bullet、blackhole、pull</x:v>
       </x:c>
+      <x:c r="P23" s="152" t="n">
+        <x:f>IF(F23&gt;0,F23,0)</x:f>
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="Q23" s="152" t="n">
+        <x:f>IF(F23&gt;0,ROUND(F23*0.5,0),0)</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="R23" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S23" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T23" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="17" t="str">
@@ -12888,6 +13838,23 @@
       <x:c r="O24" s="17" t="str">
         <x:v>tags=module、bullet、bounce</x:v>
       </x:c>
+      <x:c r="P24" s="152" t="n">
+        <x:f>IF(F24&gt;0,F24,0)</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Q24" s="152" t="n">
+        <x:f>IF(F24&gt;0,ROUND(F24*0.5,0),0)</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R24" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S24" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T24" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="17" t="str">
@@ -12931,6 +13898,23 @@
       <x:c r="O25" s="17" t="str">
         <x:v>tags=module、bullet、explosive</x:v>
       </x:c>
+      <x:c r="P25" s="152" t="n">
+        <x:f>IF(F25&gt;0,F25,0)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="Q25" s="152" t="n">
+        <x:f>IF(F25&gt;0,ROUND(F25*0.5,0),0)</x:f>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="R25" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S25" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T25" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="54" customHeight="1">
       <x:c r="A26" s="17" t="str">
@@ -12974,6 +13958,23 @@
       <x:c r="O26" s="17" t="str">
         <x:v>tags=module、bullet、homing、summon</x:v>
       </x:c>
+      <x:c r="P26" s="152" t="n">
+        <x:f>IF(F26&gt;0,F26,0)</x:f>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="Q26" s="152" t="n">
+        <x:f>IF(F26&gt;0,ROUND(F26*0.5,0),0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="R26" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S26" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T26" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="54" customHeight="1">
       <x:c r="A27" s="17" t="str">
@@ -13017,6 +14018,23 @@
       <x:c r="O27" s="17" t="str">
         <x:v>tags=module、bullet、piercing</x:v>
       </x:c>
+      <x:c r="P27" s="152" t="n">
+        <x:f>IF(F27&gt;0,F27,0)</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="Q27" s="152" t="n">
+        <x:f>IF(F27&gt;0,ROUND(F27*0.5,0),0)</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="R27" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S27" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T27" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="54" customHeight="1">
       <x:c r="A28" s="17" t="str">
@@ -13060,6 +14078,23 @@
       <x:c r="O28" s="17" t="str">
         <x:v>tags=module、bullet</x:v>
       </x:c>
+      <x:c r="P28" s="152" t="n">
+        <x:f>IF(F28&gt;0,F28,0)</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q28" s="152" t="n">
+        <x:f>IF(F28&gt;0,ROUND(F28*0.5,0),0)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="R28" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S28" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T28" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="54" customHeight="1">
       <x:c r="A29" s="17" t="str">
@@ -13103,6 +14138,23 @@
       <x:c r="O29" s="17" t="str">
         <x:v>tags=module、bullet、sticky</x:v>
       </x:c>
+      <x:c r="P29" s="152" t="n">
+        <x:f>IF(F29&gt;0,F29,0)</x:f>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q29" s="152" t="n">
+        <x:f>IF(F29&gt;0,ROUND(F29*0.5,0),0)</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="R29" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S29" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T29" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="54" customHeight="1">
       <x:c r="A30" s="17" t="str">
@@ -13146,6 +14198,23 @@
       <x:c r="O30" s="17" t="str">
         <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
+      <x:c r="P30" s="152" t="n">
+        <x:f>IF(F30&gt;0,F30,0)</x:f>
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="Q30" s="152" t="n">
+        <x:f>IF(F30&gt;0,ROUND(F30*0.5,0),0)</x:f>
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="R30" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S30" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T30" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="54" customHeight="1">
       <x:c r="A31" s="17" t="str">
@@ -13189,6 +14258,23 @@
       <x:c r="O31" s="17" t="str">
         <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
+      <x:c r="P31" s="152" t="n">
+        <x:f>IF(F31&gt;0,F31,0)</x:f>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="Q31" s="152" t="n">
+        <x:f>IF(F31&gt;0,ROUND(F31*0.5,0),0)</x:f>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="R31" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S31" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T31" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="54" customHeight="1">
       <x:c r="A32" s="17" t="str">
@@ -13232,6 +14318,23 @@
       <x:c r="O32" s="17" t="str">
         <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
+      <x:c r="P32" s="152" t="n">
+        <x:f>IF(F32&gt;0,F32,0)</x:f>
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="Q32" s="152" t="n">
+        <x:f>IF(F32&gt;0,ROUND(F32*0.5,0),0)</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="R32" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S32" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T32" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="54" customHeight="1">
       <x:c r="A33" s="17" t="str">
@@ -13275,6 +14378,23 @@
       <x:c r="O33" s="17" t="str">
         <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
+      <x:c r="P33" s="153" t="n">
+        <x:f>IF(F33&gt;0,F33,0)</x:f>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="Q33" s="153" t="n">
+        <x:f>IF(F33&gt;0,ROUND(F33*0.5,0),0)</x:f>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="R33" s="151" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S33" s="150" t="str">
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="T33" s="153" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="54" customHeight="1">
       <x:c r="A34" s="17" t="str">
@@ -13318,6 +14438,23 @@
       <x:c r="O34" s="17" t="str">
         <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
+      <x:c r="P34" s="153" t="n">
+        <x:f>IF(F34&gt;0,F34,0)</x:f>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="Q34" s="153" t="n">
+        <x:f>IF(F34&gt;0,ROUND(F34*0.5,0),0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="R34" s="151" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S34" s="150" t="str">
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="T34" s="153" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="54" customHeight="1">
       <x:c r="A35" s="17" t="str">
@@ -13361,6 +14498,23 @@
       <x:c r="O35" s="17" t="str">
         <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
+      <x:c r="P35" s="153" t="n">
+        <x:f>IF(F35&gt;0,F35,0)</x:f>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="Q35" s="153" t="n">
+        <x:f>IF(F35&gt;0,ROUND(F35*0.5,0),0)</x:f>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="R35" s="151" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S35" s="150" t="str">
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="T35" s="153" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="54" customHeight="1">
       <x:c r="A36" s="17" t="str">
@@ -13404,6 +14558,23 @@
       <x:c r="O36" s="17" t="str">
         <x:v>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</x:v>
       </x:c>
+      <x:c r="P36" s="152" t="n">
+        <x:f>IF(F36&gt;0,F36,0)</x:f>
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="Q36" s="152" t="n">
+        <x:f>IF(F36&gt;0,ROUND(F36*0.5,0),0)</x:f>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="R36" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S36" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T36" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="54" customHeight="1">
       <x:c r="A37" s="17" t="str">
@@ -13451,6 +14622,23 @@
       <x:c r="O37" s="17" t="str">
         <x:v>必须记录来源阶段ID；不能与item_room_key互换</x:v>
       </x:c>
+      <x:c r="P37" s="152" t="n">
+        <x:f>IF(F37&gt;0,F37,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q37" s="152" t="n">
+        <x:f>IF(F37&gt;0,ROUND(F37*0.5,0),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R37" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S37" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T37" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
@@ -13498,6 +14686,23 @@
       <x:c r="O38" t="str">
         <x:v>tags=equipment, backpack, capacity；基础12+2；浅层搜索/普通怪偏重</x:v>
       </x:c>
+      <x:c r="P38" s="153" t="n">
+        <x:f>IF(F38&gt;0,F38,0)</x:f>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="Q38" s="153" t="n">
+        <x:f>IF(F38&gt;0,ROUND(F38*0.5,0),0)</x:f>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="R38" s="151" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S38" s="150" t="str">
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="T38" s="153" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
@@ -13545,6 +14750,23 @@
       <x:c r="O39" t="str">
         <x:v>tags=equipment, backpack, capacity；基础12+4；中层搜索/精英偏重</x:v>
       </x:c>
+      <x:c r="P39" s="152" t="n">
+        <x:f>IF(F39&gt;0,F39,0)</x:f>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="Q39" s="152" t="n">
+        <x:f>IF(F39&gt;0,ROUND(F39*0.5,0),0)</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="R39" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S39" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T39" s="152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
@@ -13591,6 +14813,23 @@
       </x:c>
       <x:c r="O40" t="str">
         <x:v>tags=equipment, backpack, capacity；基础12+8；深层搜索/精英/Boss偏重</x:v>
+      </x:c>
+      <x:c r="P40" s="152" t="n">
+        <x:f>IF(F40&gt;0,F40,0)</x:f>
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="Q40" s="152" t="n">
+        <x:f>IF(F40&gt;0,ROUND(F40*0.5,0),0)</x:f>
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="R40" s="145" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S40" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="T40" s="152" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14880,6 +16119,136 @@
         <x:v>[用户设计]</x:v>
       </x:c>
     </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="144" t="str">
+        <x:v>物品/武器</x:v>
+      </x:c>
+      <x:c r="B51" s="144" t="str">
+        <x:v>base_buy_price</x:v>
+      </x:c>
+      <x:c r="C51" s="144" t="str">
+        <x:v>基地购买价</x:v>
+      </x:c>
+      <x:c r="D51" s="144" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="E51" s="144" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="F51" s="144" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G51" s="144" t="str">
+        <x:v>自动贩卖机购买所需 extraction_points；0 表示不可购买</x:v>
+      </x:c>
+      <x:c r="H51" s="144" t="str">
+        <x:v>掉落物品/武器</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="144" t="str">
+        <x:v>物品/武器</x:v>
+      </x:c>
+      <x:c r="B52" s="144" t="str">
+        <x:v>base_sell_price</x:v>
+      </x:c>
+      <x:c r="C52" s="144" t="str">
+        <x:v>基地出售价</x:v>
+      </x:c>
+      <x:c r="D52" s="144" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="E52" s="144" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="F52" s="144" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G52" s="144" t="str">
+        <x:v>自动贩卖机收购物品给予的 extraction_points；成交时以数据库为准</x:v>
+      </x:c>
+      <x:c r="H52" s="144" t="str">
+        <x:v>掉落物品/武器</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="144" t="str">
+        <x:v>物品/武器</x:v>
+      </x:c>
+      <x:c r="B53" s="144" t="str">
+        <x:v>base_shop_enabled</x:v>
+      </x:c>
+      <x:c r="C53" s="144" t="str">
+        <x:v>基地商店上架</x:v>
+      </x:c>
+      <x:c r="D53" s="144" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="E53" s="144" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="F53" s="144" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="G53" s="144" t="str">
+        <x:v>仅 true 且价格合法的条目进入基地货架</x:v>
+      </x:c>
+      <x:c r="H53" s="144" t="str">
+        <x:v>掉落物品/武器</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="144" t="str">
+        <x:v>物品/武器</x:v>
+      </x:c>
+      <x:c r="B54" s="144" t="str">
+        <x:v>base_stock_rule</x:v>
+      </x:c>
+      <x:c r="C54" s="144" t="str">
+        <x:v>基地库存规则</x:v>
+      </x:c>
+      <x:c r="D54" s="144" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E54" s="144" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="F54" s="144" t="str">
+        <x:v>not_listed</x:v>
+      </x:c>
+      <x:c r="G54" s="144" t="str">
+        <x:v>unlimited=无限；not_listed=不上架；为后续限购预留</x:v>
+      </x:c>
+      <x:c r="H54" s="144" t="str">
+        <x:v>掉落物品/武器</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="144" t="str">
+        <x:v>物品/武器</x:v>
+      </x:c>
+      <x:c r="B55" s="144" t="str">
+        <x:v>base_shelf_order</x:v>
+      </x:c>
+      <x:c r="C55" s="144" t="str">
+        <x:v>基地货架顺序</x:v>
+      </x:c>
+      <x:c r="D55" s="144" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="E55" s="144" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="F55" s="144" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G55" s="144" t="str">
+        <x:v>大于0的稳定展示顺序；不可用名称或数组下标作主键</x:v>
+      </x:c>
+      <x:c r="H55" s="144" t="str">
+        <x:v>掉落物品/武器</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
@@ -14893,4 +16262,452 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="34" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="22" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="22" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="22" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="157" t="str">
+        <x:v>基地自动贩卖机｜固定货物清单 v0.1</x:v>
+      </x:c>
+      <x:c r="B1" s="157"/>
+      <x:c r="C1" s="157"/>
+      <x:c r="D1" s="157"/>
+      <x:c r="E1" s="157"/>
+      <x:c r="F1" s="157"/>
+      <x:c r="G1" s="157"/>
+      <x:c r="H1" s="157"/>
+      <x:c r="I1" s="157"/>
+      <x:c r="J1" s="157"/>
+      <x:c r="K1" s="157"/>
+      <x:c r="L1" s="157"/>
+      <x:c r="M1" s="157"/>
+      <x:c r="N1" s="157"/>
+      <x:c r="O1" s="157"/>
+      <x:c r="P1" s="157"/>
+      <x:c r="Q1" s="157"/>
+      <x:c r="R1" s="157"/>
+    </x:row>
+    <x:row r="2" ht="26" customHeight="1">
+      <x:c r="A2" s="161" t="str">
+        <x:v>价格、上架与库存公式回查《掉落物品》；ItemRegistry 运行时定义必须与本表验收一致。购买进入保险柜并生成独立实例。</x:v>
+      </x:c>
+      <x:c r="B2" s="161"/>
+      <x:c r="C2" s="161"/>
+      <x:c r="D2" s="161"/>
+      <x:c r="E2" s="161"/>
+      <x:c r="F2" s="161"/>
+      <x:c r="G2" s="161"/>
+      <x:c r="H2" s="161"/>
+      <x:c r="I2" s="161"/>
+      <x:c r="J2" s="161"/>
+      <x:c r="K2" s="161"/>
+      <x:c r="L2" s="161"/>
+      <x:c r="M2" s="161"/>
+      <x:c r="N2" s="161"/>
+      <x:c r="O2" s="161"/>
+      <x:c r="P2" s="161"/>
+      <x:c r="Q2" s="161"/>
+      <x:c r="R2" s="161"/>
+    </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="A4" s="134" t="str">
+        <x:v>货架ID</x:v>
+      </x:c>
+      <x:c r="B4" s="134" t="str">
+        <x:v>facility_id</x:v>
+      </x:c>
+      <x:c r="C4" s="134" t="str">
+        <x:v>物品ID</x:v>
+      </x:c>
+      <x:c r="D4" s="134" t="str">
+        <x:v>来源表</x:v>
+      </x:c>
+      <x:c r="E4" s="134" t="str">
+        <x:v>名称</x:v>
+      </x:c>
+      <x:c r="F4" s="134" t="str">
+        <x:v>类型</x:v>
+      </x:c>
+      <x:c r="G4" s="134" t="str">
+        <x:v>货币</x:v>
+      </x:c>
+      <x:c r="H4" s="134" t="str">
+        <x:v>购买价</x:v>
+      </x:c>
+      <x:c r="I4" s="134" t="str">
+        <x:v>出售价</x:v>
+      </x:c>
+      <x:c r="J4" s="134" t="str">
+        <x:v>库存规则</x:v>
+      </x:c>
+      <x:c r="K4" s="134" t="str">
+        <x:v>顺序</x:v>
+      </x:c>
+      <x:c r="L4" s="134" t="str">
+        <x:v>购买去向</x:v>
+      </x:c>
+      <x:c r="M4" s="134" t="str">
+        <x:v>实例规则</x:v>
+      </x:c>
+      <x:c r="N4" s="134" t="str">
+        <x:v>上架</x:v>
+      </x:c>
+      <x:c r="O4" s="134" t="str">
+        <x:v>状态来源</x:v>
+      </x:c>
+      <x:c r="P4" s="134" t="str">
+        <x:v>实现状态</x:v>
+      </x:c>
+      <x:c r="Q4" s="134" t="str">
+        <x:v>事实源</x:v>
+      </x:c>
+      <x:c r="R4" s="134" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="34" customHeight="1">
+      <x:c r="A5" s="144" t="str">
+        <x:v>base_stock_pistol</x:v>
+      </x:c>
+      <x:c r="B5" s="144" t="str">
+        <x:v>base_vending</x:v>
+      </x:c>
+      <x:c r="C5" s="144" t="str">
+        <x:v>weapon_pistol</x:v>
+      </x:c>
+      <x:c r="D5" s="144" t="str">
+        <x:v>掉落物品</x:v>
+      </x:c>
+      <x:c r="E5" s="144" t="str">
+        <x:f>XLOOKUP(C5,'掉落物品'!$A$5:$A$40,'掉落物品'!$B$5:$B$40,"缺失")</x:f>
+        <x:v>豌豆手枪</x:v>
+      </x:c>
+      <x:c r="F5" s="144" t="str">
+        <x:f>XLOOKUP(C5,'掉落物品'!$A$5:$A$40,'掉落物品'!$C$5:$C$40,"缺失")</x:f>
+        <x:v>weapon</x:v>
+      </x:c>
+      <x:c r="G5" s="144" t="str">
+        <x:v>extraction_points</x:v>
+      </x:c>
+      <x:c r="H5" s="152" t="n">
+        <x:f>XLOOKUP(C5,'掉落物品'!$A$5:$A$40,'掉落物品'!$P$5:$P$40,0)</x:f>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I5" s="152" t="n">
+        <x:f>XLOOKUP(C5,'掉落物品'!$A$5:$A$40,'掉落物品'!$Q$5:$Q$40,0)</x:f>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J5" s="144" t="str">
+        <x:f>XLOOKUP(C5,'掉落物品'!$A$5:$A$40,'掉落物品'!$S$5:$S$40,"not_listed")</x:f>
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="K5" s="152" t="n">
+        <x:f>XLOOKUP(C5,'掉落物品'!$A$5:$A$40,'掉落物品'!$T$5:$T$40,0)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L5" s="144" t="str">
+        <x:v>vault</x:v>
+      </x:c>
+      <x:c r="M5" s="144" t="str">
+        <x:v>枪械进入保险柜；生成 item_instance_id + weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="N5" s="144" t="b">
+        <x:f>XLOOKUP(C5,'掉落物品'!$A$5:$A$40,'掉落物品'!$R$5:$R$40,FALSE)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O5" s="144" t="str">
+        <x:v>用户设计+Codex补充</x:v>
+      </x:c>
+      <x:c r="P5" s="144" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="Q5" s="144" t="str">
+        <x:v>ItemRegistry/BaseShopService</x:v>
+      </x:c>
+      <x:c r="R5" s="144" t="str">
+        <x:v>基础手枪</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="34" customHeight="1">
+      <x:c r="A6" s="144" t="str">
+        <x:v>base_stock_shotgun</x:v>
+      </x:c>
+      <x:c r="B6" s="144" t="str">
+        <x:v>base_vending</x:v>
+      </x:c>
+      <x:c r="C6" s="144" t="str">
+        <x:v>weapon_shotgun</x:v>
+      </x:c>
+      <x:c r="D6" s="144" t="str">
+        <x:v>掉落物品</x:v>
+      </x:c>
+      <x:c r="E6" s="144" t="str">
+        <x:f>XLOOKUP(C6,'掉落物品'!$A$5:$A$40,'掉落物品'!$B$5:$B$40,"缺失")</x:f>
+        <x:v>散射喷壶</x:v>
+      </x:c>
+      <x:c r="F6" s="144" t="str">
+        <x:f>XLOOKUP(C6,'掉落物品'!$A$5:$A$40,'掉落物品'!$C$5:$C$40,"缺失")</x:f>
+        <x:v>weapon</x:v>
+      </x:c>
+      <x:c r="G6" s="144" t="str">
+        <x:v>extraction_points</x:v>
+      </x:c>
+      <x:c r="H6" s="152" t="n">
+        <x:f>XLOOKUP(C6,'掉落物品'!$A$5:$A$40,'掉落物品'!$P$5:$P$40,0)</x:f>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="I6" s="152" t="n">
+        <x:f>XLOOKUP(C6,'掉落物品'!$A$5:$A$40,'掉落物品'!$Q$5:$Q$40,0)</x:f>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J6" s="144" t="str">
+        <x:f>XLOOKUP(C6,'掉落物品'!$A$5:$A$40,'掉落物品'!$S$5:$S$40,"not_listed")</x:f>
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="K6" s="152" t="n">
+        <x:f>XLOOKUP(C6,'掉落物品'!$A$5:$A$40,'掉落物品'!$T$5:$T$40,0)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L6" s="144" t="str">
+        <x:v>vault</x:v>
+      </x:c>
+      <x:c r="M6" s="144" t="str">
+        <x:v>枪械进入保险柜；生成 item_instance_id + weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="N6" s="144" t="b">
+        <x:f>XLOOKUP(C6,'掉落物品'!$A$5:$A$40,'掉落物品'!$R$5:$R$40,FALSE)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O6" s="144" t="str">
+        <x:v>用户设计+Codex补充</x:v>
+      </x:c>
+      <x:c r="P6" s="144" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="Q6" s="144" t="str">
+        <x:v>ItemRegistry/BaseShopService</x:v>
+      </x:c>
+      <x:c r="R6" s="144" t="str">
+        <x:v>基础霰弹枪</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="A7" s="144" t="str">
+        <x:v>base_stock_rifle</x:v>
+      </x:c>
+      <x:c r="B7" s="144" t="str">
+        <x:v>base_vending</x:v>
+      </x:c>
+      <x:c r="C7" s="144" t="str">
+        <x:v>weapon_rifle</x:v>
+      </x:c>
+      <x:c r="D7" s="144" t="str">
+        <x:v>掉落物品</x:v>
+      </x:c>
+      <x:c r="E7" s="144" t="str">
+        <x:f>XLOOKUP(C7,'掉落物品'!$A$5:$A$40,'掉落物品'!$B$5:$B$40,"缺失")</x:f>
+        <x:v>步枪</x:v>
+      </x:c>
+      <x:c r="F7" s="144" t="str">
+        <x:f>XLOOKUP(C7,'掉落物品'!$A$5:$A$40,'掉落物品'!$C$5:$C$40,"缺失")</x:f>
+        <x:v>weapon</x:v>
+      </x:c>
+      <x:c r="G7" s="144" t="str">
+        <x:v>extraction_points</x:v>
+      </x:c>
+      <x:c r="H7" s="152" t="n">
+        <x:f>XLOOKUP(C7,'掉落物品'!$A$5:$A$40,'掉落物品'!$P$5:$P$40,0)</x:f>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="I7" s="152" t="n">
+        <x:f>XLOOKUP(C7,'掉落物品'!$A$5:$A$40,'掉落物品'!$Q$5:$Q$40,0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J7" s="144" t="str">
+        <x:f>XLOOKUP(C7,'掉落物品'!$A$5:$A$40,'掉落物品'!$S$5:$S$40,"not_listed")</x:f>
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="K7" s="152" t="n">
+        <x:f>XLOOKUP(C7,'掉落物品'!$A$5:$A$40,'掉落物品'!$T$5:$T$40,0)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L7" s="144" t="str">
+        <x:v>vault</x:v>
+      </x:c>
+      <x:c r="M7" s="144" t="str">
+        <x:v>枪械进入保险柜；生成 item_instance_id + weapon_instance_id</x:v>
+      </x:c>
+      <x:c r="N7" s="144" t="b">
+        <x:f>XLOOKUP(C7,'掉落物品'!$A$5:$A$40,'掉落物品'!$R$5:$R$40,FALSE)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O7" s="144" t="str">
+        <x:v>用户设计+Codex补充</x:v>
+      </x:c>
+      <x:c r="P7" s="144" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="Q7" s="144" t="str">
+        <x:v>ItemRegistry/BaseShopService</x:v>
+      </x:c>
+      <x:c r="R7" s="144" t="str">
+        <x:v>基础步枪</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="A8" s="144" t="str">
+        <x:v>base_stock_backpack_2</x:v>
+      </x:c>
+      <x:c r="B8" s="144" t="str">
+        <x:v>base_vending</x:v>
+      </x:c>
+      <x:c r="C8" s="144" t="str">
+        <x:v>equipment_backpack_2</x:v>
+      </x:c>
+      <x:c r="D8" s="144" t="str">
+        <x:v>掉落物品</x:v>
+      </x:c>
+      <x:c r="E8" s="144" t="str">
+        <x:f>XLOOKUP(C8,'掉落物品'!$A$5:$A$40,'掉落物品'!$B$5:$B$40,"缺失")</x:f>
+        <x:v>轻型腰包</x:v>
+      </x:c>
+      <x:c r="F8" s="144" t="str">
+        <x:f>XLOOKUP(C8,'掉落物品'!$A$5:$A$40,'掉落物品'!$C$5:$C$40,"缺失")</x:f>
+        <x:v>equipment</x:v>
+      </x:c>
+      <x:c r="G8" s="144" t="str">
+        <x:v>extraction_points</x:v>
+      </x:c>
+      <x:c r="H8" s="152" t="n">
+        <x:f>XLOOKUP(C8,'掉落物品'!$A$5:$A$40,'掉落物品'!$P$5:$P$40,0)</x:f>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I8" s="152" t="n">
+        <x:f>XLOOKUP(C8,'掉落物品'!$A$5:$A$40,'掉落物品'!$Q$5:$Q$40,0)</x:f>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J8" s="144" t="str">
+        <x:f>XLOOKUP(C8,'掉落物品'!$A$5:$A$40,'掉落物品'!$S$5:$S$40,"not_listed")</x:f>
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="K8" s="152" t="n">
+        <x:f>XLOOKUP(C8,'掉落物品'!$A$5:$A$40,'掉落物品'!$T$5:$T$40,0)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L8" s="144" t="str">
+        <x:v>vault</x:v>
+      </x:c>
+      <x:c r="M8" s="144" t="str">
+        <x:v>装备进入保险柜；生成 item_instance_id</x:v>
+      </x:c>
+      <x:c r="N8" s="144" t="b">
+        <x:f>XLOOKUP(C8,'掉落物品'!$A$5:$A$40,'掉落物品'!$R$5:$R$40,FALSE)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O8" s="144" t="str">
+        <x:v>用户设计+Codex补充</x:v>
+      </x:c>
+      <x:c r="P8" s="144" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="Q8" s="144" t="str">
+        <x:v>ItemRegistry/BaseShopService</x:v>
+      </x:c>
+      <x:c r="R8" s="144" t="str">
+        <x:v>+2格初级背包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="A9" s="144" t="str">
+        <x:v>base_stock_health_potion</x:v>
+      </x:c>
+      <x:c r="B9" s="144" t="str">
+        <x:v>base_vending</x:v>
+      </x:c>
+      <x:c r="C9" s="144" t="str">
+        <x:v>item_health_potion</x:v>
+      </x:c>
+      <x:c r="D9" s="144" t="str">
+        <x:v>掉落物品</x:v>
+      </x:c>
+      <x:c r="E9" s="144" t="str">
+        <x:f>XLOOKUP(C9,'掉落物品'!$A$5:$A$40,'掉落物品'!$B$5:$B$40,"缺失")</x:f>
+        <x:v>治疗药水</x:v>
+      </x:c>
+      <x:c r="F9" s="144" t="str">
+        <x:f>XLOOKUP(C9,'掉落物品'!$A$5:$A$40,'掉落物品'!$C$5:$C$40,"缺失")</x:f>
+        <x:v>consumable</x:v>
+      </x:c>
+      <x:c r="G9" s="144" t="str">
+        <x:v>extraction_points</x:v>
+      </x:c>
+      <x:c r="H9" s="152" t="n">
+        <x:f>XLOOKUP(C9,'掉落物品'!$A$5:$A$40,'掉落物品'!$P$5:$P$40,0)</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I9" s="152" t="n">
+        <x:f>XLOOKUP(C9,'掉落物品'!$A$5:$A$40,'掉落物品'!$Q$5:$Q$40,0)</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J9" s="144" t="str">
+        <x:f>XLOOKUP(C9,'掉落物品'!$A$5:$A$40,'掉落物品'!$S$5:$S$40,"not_listed")</x:f>
+        <x:v>unlimited</x:v>
+      </x:c>
+      <x:c r="K9" s="152" t="n">
+        <x:f>XLOOKUP(C9,'掉落物品'!$A$5:$A$40,'掉落物品'!$T$5:$T$40,0)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L9" s="144" t="str">
+        <x:v>vault</x:v>
+      </x:c>
+      <x:c r="M9" s="144" t="str">
+        <x:v>道具进入保险柜；生成 item_instance_id</x:v>
+      </x:c>
+      <x:c r="N9" s="144" t="b">
+        <x:f>XLOOKUP(C9,'掉落物品'!$A$5:$A$40,'掉落物品'!$R$5:$R$40,FALSE)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O9" s="144" t="str">
+        <x:v>用户设计+Codex补充</x:v>
+      </x:c>
+      <x:c r="P9" s="144" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="Q9" s="144" t="str">
+        <x:v>ItemRegistry/BaseShopService</x:v>
+      </x:c>
+      <x:c r="R9" s="144" t="str">
+        <x:v>基础治疗药水</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:R1"/>
+    <x:mergeCell ref="A2:R2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8f8fcd40f39848a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="Re20866e40c5e4317"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R7352404713ea4b27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="R19884d60427c443f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="Rba264e0971354172"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R6a862a4277ce4c1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R9cfa40dde04d48cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" r:id="R43cb3bd164774a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R7fa677e34c994dce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="R9d09e21b4e514a69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R60440116c45a4bee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="R3a1ce48cde334b4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="R902963d45212489c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R38ab98538a4f454b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R35e47b3f0b1a453e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" r:id="R50fca7b391ab460e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3872,13 +3872,13 @@
         <x:v>史诗</x:v>
       </x:c>
       <x:c r="E8" s="91" t="str">
-        <x:v>下箱额外2件</x:v>
+        <x:v>下箱追加2抽，保留最佳</x:v>
       </x:c>
       <x:c r="F8" s="91" t="str">
-        <x:v>下一个开启容器额外掉落2件物品</x:v>
+        <x:v>下一个容器追加2次候选抽取并保留最高品质结果，地面仍只掉落1件</x:v>
       </x:c>
       <x:c r="G8" s="91" t="str">
-        <x:v>太阳延长了这一日的收成，让下一个容器吐出更多物资。</x:v>
+        <x:v>太阳延长了这一日的收成，但只让猎人带走其中最值得的一件。</x:v>
       </x:c>
       <x:c r="H8" s="91" t="str">
         <x:v>[用户设计]</x:v>
@@ -3915,7 +3915,7 @@
         <x:v>☀ 太阳命运｜皇后｜翻牌后显示正位/逆位、目标、槽位与对应功能</x:v>
       </x:c>
       <x:c r="T8" s="91" t="str">
-        <x:v>卡背绕Y轴翻面；逆位整张正面卡牌（含边框、图案、文字与布局）收束180°，并显示逆位效果描述；开箱时额外生成2件物品并清空计数</x:v>
+        <x:v>开箱时追加2次候选扫描，界面闪过候选后只生成1个最高品质地面实体并清空计数</x:v>
       </x:c>
       <x:c r="U8" s="91" t="str">
         <x:v>[部分实装] 通用卡背/翻牌/逆位倒置已验收；逐卡逆位专属VFX与音效继续QA</x:v>
@@ -3939,13 +3939,13 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="AB8" s="118" t="str">
-        <x:v>下一个开启容器额外掉落2件物品</x:v>
+        <x:v>下一个容器追加2次候选抽取并保留最高品质结果，地面仍只掉落1件</x:v>
       </x:c>
       <x:c r="AC8" s="118" t="str">
         <x:v>action=APPLY_SCOPED_MODIFIER；modifier=next_chest_extra；count=2</x:v>
       </x:c>
       <x:c r="AD8" s="115" t="str">
-        <x:v>下一容器额外4件，品质上限为稀有</x:v>
+        <x:v>下一容器追加4次候选抽取并保留最佳，品质上限为稀有，地面仍只掉落1件</x:v>
       </x:c>
       <x:c r="AE8" s="115" t="str">
         <x:v>action=APPLY_SCOPED_MODIFIER; modifier=next_chest_extra_capped; count=4; rarity_cap=RARE</x:v>
@@ -10123,13 +10123,13 @@
         <x:v>稀有</x:v>
       </x:c>
       <x:c r="E71" s="91" t="str">
-        <x:v>下一箱额外掉落一件物品</x:v>
+        <x:v>下一箱追加抽取，仍落一件</x:v>
       </x:c>
       <x:c r="F71" s="91" t="str">
-        <x:v>下一个开启的箱子额外掉落一件随机物品</x:v>
+        <x:v>下一个开启的箱子增加一次候选抽取并保留更优结果，地面仍只掉落一件物品</x:v>
       </x:c>
       <x:c r="G71" s="91" t="str">
-        <x:v>命运在下一个箱子的清单末尾多写了一行，内容直到打开才确定。</x:v>
+        <x:v>命运在下一个箱子的清单末尾多写一行，再从两份结果里只留下更好的一件。</x:v>
       </x:c>
       <x:c r="H71" s="91" t="str">
         <x:v>[Codex补充]</x:v>
@@ -10166,7 +10166,7 @@
         <x:v>☀ 太阳命运｜星币·三｜翻牌后显示正位/逆位、目标、槽位与对应功能</x:v>
       </x:c>
       <x:c r="T71" s="91" t="str">
-        <x:v>卡背绕Y轴翻面；逆位整张正面卡牌（含边框、图案、文字与布局）收束180°，并显示逆位效果描述；有效击杀或开箱时出现额外掉落光束和来源提示，触发后计数归零</x:v>
+        <x:v>开箱时出现一次额外候选扫描和来源提示，触发后只生成1个地面实体并清空计数</x:v>
       </x:c>
       <x:c r="U71" s="91" t="str">
         <x:v>[部分实装] 通用卡背/翻牌/逆位倒置已验收；逐卡逆位专属VFX与音效继续QA</x:v>
@@ -10190,13 +10190,13 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="AB71" s="118" t="str">
-        <x:v>下一个开启的箱子额外掉落一件随机物品</x:v>
+        <x:v>下一个开启的箱子增加一次候选抽取并保留更优结果，地面仍只掉落一件物品</x:v>
       </x:c>
       <x:c r="AC71" s="118" t="str">
         <x:v>action=EXTRA_LOOT；extra_count=1</x:v>
       </x:c>
       <x:c r="AD71" s="115" t="str">
-        <x:v>下一容器减少1件，剩余物品品质+1</x:v>
+        <x:v>下一容器追加一次候选抽取，保留结果品质提高1级，地面仍只掉落1件</x:v>
       </x:c>
       <x:c r="AE71" s="115" t="str">
         <x:v>action=EXTRA_LOOT_TRADE; count_delta=-1; rarity_tiers=1</x:v>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R03c7dbb9d8fc4cc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="Rdec97c2923104615"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R38db7e54969c4d6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="Rada2bcb32e974190"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="Rd04d4f16fbce432e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R0b3c9884f1104bf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R2181b74a05dc44ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" r:id="Rbfbaa03ea62045d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R3a48eead61a84fb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="R866596ae33fa4b28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R9268bc8109ab497f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="Rc9d2f8511104409c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="R8d718b8f222748c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R2d56d4bcdd0d4b08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R599fafbbae5e4367"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" r:id="R041f92cb5d0b42bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1278,11 +1278,11 @@
       </x:c>
       <x:c r="B8" s="29" t="n">
         <x:f>COUNTA('怪物与Boss'!$A$5:$A$204)</x:f>
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C8" s="34" t="n">
         <x:f>COUNTIF('怪物与Boss'!$L$5:$L$204,"[已实装]")</x:f>
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D8" s="35" t="n">
         <x:f>COUNTIF('怪物与Boss'!$L$5:$L$204,"[用户设计]")</x:f>
@@ -17301,20 +17301,14 @@
       </x:c>
     </x:row>
     <x:row r="6" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">monster_boss_generic</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Boss（通用模板）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">boss</x:t>
-        </x:is>
+      <x:c r="A6" s="17" t="str">
+        <x:v>monster_boss_generic</x:v>
+      </x:c>
+      <x:c r="B6" s="17" t="str">
+        <x:v>Boss（通用回退模板）</x:v>
+      </x:c>
+      <x:c r="C6" s="17" t="str">
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="D6" s="17" t="n">
         <x:v>520</x:v>
@@ -17331,40 +17325,26 @@
       <x:c r="H6" s="17" t="n">
         <x:v>1.45</x:v>
       </x:c>
-      <x:c r="I6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">阶段变化；1/3发爆炸弹幕；周期召唤2只；Boss HUD</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">当前95层BOSS房；未来各Boss楼层</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">boss_floor_*；Boss专用钥匙待接</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L6" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">[已实装]</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">正式3D通用Boss；独立楼层Boss内容待扩展</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">src/enemy3d/Enemy3D.gd；src/map/MonsterInjector.gd</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">正式数值以Enemy3D.PROFILES为基线；旧2D基线仅用于倍率换算</x:t>
-        </x:is>
+      <x:c r="I6" s="17" t="str">
+        <x:v>无独立内容ID时使用的确定性弹幕/召唤回退</x:v>
+      </x:c>
+      <x:c r="J6" s="17" t="str">
+        <x:v>测试/未来未配置Boss楼层</x:v>
+      </x:c>
+      <x:c r="K6" s="17" t="str">
+        <x:v>boss_floor_*</x:v>
+      </x:c>
+      <x:c r="L6" s="18" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M6" s="17" t="str">
+        <x:v>正式3D低模回退；不作为95/90/85正式内容</x:v>
+      </x:c>
+      <x:c r="N6" s="17" t="str">
+        <x:v>src/enemy3d/Enemy3D.gd；src/map/MonsterInjector.gd</x:v>
+      </x:c>
+      <x:c r="O6" s="17" t="str">
+        <x:v>正式Boss由BossContentCatalog替换模型和阶段技能袋</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="135" customFormat="1" ht="54" customHeight="1">
@@ -17700,6 +17680,147 @@
         <x:is>
           <x:t xml:space="preserve">正式数值以Enemy3D.PROFILES为基线；旧2D基线仅用于倍率换算</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>boss_abyss_archivist_95</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>深渊档案官</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>1.72</x:v>
+      </x:c>
+      <x:c r="F12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G12" t="n">
+        <x:v>9.5</x:v>
+      </x:c>
+      <x:c r="H12" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>archive_fan / index_beam / archive_storm；召唤档案侍从</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>95F不可绕过Boss竞技场</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>boss_floor_5；专用下行权限</x:v>
+      </x:c>
+      <x:c r="L12" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M12" t="str">
+        <x:v>独立Boss内容/模型/竞技场</x:v>
+      </x:c>
+      <x:c r="N12" t="str">
+        <x:v>src/enemy3d/BossContentCatalog.gd；assets/art/enemies/bosses_v01/enm_boss_archivist_95_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="O12" t="str">
+        <x:v>独立三阶段技能袋；档案竞技场8组掩体</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>boss_furnace_warden_90</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>熔炉狱监</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E13" t="n">
+        <x:v>1.72</x:v>
+      </x:c>
+      <x:c r="F13" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G13" t="n">
+        <x:v>9.5</x:v>
+      </x:c>
+      <x:c r="H13" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>molten_volley / hammer_drive / furnace_burst；召唤余烬</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>90F不可绕过Boss竞技场</x:v>
+      </x:c>
+      <x:c r="K13" t="str">
+        <x:v>boss_floor_10；专用下行权限</x:v>
+      </x:c>
+      <x:c r="L13" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M13" t="str">
+        <x:v>独立Boss内容/模型/竞技场</x:v>
+      </x:c>
+      <x:c r="N13" t="str">
+        <x:v>src/enemy3d/BossContentCatalog.gd；assets/art/enemies/bosses_v01/enm_boss_furnace_warden_90_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="O13" t="str">
+        <x:v>独立三阶段技能袋；熔炉竞技场6组掩体</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>boss_hollow_choir_85</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>空洞合唱团</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E14" t="n">
+        <x:v>1.72</x:v>
+      </x:c>
+      <x:c r="F14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G14" t="n">
+        <x:v>9.5</x:v>
+      </x:c>
+      <x:c r="H14" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>choir_wave / silence_chord / echo_burst；召唤回声</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>85F不可绕过Boss竞技场</x:v>
+      </x:c>
+      <x:c r="K14" t="str">
+        <x:v>boss_floor_15；专用下行权限</x:v>
+      </x:c>
+      <x:c r="L14" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M14" t="str">
+        <x:v>独立Boss内容/模型/竞技场</x:v>
+      </x:c>
+      <x:c r="N14" t="str">
+        <x:v>src/enemy3d/BossContentCatalog.gd；assets/art/enemies/bosses_v01/enm_boss_hollow_choir_85_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="O14" t="str">
+        <x:v>独立三阶段技能袋；合唱竞技场5组掩体</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -17746,11 +17867,23 @@
       </x:c>
     </x:row>
     <x:row r="2" s="135" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A2" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">名册固定12只并由用户设计冻结。前2只来自现有兼容原型；其余10只名称与玩法为Codex补充，可由主设计者后续调整但不改变全局唯一规则。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A2" s="7" t="str">
+        <x:v>名册固定12只并由用户设计冻结。2026-08-13已全部接入EliteRosterService、BaseData 1.7和各自实时行为；内容名称可迭代但稳定ID不可改变。</x:v>
+      </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+      <x:c r="M2"/>
+      <x:c r="N2"/>
+      <x:c r="O2"/>
     </x:row>
     <x:row r="3" s="135" customFormat="1" ht="30" customHeight="1">
       <x:c r="A3" s="7" t="inlineStr">
@@ -17897,20 +18030,14 @@
           <x:t xml:space="preserve">[已实装]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M5" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">兼容精英原型；未接正式3D</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N5" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">src/game/EliteArchiveModule.gd</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O5" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">原型名称与成长记录保留</x:t>
-        </x:is>
+      <x:c r="M5" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N5" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O5" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="135" customFormat="1" ht="54" customHeight="1">
@@ -17974,20 +18101,14 @@
           <x:t xml:space="preserve">[已实装]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">兼容精英原型；未接正式3D</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">src/game/EliteArchiveModule.gd</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">原型能力需适配Projectile3D</x:t>
-        </x:is>
+      <x:c r="M6" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N6" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O6" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="135" customFormat="1" ht="54" customHeight="1">
@@ -18051,20 +18172,14 @@
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M7" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N7" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">游戏内容数据库</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O7" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">强调绕后与穿甲价值</x:t>
-        </x:is>
+      <x:c r="M7" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N7" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O7" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="135" customFormat="1" ht="54" customHeight="1">
@@ -18128,20 +18243,14 @@
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M8" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N8" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">游戏内容数据库</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O8" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">先清节点还是集火本体的战术选择</x:t>
-        </x:is>
+      <x:c r="M8" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N8" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O8" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="135" customFormat="1" ht="54" customHeight="1">
@@ -18205,20 +18314,14 @@
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M9" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N9" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">游戏内容数据库</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O9" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">保留自爆怪识别但形成持续战斗</x:t>
-        </x:is>
+      <x:c r="M9" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N9" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O9" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="135" customFormat="1" ht="54" customHeight="1">
@@ -18282,20 +18385,14 @@
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M10" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N10" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">游戏内容数据库</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O10" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">要求地面预警清楚，不做无提示伤害</x:t>
-        </x:is>
+      <x:c r="M10" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N10" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O10" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="135" customFormat="1" ht="54" customHeight="1">
@@ -18359,20 +18456,14 @@
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M11" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N11" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">游戏内容数据库</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O11" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">避免全向反弹导致不可解</x:t>
-        </x:is>
+      <x:c r="M11" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N11" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O11" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="135" customFormat="1" ht="54" customHeight="1">
@@ -18436,20 +18527,14 @@
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M12" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N12" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">游戏内容数据库</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O12" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最直接体现精英夺取玩家枪械</x:t>
-        </x:is>
+      <x:c r="M12" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N12" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O12" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="135" customFormat="1" ht="54" customHeight="1">
@@ -18513,20 +18598,14 @@
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M13" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N13" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">游戏内容数据库</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O13" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">规则必须在HUD和场景同时预告</x:t>
-        </x:is>
+      <x:c r="M13" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N13" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O13" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="135" customFormat="1" ht="54" customHeight="1">
@@ -18590,20 +18669,14 @@
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M14" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N14" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">游戏内容数据库</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O14" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复制行为而非直接复制玩家DPS</x:t>
-        </x:is>
+      <x:c r="M14" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N14" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O14" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="135" customFormat="1" ht="54" customHeight="1">
@@ -18667,20 +18740,14 @@
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M15" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N15" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">游戏内容数据库</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O15" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">把逃脱成长变成可读追击目标</x:t>
-        </x:is>
+      <x:c r="M15" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N15" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O15" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="135" customFormat="1" ht="54" customHeight="1">
@@ -18744,20 +18811,14 @@
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M16" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N16" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">游戏内容数据库</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O16" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12只名册的长期阶段终点之一</x:t>
-        </x:is>
+      <x:c r="M16" s="17" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="N16" s="17" t="str">
+        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O16" s="17" t="str">
+        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R3a48eead61a84fb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="R866596ae33fa4b28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R9268bc8109ab497f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="Rc9d2f8511104409c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="R8d718b8f222748c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R2d56d4bcdd0d4b08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R599fafbbae5e4367"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" r:id="R041f92cb5d0b42bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf7adfbb038b5448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="R594fcde1aa0f4fc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R46273f0c23bc4307"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="Rad3e53f1ed65490d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="R9999931ccc0d406e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R49417e3a469a499c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R0e761e2868fc4421"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" r:id="R75c2f511fc5143b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -464,7 +464,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="174">
+  <x:cellXfs count="182">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -865,6 +865,30 @@
     <x:xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1154,7 +1178,7 @@
     </x:row>
     <x:row r="2" s="135" customFormat="1" ht="30" customHeight="1">
       <x:c r="A2" s="173" t="str">
-        <x:v>设计、内容与实现状态的中央索引｜最后校对：2026-08-10｜正式入口：TowerDescent3D.tscn</x:v>
+        <x:v>设计、内容与实现状态的中央索引｜最后校对：2026-08-27｜正式入口：TowerDescent3D.tscn</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="135" customFormat="1" ht="30" customHeight="1">
@@ -1315,35 +1339,25 @@
         </x:is>
       </x:c>
       <x:c r="B9" s="29" t="n">
-        <x:f>COUNTA('精英怪'!$A$5:$A$204)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="34" t="n">
-        <x:f>COUNTIF('精英怪'!$K$5:$K$204,"[已实装]")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D9" s="35" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E9" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D9" s="35" t="n">
-        <x:f>COUNTIF('精英怪'!$K$5:$K$204,"[用户设计]")</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E9" s="36" t="n">
-        <x:f>COUNTIF('精英怪'!$K$5:$K$204,"[Codex补充]")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">系统4/7</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12只唯一精英定义</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">K列统计名册来源；L列标具体内容来源</x:t>
-        </x:is>
+      <x:c r="F9" s="29" t="str">
+        <x:v>系统4/7</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="str">
+        <x:v>12只唯一精英定义；当前正式内容1/12</x:v>
+      </x:c>
+      <x:c r="H9" s="29" t="str">
+        <x:v>首只背枪的裂口爬虫已投放98—96F并完成残血逃脱、击杀玩家归因、12级成长、副枪频率、夺械转译和悬赏兑现；其余11只design_only</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="135" customFormat="1" ht="46" customHeight="1">
@@ -1556,25 +1570,17 @@
           <x:t xml:space="preserve">12精英已冻结</x:t>
         </x:is>
       </x:c>
-      <x:c r="E17" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">普通怪正式；精英原型</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">正式3D唯一名册</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G17" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">06_技术施工_怪物精英与Boss.md</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H17" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">同名只能一只</x:t>
-        </x:is>
+      <x:c r="E17" s="29" t="str">
+        <x:v>唯一系统完成；正式精英内容1/12</x:v>
+      </x:c>
+      <x:c r="F17" s="29" t="str">
+        <x:v>剩余11只独立内容与投放</x:v>
+      </x:c>
+      <x:c r="G17" s="29" t="str">
+        <x:v>06_技术施工_怪物精英与Boss.md</x:v>
+      </x:c>
+      <x:c r="H17" s="29" t="str">
+        <x:v>定义/档案/表现已解耦；未完成精英不进入随机池</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="135" customFormat="1" ht="48" customHeight="1">
@@ -17867,958 +17873,940 @@
       </x:c>
     </x:row>
     <x:row r="2" s="135" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>名册固定12只并由用户设计冻结。2026-08-13已全部接入EliteRosterService、BaseData 1.7和各自实时行为；内容名称可迭代但稳定ID不可改变。</x:v>
-      </x:c>
-      <x:c r="B2"/>
-      <x:c r="C2"/>
-      <x:c r="D2"/>
-      <x:c r="E2"/>
-      <x:c r="F2"/>
-      <x:c r="G2"/>
-      <x:c r="H2"/>
-      <x:c r="I2"/>
-      <x:c r="J2"/>
-      <x:c r="K2"/>
-      <x:c r="L2"/>
-      <x:c r="M2"/>
-      <x:c r="N2"/>
-      <x:c r="O2"/>
+      <x:c r="A2" s="174" t="str">
+        <x:v>名册固定12只并保持稳定ID。2026-08-27：首只背枪的裂口爬虫已完成独立资产、唯一投放和跨局成长闭环；其余11只保留设计与行为雏形但未投放。</x:v>
+      </x:c>
+      <x:c r="B2" s="175"/>
+      <x:c r="C2" s="175"/>
+      <x:c r="D2" s="175"/>
+      <x:c r="E2" s="175"/>
+      <x:c r="F2" s="175"/>
+      <x:c r="G2" s="175"/>
+      <x:c r="H2" s="175"/>
+      <x:c r="I2" s="175"/>
+      <x:c r="J2" s="175"/>
+      <x:c r="K2" s="175"/>
+      <x:c r="L2" s="175"/>
+      <x:c r="M2" s="175"/>
+      <x:c r="N2" s="175"/>
+      <x:c r="O2" s="175"/>
     </x:row>
     <x:row r="3" s="135" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A3" s="7" t="inlineStr">
+      <x:c r="A3" s="174" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">字体颜色：绿色=已实装；蓝色=用户设计；橙色=Codex补充。实现状态需结合事实源判断。</x:t>
         </x:is>
       </x:c>
+      <x:c r="B3" s="175"/>
+      <x:c r="C3" s="175"/>
+      <x:c r="D3" s="175"/>
+      <x:c r="E3" s="175"/>
+      <x:c r="F3" s="175"/>
+      <x:c r="G3" s="175"/>
+      <x:c r="H3" s="175"/>
+      <x:c r="I3" s="175"/>
+      <x:c r="J3" s="175"/>
+      <x:c r="K3" s="175"/>
+      <x:c r="L3" s="175"/>
+      <x:c r="M3" s="175"/>
+      <x:c r="N3" s="175"/>
+      <x:c r="O3" s="175"/>
     </x:row>
     <x:row r="4" s="135" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A4" s="13" t="inlineStr">
+      <x:c r="A4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">稳定精英ID</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="13" t="inlineStr">
+      <x:c r="B4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">独立名字</x:t>
         </x:is>
       </x:c>
-      <x:c r="C4" s="13" t="inlineStr">
+      <x:c r="C4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">基础原型</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="13" t="inlineStr">
+      <x:c r="D4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">核心特殊玩法</x:t>
         </x:is>
       </x:c>
-      <x:c r="E4" s="13" t="inlineStr">
+      <x:c r="E4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">成长方向</x:t>
         </x:is>
       </x:c>
-      <x:c r="F4" s="13" t="inlineStr">
+      <x:c r="F4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">夺械转译</x:t>
         </x:is>
       </x:c>
-      <x:c r="G4" s="13" t="inlineStr">
+      <x:c r="G4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">刷新位置</x:t>
         </x:is>
       </x:c>
-      <x:c r="H4" s="13" t="inlineStr">
+      <x:c r="H4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">唯一约束</x:t>
         </x:is>
       </x:c>
-      <x:c r="I4" s="13" t="inlineStr">
+      <x:c r="I4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">档案重点</x:t>
         </x:is>
       </x:c>
-      <x:c r="J4" s="13" t="inlineStr">
+      <x:c r="J4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">奖励概念</x:t>
         </x:is>
       </x:c>
-      <x:c r="K4" s="13" t="inlineStr">
+      <x:c r="K4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">名册来源</x:t>
         </x:is>
       </x:c>
-      <x:c r="L4" s="13" t="inlineStr">
+      <x:c r="L4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">名称/玩法来源</x:t>
         </x:is>
       </x:c>
-      <x:c r="M4" s="13" t="inlineStr">
+      <x:c r="M4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">实现状态</x:t>
         </x:is>
       </x:c>
-      <x:c r="N4" s="13" t="inlineStr">
+      <x:c r="N4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">事实源</x:t>
         </x:is>
       </x:c>
-      <x:c r="O4" s="13" t="inlineStr">
+      <x:c r="O4" s="176" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">备注</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="5" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A5" s="17" t="inlineStr">
+    <x:row r="5" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A5" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_rift_boar_armed</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="17" t="inlineStr">
+      <x:c r="B5" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">背枪的裂口爬虫</x:t>
         </x:is>
       </x:c>
-      <x:c r="C5" s="17" t="inlineStr">
+      <x:c r="C5" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">小菌猪</x:t>
         </x:is>
       </x:c>
-      <x:c r="D5" s="17" t="inlineStr">
+      <x:c r="D5" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">携带被夺取枪身，突进间隙自动射击</x:t>
         </x:is>
       </x:c>
-      <x:c r="E5" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">逃脱提升生命并增加副枪射击频率</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">枪身→跟随射击技能</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">COMBAT/ELITE；符合层级后随机</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="21" t="inlineStr">
+      <x:c r="E5" s="177" t="str">
+        <x:v>20%血量进入4.2秒可击杀撤离窗；逃脱或击杀玩家后升级，上限12级。每级生命+8%、伤害+4.5%，5/9级提高副枪追射频率</x:v>
+      </x:c>
+      <x:c r="F5" s="177" t="str">
+        <x:v>枪身→副枪追射；仅保存稳定内容ID、1—3发弹数预算和受控弹丸特征，最多3件，不保存玩家实例ID</x:v>
+      </x:c>
+      <x:c r="G5" s="177" t="str">
+        <x:v>每次行动按run_seed在98F/97F/96F三选一目标层；目标层ELITE房位置随地图种子随机；同局唯一</x:v>
+      </x:c>
+      <x:c r="H5" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I5" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">首次夺枪、逃脱次数、复仇阶段</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J5" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">枪械模块/悬赏资源</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K5" s="20" t="inlineStr">
+      <x:c r="I5" s="177" t="str">
+        <x:v>跨局等级、逃脱/击杀玩家记录、夺械转译、悬赏等级、唯一预约与陈旧预约恢复</x:v>
+      </x:c>
+      <x:c r="J5" s="177" t="str">
+        <x:v>精英专属掉落；悬赏1—5级额外兑现45/75/115/165/230魂</x:v>
+      </x:c>
+      <x:c r="K5" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L5" s="18" t="inlineStr">
+      <x:c r="L5" s="180" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[已实装]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M5" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N5" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O5" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A6" s="17" t="inlineStr">
+      <x:c r="M5" s="177" t="str">
+        <x:v>[已实装｜正式投放与成长闭环完成]</x:v>
+      </x:c>
+      <x:c r="N5" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd；src/player3d/Player3D.gd；src/world3d/Dungeon3D.gd；tests/verification/verify_first_elite_deployment_flow.gd；tests/verification/verify_first_elite_growth_flow.gd</x:v>
+      </x:c>
+      <x:c r="O5" s="177" t="str">
+        <x:v>98/97/96F每局按run_seed三选一且同局唯一；精英房首个出生点。残血撤离期间血条显示“撤离中”且仍可击杀；成功逃脱或击杀玩家后跨局成长并夺取当前枪械，下次遭遇应用成长、转译能力与悬赏。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A6" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_spore_devourer</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="17" t="inlineStr">
+      <x:c r="B6" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">吞弹者·孢子射手</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="17" t="inlineStr">
+      <x:c r="C6" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">孢子射手</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" s="17" t="inlineStr">
+      <x:c r="D6" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">吸收特定投射物并转为反击弹幕</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6" s="17" t="inlineStr">
+      <x:c r="E6" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">每次逃脱提高吸收容量和反击弹数</x:t>
         </x:is>
       </x:c>
-      <x:c r="F6" s="17" t="inlineStr">
+      <x:c r="F6" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">子弹模块→敌方弹道/状态技能</x:t>
         </x:is>
       </x:c>
-      <x:c r="G6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">COMBAT/ELITE；中深层权重提高</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" s="21" t="inlineStr">
+      <x:c r="G6" s="177" t="str">
+        <x:v>未投放；设计与行为雏形保留；完成独立内容和专项后再开放楼层</x:v>
+      </x:c>
+      <x:c r="H6" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I6" s="17" t="inlineStr">
+      <x:c r="I6" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">吞弹种类、反击记录、成长等级</x:t>
         </x:is>
       </x:c>
-      <x:c r="J6" s="17" t="inlineStr">
+      <x:c r="J6" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">子弹模块/悬赏资源</x:t>
         </x:is>
       </x:c>
-      <x:c r="K6" s="20" t="inlineStr">
+      <x:c r="K6" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L6" s="18" t="inlineStr">
+      <x:c r="L6" s="180" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[已实装]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M6" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N6" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O6" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A7" s="17" t="inlineStr">
+      <x:c r="M6" s="177" t="str">
+        <x:v>[行为雏形已实装/未投放]</x:v>
+      </x:c>
+      <x:c r="N6" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O6" s="177" t="str">
+        <x:v>稳定ID、档案字段和行为分支保留；当前deployment_status=design_only，无独立正式资产/血条/合法楼层，不进入随机池</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A7" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_iron_carapace</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="17" t="inlineStr">
+      <x:c r="B7" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">铁壁·壳甲统领</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="17" t="inlineStr">
+      <x:c r="C7" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">壳甲卫兵</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" s="17" t="inlineStr">
+      <x:c r="D7" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">旋转护甲面控制可攻击窗口，受击后反冲</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="17" t="inlineStr">
+      <x:c r="E7" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">成长后增加护甲面并缩短转向间隔</x:t>
         </x:is>
       </x:c>
-      <x:c r="F7" s="17" t="inlineStr">
+      <x:c r="F7" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">枪托/弹匣→格挡反击与耐久技能</x:t>
         </x:is>
       </x:c>
-      <x:c r="G7" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ELITE；中层后</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" s="21" t="inlineStr">
+      <x:c r="G7" s="177" t="str">
+        <x:v>未投放；设计与行为雏形保留；完成独立内容和专项后再开放楼层</x:v>
+      </x:c>
+      <x:c r="H7" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I7" s="17" t="inlineStr">
+      <x:c r="I7" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">破盾次数、反击命中、当前护甲</x:t>
         </x:is>
       </x:c>
-      <x:c r="J7" s="17" t="inlineStr">
+      <x:c r="J7" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">护甲配件/高价壳片</x:t>
         </x:is>
       </x:c>
-      <x:c r="K7" s="20" t="inlineStr">
+      <x:c r="K7" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L7" s="19" t="inlineStr">
+      <x:c r="L7" s="181" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M7" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N7" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O7" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A8" s="17" t="inlineStr">
+      <x:c r="M7" s="177" t="str">
+        <x:v>[行为雏形已实装/未投放]</x:v>
+      </x:c>
+      <x:c r="N7" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O7" s="177" t="str">
+        <x:v>稳定ID、档案字段和行为分支保留；当前deployment_status=design_only，无独立正式资产/血条/合法楼层，不进入随机池</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A8" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_ninth_hive_queen</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="17" t="inlineStr">
+      <x:c r="B8" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">蜂后“第九巢”</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" s="17" t="inlineStr">
+      <x:c r="C8" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">蜂巢怪</x:t>
         </x:is>
       </x:c>
-      <x:c r="D8" s="17" t="inlineStr">
+      <x:c r="D8" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">建立蜂巢网络，存活节点为本体转移伤害</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" s="17" t="inlineStr">
+      <x:c r="E8" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">成长后增加巢数并强化节点协同</x:t>
         </x:is>
       </x:c>
-      <x:c r="F8" s="17" t="inlineStr">
+      <x:c r="F8" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">配件→召唤物共享修饰</x:t>
         </x:is>
       </x:c>
-      <x:c r="G8" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ELITE/大型支路；中深层</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" s="21" t="inlineStr">
+      <x:c r="G8" s="177" t="str">
+        <x:v>未投放；设计与行为雏形保留；完成独立内容和专项后再开放楼层</x:v>
+      </x:c>
+      <x:c r="H8" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I8" s="17" t="inlineStr">
+      <x:c r="I8" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">存活巢数、召唤谱系、逃脱路线</x:t>
         </x:is>
       </x:c>
-      <x:c r="J8" s="17" t="inlineStr">
+      <x:c r="J8" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">蜂巢核心/召唤系模块</x:t>
         </x:is>
       </x:c>
-      <x:c r="K8" s="20" t="inlineStr">
+      <x:c r="K8" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L8" s="19" t="inlineStr">
+      <x:c r="L8" s="181" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M8" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N8" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O8" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A9" s="17" t="inlineStr">
+      <x:c r="M8" s="177" t="str">
+        <x:v>[行为雏形已实装/未投放]</x:v>
+      </x:c>
+      <x:c r="N8" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O8" s="177" t="str">
+        <x:v>稳定ID、档案字段和行为分支保留；当前deployment_status=design_only，无独立正式资产/血条/合法楼层，不进入随机池</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A9" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_emberfruit</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="17" t="inlineStr">
+      <x:c r="B9" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">焦雷果·余烬</x:t>
         </x:is>
       </x:c>
-      <x:c r="C9" s="17" t="inlineStr">
+      <x:c r="C9" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">炸弹果</x:t>
         </x:is>
       </x:c>
-      <x:c r="D9" s="17" t="inlineStr">
+      <x:c r="D9" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">投放可再生爆雷种子，本体不会首次爆炸即死亡</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9" s="17" t="inlineStr">
+      <x:c r="E9" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">成长后种子可连锁并留下燃烧区</x:t>
         </x:is>
       </x:c>
-      <x:c r="F9" s="17" t="inlineStr">
+      <x:c r="F9" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">爆炸子弹→地雷/燃烧区技能</x:t>
         </x:is>
       </x:c>
-      <x:c r="G9" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TRAP/ELITE；深度2+</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" s="21" t="inlineStr">
+      <x:c r="G9" s="177" t="str">
+        <x:v>未投放；设计与行为雏形保留；完成独立内容和专项后再开放楼层</x:v>
+      </x:c>
+      <x:c r="H9" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I9" s="17" t="inlineStr">
+      <x:c r="I9" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">种子批次、连锁次数、重生次数</x:t>
         </x:is>
       </x:c>
-      <x:c r="J9" s="17" t="inlineStr">
+      <x:c r="J9" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">爆炸模块/余烬核</x:t>
         </x:is>
       </x:c>
-      <x:c r="K9" s="20" t="inlineStr">
+      <x:c r="K9" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L9" s="19" t="inlineStr">
+      <x:c r="L9" s="181" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M9" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N9" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O9" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A10" s="17" t="inlineStr">
+      <x:c r="M9" s="177" t="str">
+        <x:v>[行为雏形已实装/未投放]</x:v>
+      </x:c>
+      <x:c r="N9" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O9" s="177" t="str">
+        <x:v>稳定ID、档案字段和行为分支保留；当前deployment_status=design_only，无独立正式资产/血条/合法楼层，不进入随机池</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A10" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_blackneedle</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="17" t="inlineStr">
+      <x:c r="B10" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">缝行者“黑针”</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" s="17" t="inlineStr">
+      <x:c r="C10" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">地刺虫</x:t>
         </x:is>
       </x:c>
-      <x:c r="D10" s="17" t="inlineStr">
+      <x:c r="D10" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">沿地面标记潜行线路，从玩家盲区连续穿刺</x:t>
         </x:is>
       </x:c>
-      <x:c r="E10" s="17" t="inlineStr">
+      <x:c r="E10" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">成长后假路线增多并获得第二次突袭</x:t>
         </x:is>
       </x:c>
-      <x:c r="F10" s="17" t="inlineStr">
+      <x:c r="F10" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">穿甲子弹/瞄具→直线穿刺与锁定</x:t>
         </x:is>
       </x:c>
-      <x:c r="G10" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">COMBAT/ELITE；狭长房/深层</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H10" s="21" t="inlineStr">
+      <x:c r="G10" s="177" t="str">
+        <x:v>未投放；设计与行为雏形保留；完成独立内容和专项后再开放楼层</x:v>
+      </x:c>
+      <x:c r="H10" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I10" s="17" t="inlineStr">
+      <x:c r="I10" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">潜行路线、揭示次数、命中角度</x:t>
         </x:is>
       </x:c>
-      <x:c r="J10" s="17" t="inlineStr">
+      <x:c r="J10" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">穿甲模块/黑针</x:t>
         </x:is>
       </x:c>
-      <x:c r="K10" s="20" t="inlineStr">
+      <x:c r="K10" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L10" s="19" t="inlineStr">
+      <x:c r="L10" s="181" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M10" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N10" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O10" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A11" s="17" t="inlineStr">
+      <x:c r="M10" s="177" t="str">
+        <x:v>[行为雏形已实装/未投放]</x:v>
+      </x:c>
+      <x:c r="N10" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O10" s="177" t="str">
+        <x:v>稳定ID、档案字段和行为分支保留；当前deployment_status=design_only，无独立正式资产/血条/合法楼层，不进入随机池</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A11" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_mirror_shell</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" s="17" t="inlineStr">
+      <x:c r="B11" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">反射者·镜壳</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" s="17" t="inlineStr">
+      <x:c r="C11" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">壳甲卫兵</x:t>
         </x:is>
       </x:c>
-      <x:c r="D11" s="17" t="inlineStr">
+      <x:c r="D11" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">周期展开镜面扇区，反射正面投射物</x:t>
         </x:is>
       </x:c>
-      <x:c r="E11" s="17" t="inlineStr">
+      <x:c r="E11" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">成长后扇区扩大但保留可读空隙</x:t>
         </x:is>
       </x:c>
-      <x:c r="F11" s="17" t="inlineStr">
+      <x:c r="F11" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">弹跳子弹/瞄具→定向反射与弱点窗口</x:t>
         </x:is>
       </x:c>
-      <x:c r="G11" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ELITE；中深层</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" s="21" t="inlineStr">
+      <x:c r="G11" s="177" t="str">
+        <x:v>未投放；设计与行为雏形保留；完成独立内容和专项后再开放楼层</x:v>
+      </x:c>
+      <x:c r="H11" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I11" s="17" t="inlineStr">
+      <x:c r="I11" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">反射弹种、弱点击破、镜面阶段</x:t>
         </x:is>
       </x:c>
-      <x:c r="J11" s="17" t="inlineStr">
+      <x:c r="J11" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">反射配件/镜壳碎片</x:t>
         </x:is>
       </x:c>
-      <x:c r="K11" s="20" t="inlineStr">
+      <x:c r="K11" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L11" s="19" t="inlineStr">
+      <x:c r="L11" s="181" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M11" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N11" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O11" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A12" s="17" t="inlineStr">
+      <x:c r="M11" s="177" t="str">
+        <x:v>[行为雏形已实装/未投放]</x:v>
+      </x:c>
+      <x:c r="N11" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O11" s="177" t="str">
+        <x:v>稳定ID、档案字段和行为分支保留；当前deployment_status=design_only，无独立正式资产/血条/合法楼层，不进入随机池</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A12" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_arms_taker</x:t>
         </x:is>
       </x:c>
-      <x:c r="B12" s="17" t="inlineStr">
+      <x:c r="B12" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">夺械者“收租人”</x:t>
         </x:is>
       </x:c>
-      <x:c r="C12" s="17" t="inlineStr">
+      <x:c r="C12" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">小菌猪/孢子射手混合</x:t>
         </x:is>
       </x:c>
-      <x:c r="D12" s="17" t="inlineStr">
+      <x:c r="D12" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">遭遇中扫描玩家主枪并切换近战/远程阶段</x:t>
         </x:is>
       </x:c>
-      <x:c r="E12" s="17" t="inlineStr">
+      <x:c r="E12" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">逃脱后永久保留一次完整枪身转译</x:t>
         </x:is>
       </x:c>
-      <x:c r="F12" s="17" t="inlineStr">
+      <x:c r="F12" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">枪身→阶段主技能；配件→副技能</x:t>
         </x:is>
       </x:c>
-      <x:c r="G12" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ELITE；任意深度低概率</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="21" t="inlineStr">
+      <x:c r="G12" s="177" t="str">
+        <x:v>未投放；设计与行为雏形保留；完成独立内容和专项后再开放楼层</x:v>
+      </x:c>
+      <x:c r="H12" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I12" s="17" t="inlineStr">
+      <x:c r="I12" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">夺械清单、阶段偏好、玩家克制记录</x:t>
         </x:is>
       </x:c>
-      <x:c r="J12" s="17" t="inlineStr">
+      <x:c r="J12" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">被夺枪械蓝图/高额悬赏</x:t>
         </x:is>
       </x:c>
-      <x:c r="K12" s="20" t="inlineStr">
+      <x:c r="K12" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L12" s="19" t="inlineStr">
+      <x:c r="L12" s="181" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M12" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N12" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O12" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A13" s="17" t="inlineStr">
+      <x:c r="M12" s="177" t="str">
+        <x:v>[行为雏形已实装/未投放]</x:v>
+      </x:c>
+      <x:c r="N12" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O12" s="177" t="str">
+        <x:v>稳定ID、档案字段和行为分支保留；当前deployment_status=design_only，无独立正式资产/血条/合法楼层，不进入随机池</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A13" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_seven_signs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B13" s="17" t="inlineStr">
+      <x:c r="B13" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">命运残响“七签”</x:t>
         </x:is>
       </x:c>
-      <x:c r="C13" s="17" t="inlineStr">
+      <x:c r="C13" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">孢子射手</x:t>
         </x:is>
       </x:c>
-      <x:c r="D13" s="17" t="inlineStr">
+      <x:c r="D13" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">每七次攻击切换一条公开命运规则</x:t>
         </x:is>
       </x:c>
-      <x:c r="E13" s="17" t="inlineStr">
+      <x:c r="E13" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">成长后规则组合从一条增至两条</x:t>
         </x:is>
       </x:c>
-      <x:c r="F13" s="17" t="inlineStr">
+      <x:c r="F13" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">命运卡→受预算约束的敌方规则</x:t>
         </x:is>
       </x:c>
-      <x:c r="G13" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EVENT/ELITE；命运卡使用后权重提高</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" s="21" t="inlineStr">
+      <x:c r="G13" s="177" t="str">
+        <x:v>未投放；设计与行为雏形保留；完成独立内容和专项后再开放楼层</x:v>
+      </x:c>
+      <x:c r="H13" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I13" s="17" t="inlineStr">
+      <x:c r="I13" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">已见规则、卡片残响、七签序列</x:t>
         </x:is>
       </x:c>
-      <x:c r="J13" s="17" t="inlineStr">
+      <x:c r="J13" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">命运残片/稀有卡机会</x:t>
         </x:is>
       </x:c>
-      <x:c r="K13" s="20" t="inlineStr">
+      <x:c r="K13" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L13" s="19" t="inlineStr">
+      <x:c r="L13" s="181" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M13" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N13" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O13" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A14" s="17" t="inlineStr">
+      <x:c r="M13" s="177" t="str">
+        <x:v>[行为雏形已实装/未投放]</x:v>
+      </x:c>
+      <x:c r="N13" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O13" s="177" t="str">
+        <x:v>稳定ID、档案字段和行为分支保留；当前deployment_status=design_only，无独立正式资产/血条/合法楼层，不进入随机池</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A14" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_echo_brood</x:t>
         </x:is>
       </x:c>
-      <x:c r="B14" s="17" t="inlineStr">
+      <x:c r="B14" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">寄生母体“回声”</x:t>
         </x:is>
       </x:c>
-      <x:c r="C14" s="17" t="inlineStr">
+      <x:c r="C14" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">蜂巢怪</x:t>
         </x:is>
       </x:c>
-      <x:c r="D14" s="17" t="inlineStr">
+      <x:c r="D14" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">召唤物复制玩家最近使用的一个配件行为</x:t>
         </x:is>
       </x:c>
-      <x:c r="E14" s="17" t="inlineStr">
+      <x:c r="E14" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">成长后可维持两种回声但降低单体强度</x:t>
         </x:is>
       </x:c>
-      <x:c r="F14" s="17" t="inlineStr">
+      <x:c r="F14" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">配件→召唤物修饰模板</x:t>
         </x:is>
       </x:c>
-      <x:c r="G14" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ELITE/巢穴主题；深度2+</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" s="21" t="inlineStr">
+      <x:c r="G14" s="177" t="str">
+        <x:v>未投放；设计与行为雏形保留；完成独立内容和专项后再开放楼层</x:v>
+      </x:c>
+      <x:c r="H14" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I14" s="17" t="inlineStr">
+      <x:c r="I14" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">复制配件、召唤代次、母体伤势</x:t>
         </x:is>
       </x:c>
-      <x:c r="J14" s="17" t="inlineStr">
+      <x:c r="J14" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">寄生样本/配件</x:t>
         </x:is>
       </x:c>
-      <x:c r="K14" s="20" t="inlineStr">
+      <x:c r="K14" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L14" s="19" t="inlineStr">
+      <x:c r="L14" s="181" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M14" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N14" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O14" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A15" s="17" t="inlineStr">
+      <x:c r="M14" s="177" t="str">
+        <x:v>[行为雏形已实装/未投放]</x:v>
+      </x:c>
+      <x:c r="N14" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O14" s="177" t="str">
+        <x:v>稳定ID、档案字段和行为分支保留；当前deployment_status=design_only，无独立正式资产/血条/合法楼层，不进入随机池</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A15" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_returning_king</x:t>
         </x:is>
       </x:c>
-      <x:c r="B15" s="17" t="inlineStr">
+      <x:c r="B15" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">逃亡王“折返者”</x:t>
         </x:is>
       </x:c>
-      <x:c r="C15" s="17" t="inlineStr">
+      <x:c r="C15" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">地刺虫</x:t>
         </x:is>
       </x:c>
-      <x:c r="D15" s="17" t="inlineStr">
+      <x:c r="D15" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">低生命触发一次公开撤退路线，阻止其离开可获额外奖励</x:t>
         </x:is>
       </x:c>
-      <x:c r="E15" s="17" t="inlineStr">
+      <x:c r="E15" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">每次成功逃脱增加新折返段和伏击次数</x:t>
         </x:is>
       </x:c>
-      <x:c r="F15" s="17" t="inlineStr">
+      <x:c r="F15" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">回旋/返航子弹→折返突袭技能</x:t>
         </x:is>
       </x:c>
-      <x:c r="G15" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">COMBAT/ELITE；有双出口房间</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" s="21" t="inlineStr">
+      <x:c r="G15" s="177" t="str">
+        <x:v>未投放；设计与行为雏形保留；完成独立内容和专项后再开放楼层</x:v>
+      </x:c>
+      <x:c r="H15" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I15" s="17" t="inlineStr">
+      <x:c r="I15" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">逃脱次数、追击失败、路线记忆</x:t>
         </x:is>
       </x:c>
-      <x:c r="J15" s="17" t="inlineStr">
+      <x:c r="J15" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">逃亡悬赏/返航模块</x:t>
         </x:is>
       </x:c>
-      <x:c r="K15" s="20" t="inlineStr">
+      <x:c r="K15" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L15" s="19" t="inlineStr">
+      <x:c r="L15" s="181" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M15" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N15" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O15" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" s="135" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A16" s="17" t="inlineStr">
+      <x:c r="M15" s="177" t="str">
+        <x:v>[行为雏形已实装/未投放]</x:v>
+      </x:c>
+      <x:c r="N15" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O15" s="177" t="str">
+        <x:v>稳定ID、档案字段和行为分支保留；当前deployment_status=design_only，无独立正式资产/血条/合法楼层，不进入随机池</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" s="135" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A16" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">elite_nameless_crown</x:t>
         </x:is>
       </x:c>
-      <x:c r="B16" s="17" t="inlineStr">
+      <x:c r="B16" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">准首领“无名王冠”</x:t>
         </x:is>
       </x:c>
-      <x:c r="C16" s="17" t="inlineStr">
+      <x:c r="C16" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Boss轻量模板</x:t>
         </x:is>
       </x:c>
-      <x:c r="D16" s="17" t="inlineStr">
+      <x:c r="D16" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">根据玩家已遭遇精英数量轮换三种战术冠位</x:t>
         </x:is>
       </x:c>
-      <x:c r="E16" s="17" t="inlineStr">
+      <x:c r="E16" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">成长受整个精英档案推进，接近区域Boss</x:t>
         </x:is>
       </x:c>
-      <x:c r="F16" s="17" t="inlineStr">
+      <x:c r="F16" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完整装配快照→三阶段技能组</x:t>
         </x:is>
       </x:c>
-      <x:c r="G16" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Boss前ELITE/特殊悬赏房；深层</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="21" t="inlineStr">
+      <x:c r="G16" s="177" t="str">
+        <x:v>未投放；设计与行为雏形保留；完成独立内容和专项后再开放楼层</x:v>
+      </x:c>
+      <x:c r="H16" s="178" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同ID全局单例；预约后才可实例化</x:t>
         </x:is>
       </x:c>
-      <x:c r="I16" s="17" t="inlineStr">
+      <x:c r="I16" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">冠位阶段、遭遇名册、夺取装配</x:t>
         </x:is>
       </x:c>
-      <x:c r="J16" s="17" t="inlineStr">
+      <x:c r="J16" s="177" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">王冠核心/阶段级奖励</x:t>
         </x:is>
       </x:c>
-      <x:c r="K16" s="20" t="inlineStr">
+      <x:c r="K16" s="179" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[用户设计]</x:t>
         </x:is>
       </x:c>
-      <x:c r="L16" s="19" t="inlineStr">
+      <x:c r="L16" s="181" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">[Codex补充]</x:t>
         </x:is>
       </x:c>
-      <x:c r="M16" s="17" t="str">
-        <x:v>[已实装]</x:v>
-      </x:c>
-      <x:c r="N16" s="17" t="str">
-        <x:v>src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
-      </x:c>
-      <x:c r="O16" s="17" t="str">
-        <x:v>稳定名册、预约唯一性、跨局成长/结算、夺械转译与独立实时行为已通过专项；正式高模可后续替换</x:v>
+      <x:c r="M16" s="177" t="str">
+        <x:v>[行为雏形已实装/未投放]</x:v>
+      </x:c>
+      <x:c r="N16" s="177" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd；src/enemy3d/EliteRosterService.gd；src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="O16" s="177" t="str">
+        <x:v>稳定ID、档案字段和行为分支保留；当前deployment_status=design_only，无独立正式资产/血条/合法楼层，不进入随机池</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf7adfbb038b5448f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="R594fcde1aa0f4fc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R46273f0c23bc4307"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="Rad3e53f1ed65490d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="R9999931ccc0d406e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R49417e3a469a499c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="R0e761e2868fc4421"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" r:id="R75c2f511fc5143b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R5895965741ab4095"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="R6e67e5d0870b4abc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R108879c454494db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="R80774a5a173c4941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="Re902e9059df147a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R56caeead88924a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="Rc2cb1d9faed94fdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" r:id="R09701448f3ff4978"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18860,9 +18860,9 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2" s="135" customFormat="1" ht="30" customHeight="1">
+    <x:row r="2" s="135" customFormat="1" ht="31.5" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>导入ItemRegistry当前37条正式记录与7条设计契约条目（Boss下行专用钥匙、3类电池、3档手电筒模块），共44条；新增2把大型近战武器均为完整WeaponInstance。价格0不自动代表免费，进度物不进入普通商店。</x:v>
+        <x:v>导入ItemRegistry当前44条正式记录与1条设计契约条目（Boss下行专用钥匙），共45条；大型电池、电芯包和三档手电模块均使用正式运行ID。价格0不自动代表免费，进度物不进入普通商店。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="135" customFormat="1" ht="30" customHeight="1">
@@ -20102,10 +20102,8 @@
           <x:t xml:space="preserve">item_ammo_pack</x:t>
         </x:is>
       </x:c>
-      <x:c r="B18" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">弹药包</x:t>
-        </x:is>
+      <x:c r="B18" s="17" t="str">
+        <x:v>通用弹药</x:v>
       </x:c>
       <x:c r="C18" s="17" t="inlineStr">
         <x:is>
@@ -22078,75 +22076,51 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">battery_l</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B42" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">大型电池</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C42" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">consumable</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D42" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">battery</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E42" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">uncommon</x:t>
-        </x:is>
+    <x:row r="42" ht="57" customHeight="1">
+      <x:c r="A42" s="167" t="str">
+        <x:v>item_battery_l</x:v>
+      </x:c>
+      <x:c r="B42" s="167" t="str">
+        <x:v>大型电池</x:v>
+      </x:c>
+      <x:c r="C42" s="167" t="str">
+        <x:v>consumable</x:v>
+      </x:c>
+      <x:c r="D42" s="167" t="str">
+        <x:v>battery</x:v>
+      </x:c>
+      <x:c r="E42" s="167" t="str">
+        <x:v>uncommon</x:v>
       </x:c>
       <x:c r="F42" s="167" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="G42" s="167" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H42" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">refill_flashlight</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I42" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">恢复手电筒 75% 电量，仅作用于自身手电筒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J42" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">scavenge_floor_3×1；scavenge_floor_4×1.5；scavenge_floor_5×1；elite_floor_2×1.2；elite_floor_3×1；boss_floor_1×0.8；loot_floor_3_4×0.8；loot_floor_5×1</x:t>
-        </x:is>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H42" s="167" t="str">
+        <x:v>restore_flashlight_charge</x:v>
+      </x:c>
+      <x:c r="I42" s="167" t="str">
+        <x:v>恢复手电筒75%电量。中深层掉落或精英包。</x:v>
+      </x:c>
+      <x:c r="J42" s="167" t="str">
+        <x:v>loot_floor_3_4×1.2；scavenge_floor_3×1；scavenge_floor_4×1；scavenge_floor_5×1；elite_floor_1×0.8；elite_floor_2×0.8；boss_floor_1×1.5</x:v>
       </x:c>
       <x:c r="K42" s="167" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L42" s="168" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">[用户设计]</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M42" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N42" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">docs/v0.1/03_技术施工_玩家与操作.md §10.3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O42" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags=consumable, battery, flashlight; 大型电池</x:t>
-        </x:is>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L42" s="168" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M42" s="167" t="str">
+        <x:v>已注册；75%恢复、堆叠与运行掉落已接入</x:v>
+      </x:c>
+      <x:c r="N42" s="167" t="str">
+        <x:v>src/base/ItemRegistry.gd；src/game/ItemUseHandler.gd；tests/verification/verify_3d_flashlight_charge_flow.gd</x:v>
+      </x:c>
+      <x:c r="O42" s="167" t="str">
+        <x:v>tags=consumable、flashlight、battery；正式ID=item_battery_l</x:v>
       </x:c>
       <x:c r="P42" s="170" t="n">
         <x:f>IF(F42&gt;0,F42,0)</x:f>
@@ -22168,75 +22142,51 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">cell_pack</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B43" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">能量包</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C43" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">consumable</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D43" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">battery</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E43" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">rare</x:t>
-        </x:is>
+    <x:row r="43" ht="57" customHeight="1">
+      <x:c r="A43" s="167" t="str">
+        <x:v>item_cell_pack</x:v>
+      </x:c>
+      <x:c r="B43" s="167" t="str">
+        <x:v>电芯包</x:v>
+      </x:c>
+      <x:c r="C43" s="167" t="str">
+        <x:v>consumable</x:v>
+      </x:c>
+      <x:c r="D43" s="167" t="str">
+        <x:v>battery</x:v>
+      </x:c>
+      <x:c r="E43" s="167" t="str">
+        <x:v>rare</x:v>
       </x:c>
       <x:c r="F43" s="167" t="n">
         <x:v>120</x:v>
       </x:c>
       <x:c r="G43" s="167" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H43" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">refill_flashlight_full</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I43" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">完全恢复手电筒电量至 100%，仅作用于自身手电筒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J43" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">elite_floor_3×0.6；elite_floor_4×0.8；boss_floor_1×0.5；boss_floor_2×0.5；loot_floor_5×1；loot_abyss×1.5</x:t>
-        </x:is>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H43" s="167" t="str">
+        <x:v>restore_flashlight_charge</x:v>
+      </x:c>
+      <x:c r="I43" s="167" t="str">
+        <x:v>完全充满手电筒。稀有掉落。</x:v>
+      </x:c>
+      <x:c r="J43" s="167" t="str">
+        <x:v>loot_floor_5×0.6；loot_abyss×1；boss_floor_2×1.5</x:v>
       </x:c>
       <x:c r="K43" s="167" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L43" s="168" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">[用户设计]</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M43" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N43" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">docs/v0.1/03_技术施工_玩家与操作.md §10.3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O43" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags=consumable, battery, flashlight, rare; 能量包</x:t>
-        </x:is>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L43" s="168" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M43" s="167" t="str">
+        <x:v>已注册；100%恢复、堆叠与运行掉落已接入</x:v>
+      </x:c>
+      <x:c r="N43" s="167" t="str">
+        <x:v>src/base/ItemRegistry.gd；src/game/ItemUseHandler.gd；tests/verification/verify_3d_flashlight_charge_flow.gd</x:v>
+      </x:c>
+      <x:c r="O43" s="167" t="str">
+        <x:v>tags=consumable、flashlight、battery；正式ID=item_cell_pack</x:v>
       </x:c>
       <x:c r="P43" s="170" t="n">
         <x:f>IF(F43&gt;0,F43,0)</x:f>
@@ -22258,31 +22208,21 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flashlight_module_basic</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B44" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">基础手电筒模块</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C44" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">equipment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D44" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flashlight</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E44" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">common</x:t>
-        </x:is>
+    <x:row r="44" ht="57" customHeight="1">
+      <x:c r="A44" s="167" t="str">
+        <x:v>item_flashlight_basic</x:v>
+      </x:c>
+      <x:c r="B44" s="167" t="str">
+        <x:v>基础模块</x:v>
+      </x:c>
+      <x:c r="C44" s="167" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="D44" s="167" t="str">
+        <x:v>flashlight_module</x:v>
+      </x:c>
+      <x:c r="E44" s="167" t="str">
+        <x:v>common</x:v>
       </x:c>
       <x:c r="F44" s="167" t="n">
         <x:v>0</x:v>
@@ -22290,41 +22230,27 @@
       <x:c r="G44" s="167" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H44" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">equip_flashlight_module</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I44" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">装备到 flashlight_module 槽位；功耗 1.0×，光照范围 1.0×；默认装备，模块切换仅在基地内可执行</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J44" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">默认装备，未列入普通掉落</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K44" s="167" t="n"/>
-      <x:c r="L44" s="168" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">[用户设计]</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M44" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N44" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">docs/v0.1/03_技术施工_玩家与操作.md §10.4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O44" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags=equipment, flashlight, default; 玩家初始装备</x:t>
-        </x:is>
+      <x:c r="H44" s="167" t="str">
+        <x:v>equip_flashlight_module</x:v>
+      </x:c>
+      <x:c r="I44" s="167" t="str">
+        <x:v>默认手电筒模块。耗电1.00×，揭示1.00×。</x:v>
+      </x:c>
+      <x:c r="J44" s="167" t="str">
+        <x:v>默认装备，未列入普通掉落</x:v>
+      </x:c>
+      <x:c r="K44" s="167"/>
+      <x:c r="L44" s="168" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M44" s="167" t="str">
+        <x:v>已注册；默认模块已接入运行与存档</x:v>
+      </x:c>
+      <x:c r="N44" s="167" t="str">
+        <x:v>src/base/ItemRegistry.gd；src/player3d/PlayerFlashlight3D.gd；src/base/BaseManager.gd</x:v>
+      </x:c>
+      <x:c r="O44" s="167" t="str">
+        <x:v>module_id=basic；tags=module、flashlight_module、basic</x:v>
       </x:c>
       <x:c r="P44" s="170" t="n">
         <x:f>IF(F44&gt;0,F44,0)</x:f>
@@ -22346,83 +22272,57 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flashlight_module_advanced</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B45" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">加强手电筒模块</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C45" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">equipment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D45" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flashlight</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E45" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">uncommon</x:t>
-        </x:is>
+    <x:row r="45" ht="57" customHeight="1">
+      <x:c r="A45" s="167" t="str">
+        <x:v>item_flashlight_advanced</x:v>
+      </x:c>
+      <x:c r="B45" s="167" t="str">
+        <x:v>加强模块</x:v>
+      </x:c>
+      <x:c r="C45" s="167" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="D45" s="167" t="str">
+        <x:v>flashlight_module</x:v>
+      </x:c>
+      <x:c r="E45" s="167" t="str">
+        <x:v>uncommon</x:v>
       </x:c>
       <x:c r="F45" s="167" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G45" s="167" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H45" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">equip_flashlight_module</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I45" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">装备到 flashlight_module 槽位；功耗 0.75×，光照范围 1.20×；需要解锁蓝图或基地工坊制造</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J45" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">loot_floor_3_4×1.5；loot_floor_5×1.2；elite_floor_2×0.8；scavenge_floor_4×1；scavenge_floor_5×1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K45" s="167" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L45" s="168" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">[用户设计]</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M45" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N45" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">docs/v0.1/03_技术施工_玩家与操作.md §10.4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O45" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags=equipment, flashlight, advanced; 蓝图或基地工坊制造</x:t>
-        </x:is>
+      <x:c r="H45" s="167" t="str">
+        <x:v>equip_flashlight_module</x:v>
+      </x:c>
+      <x:c r="I45" s="167" t="str">
+        <x:v>耗电0.7143×，揭示1.20×。蓝图解锁后工坊可选。</x:v>
+      </x:c>
+      <x:c r="J45" s="167" t="str">
+        <x:v>blueprint_attachment_unlock×1</x:v>
+      </x:c>
+      <x:c r="K45" s="167"/>
+      <x:c r="L45" s="168" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M45" s="167" t="str">
+        <x:v>已注册；Tier 1解锁、工坊切换与存档恢复已接入</x:v>
+      </x:c>
+      <x:c r="N45" s="167" t="str">
+        <x:v>src/base/ItemRegistry.gd；src/player3d/PlayerFlashlight3D.gd；src/base/BaseManager.gd；tests/verification/verify_3d_flashlight_charge_flow.gd</x:v>
+      </x:c>
+      <x:c r="O45" s="167" t="str">
+        <x:v>module_id=advanced；blueprint_unlock_tier=1</x:v>
       </x:c>
       <x:c r="P45" s="169" t="n">
         <x:f>IF(F45&gt;0,F45,0)</x:f>
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q45" s="169" t="n">
         <x:f>IF(F45&gt;0,ROUND(F45*0.5,0),0)</x:f>
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R45" s="169" t="b">
         <x:v>1</x:v>
@@ -22436,83 +22336,57 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flashlight_module_efficient</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B46" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">节能手电筒模块</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C46" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">equipment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D46" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flashlight</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E46" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">rare</x:t>
-        </x:is>
+    <x:row r="46" ht="57" customHeight="1">
+      <x:c r="A46" s="167" t="str">
+        <x:v>item_flashlight_efficient</x:v>
+      </x:c>
+      <x:c r="B46" s="167" t="str">
+        <x:v>节能模块</x:v>
+      </x:c>
+      <x:c r="C46" s="167" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="D46" s="167" t="str">
+        <x:v>flashlight_module</x:v>
+      </x:c>
+      <x:c r="E46" s="167" t="str">
+        <x:v>rare</x:v>
       </x:c>
       <x:c r="F46" s="167" t="n">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G46" s="167" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H46" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">equip_flashlight_module</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I46" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">装备到 flashlight_module 槽位；功耗 0.50×，光照范围 0.85×；稀有模块，仅精英掉落或带出</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J46" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">elite_floor_3×0.6；elite_floor_4×0.8；boss_floor_1×0.4；loot_abyss×1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K46" s="167" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L46" s="168" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">[用户设计]</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M46" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计完成；未实装</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N46" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">docs/v0.1/03_技术施工_玩家与操作.md §10.4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O46" s="167" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags=equipment, flashlight, efficient; 稀有模块</x:t>
-        </x:is>
+      <x:c r="H46" s="167" t="str">
+        <x:v>equip_flashlight_module</x:v>
+      </x:c>
+      <x:c r="I46" s="167" t="str">
+        <x:v>耗电0.50×，范围/揭示0.85×。带回99F安装后永久解锁。</x:v>
+      </x:c>
+      <x:c r="J46" s="167" t="str">
+        <x:v>elite_floor_1×0.6；elite_floor_2×0.8；boss_floor_2×1</x:v>
+      </x:c>
+      <x:c r="K46" s="167"/>
+      <x:c r="L46" s="168" t="str">
+        <x:v>[已实装]</x:v>
+      </x:c>
+      <x:c r="M46" s="167" t="str">
+        <x:v>已注册；掉落、带回解锁、工坊切换与存档已接入</x:v>
+      </x:c>
+      <x:c r="N46" s="167" t="str">
+        <x:v>src/base/ItemRegistry.gd；src/player3d/PlayerFlashlight3D.gd；src/base/BaseManager.gd；tests/verification/verify_3d_flashlight_charge_flow.gd</x:v>
+      </x:c>
+      <x:c r="O46" s="167" t="str">
+        <x:v>module_id=efficient；tags=module、flashlight_module、efficient</x:v>
       </x:c>
       <x:c r="P46" s="170" t="n">
         <x:f>IF(F46&gt;0,F46,0)</x:f>
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q46" s="170" t="n">
         <x:f>IF(F46&gt;0,ROUND(F46*0.5,0),0)</x:f>
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R46" s="170" t="b">
         <x:v>0</x:v>
@@ -25160,11 +25034,9 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2" s="135" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A2" s="161" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">价格、上架与库存公式回查《掉落物品》；ItemRegistry 运行时定义必须与本表验收一致。购买进入保险柜并生成独立实例。</x:t>
-        </x:is>
+    <x:row r="2" s="135" customFormat="1" ht="31.5" customHeight="1">
+      <x:c r="A2" s="161" t="str">
+        <x:v>价格、上架与库存公式回查《掉落物品》；ItemRegistry运行时定义必须与本表验收一致。正式99F购买进入当前I键背包并生成独立实例；独立主基地使用待装载集合，不写成保险柜。</x:v>
       </x:c>
       <x:c r="B2" s="171" t="n"/>
       <x:c r="C2" s="171" t="n"/>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R5895965741ab4095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="R6e67e5d0870b4abc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R108879c454494db7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="R80774a5a173c4941"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="Re902e9059df147a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="R56caeead88924a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="Rc2cb1d9faed94fdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" r:id="R09701448f3ff4978"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb559d6a886b44145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" r:id="R60f921fca112486b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" r:id="R7ff822943f8a448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" r:id="Rcb2cf3fc70474c75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" r:id="R338b3fba6c6e4fde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" r:id="Rbb97f41362c34e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" r:id="Rd536db2095924f3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" r:id="Rc2e7f8b2efc64987"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20120,7 +20120,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G18" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>999</x:v>
       </x:c>
       <x:c r="H18" s="17" t="inlineStr">
         <x:is>
@@ -20367,16 +20367,14 @@
         </x:is>
       </x:c>
       <x:c r="F21" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G21" s="17" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="H21" s="17" t="str"/>
-      <x:c r="I21" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">用于开启地图上的一扇房门。来自怪物掉落或房间搜索。</x:t>
-        </x:is>
+      <x:c r="I21" s="17" t="str">
+        <x:v>普通房间钥匙；不进入基地购买货架，可按单把20魂出售。Boss与任务钥匙不使用此价格。</x:v>
       </x:c>
       <x:c r="J21" s="17" t="inlineStr">
         <x:is>
@@ -20405,12 +20403,10 @@
         </x:is>
       </x:c>
       <x:c r="P21" s="162" t="n">
-        <x:f>IF(F21&gt;0,F21,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="Q21" s="162" t="n">
-        <x:f>IF(F21&gt;0,ROUND(F21*0.5,0),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R21" s="145" t="b">
         <x:v>0</x:v>
@@ -22444,8 +22440,12 @@
       <x:c r="O47" t="str">
         <x:v>tags=weapon, melee, heavy_melee, greatblade；stack_max=1；assembly_id=bp_greatblade</x:v>
       </x:c>
-      <x:c r="P47"/>
-      <x:c r="Q47"/>
+      <x:c r="P47" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="Q47" t="n">
+        <x:v>83</x:v>
+      </x:c>
       <x:c r="R47" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -22500,8 +22500,12 @@
       <x:c r="O48" t="str">
         <x:v>tags=weapon, melee, heavy_melee, waraxe；stack_max=1；assembly_id=bp_waraxe</x:v>
       </x:c>
-      <x:c r="P48"/>
-      <x:c r="Q48"/>
+      <x:c r="P48" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="Q48" t="n">
+        <x:v>120</x:v>
+      </x:c>
       <x:c r="R48" t="n">
         <x:v>0</x:v>
       </x:c>
